--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>확정 / 검토 중 / 초안 / 가안 / 보류 / 제외 — ‘제외’ 행은 목차에서 빠지고 ‘실습 목차에서 뺀 아이디어’에 비고(이유)와 함께 표시</t>
+          <t>확정 / 검토 중 / 초안 / 가안 / 보류 / 재검토 — ‘재검토’ 행은 목차에서 빠지고 ‘재검토 아이디어’에 비고(이유)와 함께 표시</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       <c r="G26" s="8" t="inlineStr"/>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -1646,7 +1646,7 @@
       <c r="G34" s="8" t="inlineStr"/>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -2319,7 +2319,7 @@
       <c r="G51" s="8" t="inlineStr"/>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
@@ -2357,7 +2357,7 @@
       <c r="G52" s="8" t="inlineStr"/>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I52" s="8" t="inlineStr">
@@ -2395,7 +2395,7 @@
       <c r="G53" s="8" t="inlineStr"/>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
@@ -2433,7 +2433,7 @@
       <c r="G54" s="8" t="inlineStr"/>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I54" s="8" t="inlineStr">
@@ -2551,7 +2551,7 @@
       <c r="G57" s="8" t="inlineStr"/>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
@@ -2589,7 +2589,7 @@
       <c r="G58" s="8" t="inlineStr"/>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
@@ -2627,7 +2627,7 @@
       <c r="G59" s="8" t="inlineStr"/>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I59" s="8" t="inlineStr">
@@ -2665,7 +2665,7 @@
       <c r="G60" s="8" t="inlineStr"/>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -2783,7 +2783,7 @@
       <c r="G63" s="8" t="inlineStr"/>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -2821,7 +2821,7 @@
       <c r="G64" s="8" t="inlineStr"/>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
@@ -2859,7 +2859,7 @@
       <c r="G65" s="8" t="inlineStr"/>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I65" s="8" t="inlineStr">
@@ -2897,7 +2897,7 @@
       <c r="G66" s="8" t="inlineStr"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I66" s="8" t="inlineStr">
@@ -3087,7 +3087,7 @@
       <c r="G71" s="8" t="inlineStr"/>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I71" s="8" t="inlineStr">
@@ -3125,7 +3125,7 @@
       <c r="G72" s="8" t="inlineStr"/>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr">
@@ -3247,7 +3247,7 @@
       <c r="G75" s="8" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I75" s="8" t="inlineStr">
@@ -3285,7 +3285,7 @@
       <c r="G76" s="8" t="inlineStr"/>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I76" s="8" t="inlineStr">
@@ -3323,7 +3323,7 @@
       <c r="G77" s="8" t="inlineStr"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
@@ -3361,7 +3361,7 @@
       <c r="G78" s="8" t="inlineStr"/>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>조아리</t>
+          <t>미정</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재검토</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재검토</t>
         </is>
       </c>
       <c r="J80" s="11" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I81" s="10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재검토</t>
         </is>
       </c>
       <c r="J81" s="11" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재검토</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재검토</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재검토</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재검토</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재검토</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>재검토</t>
         </is>
       </c>
       <c r="J87" s="11" t="inlineStr">
@@ -3953,7 +3953,7 @@
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
     <dataValidation sqref="I11:I107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"확정,검토 중,초안,가안,보류,제외"</formula1>
+      <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>수업 준비: AI로 설계하고 자료 만들기</t>
+          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>수업 준비: AI로 설계하고 자료 만들기</t>
+          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
@@ -931,7 +931,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>수업 준비: AI로 설계하고 자료 만들기</t>
+          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
@@ -969,11 +969,11 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>수업 진행: 전자칠판으로 교실 이끌기</t>
+          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>수업 진행: 전자칠판으로 교실 이끌기</t>
+          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1049,11 +1049,11 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>수업 진행: 전자칠판으로 교실 이끌기</t>
+          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1087,11 +1087,11 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>수업 진행: 전자칠판으로 교실 이끌기</t>
+          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
@@ -1129,11 +1129,11 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>개념 설명: 시뮬레이션으로 보여 주기</t>
+          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
@@ -1171,11 +1171,11 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>개념 설명: 시뮬레이션으로 보여 주기</t>
+          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1213,11 +1213,11 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>개념 설명: 시뮬레이션으로 보여 주기</t>
+          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>개념 설명: 시뮬레이션으로 보여 주기</t>
+          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -1297,11 +1297,11 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>개념 설명: 시뮬레이션으로 보여 주기</t>
+          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
@@ -1335,23 +1335,23 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>학생 활동: 교과별 활동판 만들기</t>
+          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>낚시 제목 감별 카드</t>
+          <t>답 대신 질문하는 수업 챗봇 만들기</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>[국어]</t>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
       </c>
     </row>
@@ -1377,23 +1377,23 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>학생 활동: 교과별 활동판 만들기</t>
+          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>문단 번호 읽기판</t>
+          <t>근거를 되묻는 AI 읽기 코치</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>[국어]</t>
+          <t>[국어] / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
       </c>
     </row>
@@ -1419,23 +1419,23 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>학생 활동: 교과별 활동판 만들기</t>
+          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>다섯 칸으로 쓰는 시 설계도</t>
+          <t>과제에 붙이는 AI 사용 내역 카드</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -1448,11 +1448,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>[국어]</t>
-        </is>
-      </c>
+      <c r="J29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1461,23 +1457,23 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>학생 활동: 교과별 활동판 만들기</t>
+          <t>교과 활동: 교과별 활동판 만들기</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>품사 분류 바구니에서 내 말로 품사 문제 만들기까지</t>
+          <t>낚시 제목 감별 카드</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>11, 18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1492,7 +1488,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>[국어] 같은 주제 두 앱을 기본→심화로 묶음 / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>[국어]</t>
         </is>
       </c>
     </row>
@@ -1503,23 +1499,23 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>학생 활동: 교과별 활동판 만들기</t>
+          <t>교과 활동: 교과별 활동판 만들기</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>문장 구조 분석기</t>
+          <t>문단 번호 읽기판</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -1534,7 +1530,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>[국어] / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>[국어]</t>
         </is>
       </c>
     </row>
@@ -1545,23 +1541,23 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>학생 활동: 교과별 활동판 만들기</t>
+          <t>교과 활동: 교과별 활동판 만들기</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>모둠 토의 진행판</t>
+          <t>다섯 칸으로 쓰는 시 설계도</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1576,7 +1572,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>[국어] 다른 교과 토의·토론으로 확장 가능</t>
+          <t>[국어]</t>
         </is>
       </c>
     </row>
@@ -1587,23 +1583,23 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>학생 활동: 교과별 활동판 만들기</t>
+          <t>교과 활동: 교과별 활동판 만들기</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>한 권 읽기 독서일지</t>
+          <t>품사 분류 바구니에서 내 말로 품사 문제 만들기까지</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11, 18</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -1618,45 +1614,49 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>참여 코드·학급별 기록 저장(DB)이 필요한 심화 실습</t>
+          <t>[국어] 같은 주제 두 앱을 기본→심화로 묶음 / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>학생 활동: 교과별 활동판 만들기</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>듣고 따라 말하는 영어 문장 카드</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr"/>
-      <c r="G34" s="8" t="inlineStr"/>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J34" s="9" t="inlineStr">
-        <is>
-          <t>가안 · [영어] 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
+      <c r="B34" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>교과 활동: 교과별 활동판 만들기</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>문장 구조 분석기</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>김형훈</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>[국어] / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
       </c>
     </row>
@@ -1667,23 +1667,23 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>AI 활용: AI와 질문하며 배우기</t>
+          <t>교과 활동: 교과별 활동판 만들기</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>답 대신 질문하는 수업 챗봇 만들기</t>
+          <t>모둠 토의 진행판</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>[국어] 다른 교과 토의·토론으로 확장 가능</t>
         </is>
       </c>
     </row>
@@ -1709,23 +1709,23 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>AI 활용: AI와 질문하며 배우기</t>
+          <t>교과 활동: 교과별 활동판 만들기</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>근거를 되묻는 AI 읽기 코치</t>
+          <t>한 권 읽기 독서일지</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -1740,47 +1740,47 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>[국어] / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>참여 코드·학급별 기록 저장(DB)이 필요한 심화 실습</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>AI 활용: AI와 질문하며 배우기</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>과제에 붙이는 AI 사용 내역 카드</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr"/>
+      <c r="B37" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>교과 활동: 교과별 활동판 만들기</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>듣고 따라 말하는 영어 문장 카드</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>가안 · [영어] 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1789,11 +1789,11 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>확인·피드백: 수업 중 바로 확인하기</t>
+          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
@@ -1827,11 +1827,11 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>확인·피드백: 수업 중 바로 확인하기</t>
+          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
@@ -1869,11 +1869,11 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>확인·피드백: 수업 중 바로 확인하기</t>
+          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
@@ -1911,11 +1911,11 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>정리·복습: 게임으로 다지기</t>
+          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
@@ -1949,11 +1949,11 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>정리·복습: 게임으로 다지기</t>
+          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>정리·복습: 게임으로 다지기</t>
+          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
@@ -2029,11 +2029,11 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>정리·복습: 게임으로 다지기</t>
+          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>새 학년 준비: 학급 세우기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>새 학년 준비: 학급 세우기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>새 학년 준비: 학급 세우기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr"/>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>새 학년 준비: 학급 세우기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>새 학년 준비: 학급 세우기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>새 학년 준비: 학급 세우기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr"/>
@@ -2454,11 +2454,11 @@
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>학급 운영: 매일의 기록 관리하기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr"/>
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="B56" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>학급 운영: 매일의 기록 관리하기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr"/>
@@ -2534,11 +2534,11 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>학급 운영: 매일의 기록 관리하기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr"/>
@@ -2572,11 +2572,11 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>학급 운영: 매일의 기록 관리하기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr"/>
@@ -2610,11 +2610,11 @@
         </is>
       </c>
       <c r="B59" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>학급 운영: 매일의 기록 관리하기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr"/>
@@ -2648,11 +2648,11 @@
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>학급 운영: 매일의 기록 관리하기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr"/>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="B61" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="B67" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="B68" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         </is>
       </c>
       <c r="B69" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="B70" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="B73" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="B74" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="B75" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -857,7 +857,7 @@
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>성취기준으로 지도안·학습지 초안 만들기</t>
+          <t>[공통] 성취기준으로 지도안·학습지 초안 만들기</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
@@ -899,7 +899,7 @@
       <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>학생용·교사용 학습지 한 번에 찍어내기</t>
+          <t>[공통] 학생용·교사용 학습지 한 번에 찍어내기</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
@@ -937,7 +937,7 @@
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>시험지에 바로 붙이는 함수 그래프 만들기</t>
+          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>[수학] 시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
+          <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>활동 순서와 남은 시간을 띄우는 수업 전광판</t>
+          <t>[공통] 활동 순서와 남은 시간을 띄우는 수업 전광판</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
@@ -1017,7 +1017,7 @@
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>모둠 활동 소음 신호등</t>
+          <t>[공통] 모둠 활동 소음 신호등</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>질문·발표자를 뽑는 캡슐 뽑기 기계</t>
+          <t>[공통] 질문·발표자를 뽑는 캡슐 뽑기 기계</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
@@ -1097,7 +1097,7 @@
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>종목별 경기 점수판</t>
+          <t>[체육] 종목별 경기 점수판</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
@@ -1116,11 +1116,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>[체육]</t>
-        </is>
-      </c>
+      <c r="J21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1139,7 +1135,7 @@
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>정렬 알고리즘 실험실</t>
+          <t>[정보] 정렬 알고리즘 실험실</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
@@ -1158,11 +1154,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>[정보]</t>
-        </is>
-      </c>
+      <c r="J22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1181,7 +1173,7 @@
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>화학 결합 실험실</t>
+          <t>[과학] 화학 결합 실험실</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
@@ -1200,11 +1192,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>[과학]</t>
-        </is>
-      </c>
+      <c r="J23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1223,7 +1211,7 @@
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>기체 법칙 탐구 실험실</t>
+          <t>[과학] 기체 법칙 탐구 실험실</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
@@ -1244,7 +1232,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>[과학] 화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
+          <t>화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1253,7 @@
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>설치 없이 쓰는 파이썬 연습장</t>
+          <t>[정보] 설치 없이 쓰는 파이썬 연습장</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
@@ -1284,11 +1272,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>[정보]</t>
-        </is>
-      </c>
+      <c r="J25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -1307,7 +1291,7 @@
       <c r="D26" s="8" t="inlineStr"/>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>함수 그래프가 움직이는 계수 탐구판</t>
+          <t>[수학] 함수 그래프가 움직이는 계수 탐구판</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr"/>
@@ -1324,7 +1308,7 @@
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>가안 · [수학] 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
+          <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1329,7 @@
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>답 대신 질문하는 수업 챗봇 만들기</t>
+          <t>[공통] 답 대신 질문하는 수업 챗봇 만들기</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
@@ -1387,7 +1371,7 @@
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>근거를 되묻는 AI 읽기 코치</t>
+          <t>[국어] 근거를 되묻는 AI 읽기 코치</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
@@ -1408,7 +1392,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>[국어] / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1413,7 @@
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>과제에 붙이는 AI 사용 내역 카드</t>
+          <t>[공통] 과제에 붙이는 AI 사용 내역 카드</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
@@ -1467,7 +1451,7 @@
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>낚시 제목 감별 카드</t>
+          <t>[국어] 낚시 제목 감별 카드</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
@@ -1486,11 +1470,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr">
-        <is>
-          <t>[국어]</t>
-        </is>
-      </c>
+      <c r="J30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -1509,7 +1489,7 @@
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>문단 번호 읽기판</t>
+          <t>[국어] 문단 번호 읽기판</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
@@ -1528,11 +1508,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>[국어]</t>
-        </is>
-      </c>
+      <c r="J31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -1551,7 +1527,7 @@
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>다섯 칸으로 쓰는 시 설계도</t>
+          <t>[국어] 다섯 칸으로 쓰는 시 설계도</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
@@ -1570,11 +1546,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>[국어]</t>
-        </is>
-      </c>
+      <c r="J32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -1593,7 +1565,7 @@
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>품사 분류 바구니에서 내 말로 품사 문제 만들기까지</t>
+          <t>[국어] 품사 분류 바구니에서 내 말로 품사 문제 만들기까지</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
@@ -1614,7 +1586,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>[국어] 같은 주제 두 앱을 기본→심화로 묶음 / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>같은 주제 두 앱을 기본→심화로 묶음 / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1607,7 @@
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>문장 구조 분석기</t>
+          <t>[국어] 문장 구조 분석기</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
@@ -1656,7 +1628,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>[국어] / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1649,7 @@
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>모둠 토의 진행판</t>
+          <t>[국어] 모둠 토의 진행판</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
@@ -1698,7 +1670,7 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>[국어] 다른 교과 토의·토론으로 확장 가능</t>
+          <t>다른 교과 토의·토론으로 확장 가능</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1691,7 @@
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>한 권 읽기 독서일지</t>
+          <t>[공통] 한 권 읽기 독서일지</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
@@ -1761,7 +1733,7 @@
       <c r="D37" s="8" t="inlineStr"/>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>듣고 따라 말하는 영어 문장 카드</t>
+          <t>[영어] 듣고 따라 말하는 영어 문장 카드</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr"/>
@@ -1778,7 +1750,7 @@
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>가안 · [영어] 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
+          <t>가안 · 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1771,7 @@
       <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>구글 폼 응답을 전자칠판에 띄우기</t>
+          <t>[공통] 구글 폼 응답을 전자칠판에 띄우기</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
@@ -1837,7 +1809,7 @@
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>고쳐 쓴 부분이 보이는 비교판</t>
+          <t>[국어] 고쳐 쓴 부분이 보이는 비교판</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -1856,11 +1828,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>[국어]</t>
-        </is>
-      </c>
+      <c r="J39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -1879,7 +1847,7 @@
       <c r="D40" s="6" t="inlineStr"/>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>활동 사진 반별 제출함</t>
+          <t>[공통] 활동 사진 반별 제출함</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
@@ -1921,7 +1889,7 @@
       <c r="D41" s="6" t="inlineStr"/>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>단원 용어 플래시 학습 게임</t>
+          <t>[공통] 단원 용어 플래시 학습 게임</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
@@ -1959,7 +1927,7 @@
       <c r="D42" s="6" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>개념 빙고판 30장 자동 생성기</t>
+          <t>[공통] 개념 빙고판 30장 자동 생성기</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
@@ -1997,7 +1965,7 @@
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>선사시대 시간 탐사 게임</t>
+          <t>[사회] 선사시대 시간 탐사 게임</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
@@ -2016,11 +1984,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr">
-        <is>
-          <t>[사회]</t>
-        </is>
-      </c>
+      <c r="J43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -2039,7 +2003,7 @@
       <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>개념 허들 레이스 게임</t>
+          <t>[정보] 개념 허들 레이스 게임</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
@@ -2060,7 +2024,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>[정보] 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
+          <t>실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
         </is>
       </c>
     </row>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
@@ -931,24 +931,24 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기</t>
+          <t>[공통] 활동 순서와 남은 시간을 띄우는 수업 전광판</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>김진혁</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -956,11 +956,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
-        </is>
-      </c>
+      <c r="J17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -973,24 +969,24 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>[공통] 활동 순서와 남은 시간을 띄우는 수업 전광판</t>
+          <t>[공통] 모둠 활동 소음 신호등</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>임부현</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -998,7 +994,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>전광판(2-1)과 한 꼭지로 합칠지 검토</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1011,19 +1011,19 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>[공통] 모둠 활동 소음 신호등</t>
+          <t>[공통] 질문·발표자를 뽑는 캡슐 뽑기 기계</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1036,11 +1036,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>전광판(2-1)과 한 꼭지로 합칠지 검토</t>
-        </is>
-      </c>
+      <c r="J19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1053,24 +1049,24 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>[공통] 질문·발표자를 뽑는 캡슐 뽑기 기계</t>
+          <t>[공통] 답 대신 질문하는 수업 챗봇 만들기</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1078,7 +1074,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>수업 준비·진행: 자료를 만들고 교실 이끌기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>[체육] 종목별 경기 점수판</t>
+          <t>[공통] 과제에 붙이는 AI 사용 내역 카드</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1125,28 +1125,28 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>[정보] 정렬 알고리즘 실험실</t>
+          <t>[공통] 한 권 읽기 독서일지</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -1154,7 +1154,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>참여 코드·학급별 기록 저장(DB)이 필요한 심화 실습</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1163,28 +1167,28 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>[과학] 화학 결합 실험실</t>
+          <t>[공통] 구글 폼 응답을 전자칠판에 띄우기</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>강현수</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -1201,28 +1205,28 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>[과학] 기체 법칙 탐구 실험실</t>
+          <t>[공통] 활동 사진 반별 제출함</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>강현수</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1232,7 +1236,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
+          <t>구글 앱스 스크립트 실습(clasp 자동 업로드는 빼고 진행)</t>
         </is>
       </c>
     </row>
@@ -1243,23 +1247,23 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>[정보] 설치 없이 쓰는 파이썬 연습장</t>
+          <t>[공통] 단원 용어 플래시 학습 게임</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -1275,42 +1279,42 @@
       <c r="J25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr"/>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>[수학] 함수 그래프가 움직이는 계수 탐구판</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr"/>
-      <c r="G26" s="8" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
-        </is>
-      </c>
+      <c r="B26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>[공통] 개념 빙고판 30장 자동 생성기</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1323,19 +1327,19 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>[공통] 답 대신 질문하는 수업 챗봇 만들기</t>
+          <t>[국어] 근거를 되묻는 AI 읽기 코치</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -1365,19 +1369,19 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>[국어] 근거를 되묻는 AI 읽기 코치</t>
+          <t>[국어] 낚시 제목 감별 카드</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -1390,11 +1394,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="J28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1407,19 +1407,19 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>탐구 수업: 시뮬레이션과 AI로 탐구하기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>[공통] 과제에 붙이는 AI 사용 내역 카드</t>
+          <t>[국어] 문단 번호 읽기판</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -1441,23 +1441,23 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>교과 활동: 교과별 활동판 만들기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>[국어] 낚시 제목 감별 카드</t>
+          <t>[국어] 다섯 칸으로 쓰는 시 설계도</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>교과 활동: 교과별 활동판 만들기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문단 번호 읽기판</t>
+          <t>[국어] 품사 분류 바구니에서 내 말로 품사 문제 만들기까지</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11, 18</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -1508,7 +1508,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>같은 주제 두 앱을 기본→심화로 묶음 / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -1517,23 +1521,23 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>교과 활동: 교과별 활동판 만들기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>[국어] 다섯 칸으로 쓰는 시 설계도</t>
+          <t>[국어] 문장 구조 분석기</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1546,7 +1550,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -1555,23 +1563,23 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>교과 활동: 교과별 활동판 만들기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>[국어] 품사 분류 바구니에서 내 말로 품사 문제 만들기까지</t>
+          <t>[국어] 모둠 토의 진행판</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>11, 18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -1586,7 +1594,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>같은 주제 두 앱을 기본→심화로 묶음 / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>다른 교과 토의·토론으로 확장 가능</t>
         </is>
       </c>
     </row>
@@ -1597,23 +1605,23 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>교과 활동: 교과별 활동판 만들기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문장 구조 분석기</t>
+          <t>[국어] 고쳐 쓴 부분이 보이는 비교판</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1626,51 +1634,43 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="J34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>교과 활동: 교과별 활동판 만들기</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>[국어] 모둠 토의 진행판</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
-        <is>
-          <t>다른 교과 토의·토론으로 확장 가능</t>
+      <c r="B35" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>[영어] 듣고 따라 말하는 영어 문장 카드</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr"/>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
         </is>
       </c>
     </row>
@@ -1681,28 +1681,28 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>교과 활동: 교과별 활동판 만들기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>[공통] 한 권 읽기 독서일지</t>
+          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>김진혁</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>참여 코드·학급별 기록 저장(DB)이 필요한 심화 실습</t>
+          <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
         </is>
       </c>
     </row>
@@ -1723,17 +1723,17 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>교과 활동: 교과별 활동판 만들기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr"/>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>[영어] 듣고 따라 말하는 영어 문장 카드</t>
+          <t>[수학] 함수 그래프가 움직이는 계수 탐구판</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>가안 · 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
+          <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
         </is>
       </c>
     </row>
@@ -1761,28 +1761,28 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>[공통] 구글 폼 응답을 전자칠판에 띄우기</t>
+          <t>[사회] 선사시대 시간 탐사 게임</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -1799,28 +1799,28 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>[국어] 고쳐 쓴 부분이 보이는 비교판</t>
+          <t>[과학] 화학 결합 실험실</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -1837,28 +1837,28 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>[공통] 활동 사진 반별 제출함</t>
+          <t>[과학] 기체 법칙 탐구 실험실</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>구글 앱스 스크립트 실습(clasp 자동 업로드는 빼고 진행)</t>
+          <t>화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
         </is>
       </c>
     </row>
@@ -1879,23 +1879,23 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>[공통] 단원 용어 플래시 학습 게임</t>
+          <t>[정보] 정렬 알고리즘 실험실</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -1917,28 +1917,28 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>[공통] 개념 빙고판 30장 자동 생성기</t>
+          <t>[정보] 설치 없이 쓰는 파이썬 연습장</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>[사회] 선사시대 시간 탐사 게임</t>
+          <t>[정보] 개념 허들 레이스 게임</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -1984,7 +1984,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -1993,28 +1997,28 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>확인·복습: 바로 확인하고 게임으로 다지기</t>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>[정보] 개념 허들 레이스 게임</t>
+          <t>[체육] 종목별 경기 점수판</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -2022,11 +2026,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
-        </is>
-      </c>
+      <c r="J44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -1333,13 +1333,13 @@
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>[국어] 근거를 되묻는 AI 읽기 코치</t>
+          <t>[국어] 낚시 제목 감별 카드</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -1352,11 +1352,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="J27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1375,13 +1371,13 @@
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>[국어] 낚시 제목 감별 카드</t>
+          <t>[국어] 문단 번호 읽기판</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -1413,13 +1409,13 @@
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문단 번호 읽기판</t>
+          <t>[국어] 다섯 칸으로 쓰는 시 설계도</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -1451,13 +1447,13 @@
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>[국어] 다섯 칸으로 쓰는 시 설계도</t>
+          <t>[국어] 품사 분류 바구니에서 내 말로 품사 문제 만들기까지</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11, 18</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1470,7 +1466,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J30" s="7" t="inlineStr"/>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>같은 주제 두 앱을 기본→심화로 묶음 / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -1489,13 +1489,13 @@
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>[국어] 품사 분류 바구니에서 내 말로 품사 문제 만들기까지</t>
+          <t>[국어] 문장 구조 분석기</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>11, 18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>같은 주제 두 앱을 기본→심화로 묶음 / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
       </c>
     </row>
@@ -1531,13 +1531,13 @@
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문장 구조 분석기</t>
+          <t>[국어] 모둠 토의 진행판</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>다른 교과 토의·토론으로 확장 가능</t>
         </is>
       </c>
     </row>
@@ -1573,13 +1573,13 @@
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>[국어] 모둠 토의 진행판</t>
+          <t>[국어] 고쳐 쓴 부분이 보이는 비교판</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -1592,11 +1592,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>다른 교과 토의·토론으로 확장 가능</t>
-        </is>
-      </c>
+      <c r="J33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -1615,13 +1611,13 @@
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>[국어] 고쳐 쓴 부분이 보이는 비교판</t>
+          <t>[국어] 근거를 되묻는 AI 읽기 코치</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -1634,7 +1630,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -1675,82 +1675,82 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>[수학] 함수 그래프가 움직이는 계수 탐구판</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr"/>
+      <c r="G36" s="8" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>수업자동화</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>김진혁</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr"/>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>[수학] 함수 그래프가 움직이는 계수 탐구판</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr"/>
-      <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
         </is>
       </c>
     </row>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -1333,7 +1333,7 @@
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>[국어] 낚시 제목 감별 카드</t>
+          <t>[국어] 낚시 제목 감별 카드 (사회) (정보)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문단 번호 읽기판</t>
+          <t>[국어] 문단 번호 읽기판 (영어) (사회)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
@@ -1409,7 +1409,7 @@
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>[국어] 다섯 칸으로 쓰는 시 설계도</t>
+          <t>[국어] 다섯 칸으로 쓰는 시 설계도 (영어) (음악)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>[국어] 품사 분류 바구니에서 내 말로 품사 문제 만들기까지</t>
+          <t>[국어] 품사 분류 바구니에서 내 말로 품사 문제 만들기까지 (영어) (과학)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문장 구조 분석기</t>
+          <t>[국어] 문장 구조 분석기 (영어)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>[국어] 모둠 토의 진행판</t>
+          <t>[국어] 모둠 토의 진행판 (사회) (도덕)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
@@ -1573,7 +1573,7 @@
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>[국어] 고쳐 쓴 부분이 보이는 비교판</t>
+          <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (사회)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
@@ -1611,7 +1611,7 @@
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>[국어] 근거를 되묻는 AI 읽기 코치</t>
+          <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
@@ -1653,7 +1653,7 @@
       <c r="D35" s="8" t="inlineStr"/>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>[영어] 듣고 따라 말하는 영어 문장 카드</t>
+          <t>[영어] 듣고 따라 말하는 영어 문장 카드 (국어)</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr"/>
@@ -1691,7 +1691,7 @@
       <c r="D36" s="8" t="inlineStr"/>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>[수학] 함수 그래프가 움직이는 계수 탐구판</t>
+          <t>[수학] 함수 그래프가 움직이는 계수 탐구판 (과학) (정보)</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기</t>
+          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
       <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>[사회] 선사시대 시간 탐사 게임</t>
+          <t>[사회] 선사시대 시간 탐사 게임 (과학) (국어)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
@@ -1809,7 +1809,7 @@
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>[과학] 화학 결합 실험실</t>
+          <t>[과학] 화학 결합 실험실 (수학) (정보)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -1847,7 +1847,7 @@
       <c r="D40" s="6" t="inlineStr"/>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>[과학] 기체 법칙 탐구 실험실</t>
+          <t>[과학] 기체 법칙 탐구 실험실 (수학)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       <c r="D41" s="6" t="inlineStr"/>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>[정보] 정렬 알고리즘 실험실</t>
+          <t>[정보] 정렬 알고리즘 실험실 (수학)</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
@@ -1927,7 +1927,7 @@
       <c r="D42" s="6" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>[정보] 설치 없이 쓰는 파이썬 연습장</t>
+          <t>[정보] 설치 없이 쓰는 파이썬 연습장 (수학) (과학)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>[정보] 개념 허들 레이스 게임</t>
+          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (사회)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
@@ -2007,7 +2007,7 @@
       <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>[체육] 종목별 경기 점수판</t>
+          <t>[체육] 종목별 경기 점수판 (수학) (영어)</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr"/>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
@@ -1441,19 +1441,19 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>[국어] 품사 분류 바구니에서 내 말로 품사 문제 만들기까지 (영어) (과학)</t>
+          <t>[국어] 끌어다 놓는 품사 분류 바구니 (영어) (과학)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>11, 18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>같은 주제 두 앱을 기본→심화로 묶음 / AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>기본편. 같은 주제의 심화편은 PART 4 ‘품사 문제 출제기’</t>
         </is>
       </c>
     </row>
@@ -1483,19 +1483,19 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문장 구조 분석기 (영어)</t>
+          <t>[국어] 모둠 토의 진행판 (사회) (도덕)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+          <t>다른 교과 토의·토론으로 확장 가능</t>
         </is>
       </c>
     </row>
@@ -1525,19 +1525,19 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>[국어] 모둠 토의 진행판 (사회) (도덕)</t>
+          <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (사회)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -1550,167 +1550,163 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J32" s="7" t="inlineStr">
-        <is>
-          <t>다른 교과 토의·토론으로 확장 가능</t>
-        </is>
-      </c>
+      <c r="J32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (사회)</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>[영어] 듣고 따라 말하는 영어 문장 카드 (국어)</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학)</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr"/>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J34" s="7" t="inlineStr">
-        <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr"/>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>[수학] 함수 그래프가 움직이는 계수 탐구판 (과학) (정보)</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr"/>
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
+      <c r="B35" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr"/>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>[영어] 듣고 따라 말하는 영어 문장 카드 (국어)</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr"/>
-      <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학)</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>김진혁</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B36" s="8" t="n">
+      <c r="B36" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr"/>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>[수학] 함수 그래프가 움직이는 계수 탐구판 (과학) (정보)</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr"/>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J36" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
-        </is>
-      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>[사회] 선사시대 시간 탐사 게임 (과학) (국어)</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>이은덕</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -1723,24 +1719,24 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학)</t>
+          <t>[체육] 종목별 경기 점수판 (수학) (영어)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>김진혁</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -1748,11 +1744,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
-        </is>
-      </c>
+      <c r="J37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1761,28 +1753,28 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>[사회] 선사시대 시간 탐사 게임 (과학) (국어)</t>
+          <t>[국어] 내 말로 만드는 품사 문제 출제기 (영어)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -1790,7 +1782,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: AI API(OpenAI)로 학생 글에서 문제를 만듦 / 기본편은 PART 3 ‘품사 분류 바구니’</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -1799,28 +1795,28 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>[과학] 화학 결합 실험실 (수학) (정보)</t>
+          <t>[국어] 문장 구조 분석기 (영어)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>강현수</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -1828,7 +1824,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: AI API(Gemini)로 문장을 분석함</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -1837,28 +1837,28 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr"/>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>[과학] 기체 법칙 탐구 실험실 (수학)</t>
+          <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>강현수</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
+          <t>심화 이유: AI API 연결과 ‘답 대신 되묻기’ 프롬프트 설계가 필요함</t>
         </is>
       </c>
     </row>
@@ -1879,28 +1879,28 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr"/>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>[정보] 정렬 알고리즘 실험실 (수학)</t>
+          <t>[과학] 화학 결합 실험실 (수학) (정보)</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -1908,7 +1908,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: 전자 이동·공유를 과학적으로 맞게 움직이는 애니메이션 구현</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -1917,28 +1921,28 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>[정보] 설치 없이 쓰는 파이썬 연습장 (수학) (과학)</t>
+          <t>[과학] 기체 법칙 탐구 실험실 (수학)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -1946,7 +1950,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J42" s="7" t="inlineStr"/>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: 압력·부피·온도 관계를 입자 움직임으로 시뮬레이션 / 화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -1955,28 +1963,28 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (사회)</t>
+          <t>[정보] 정렬 알고리즘 실험실 (수학)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -1986,7 +1994,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
+          <t>심화 이유: 정렬 과정을 단계별로 멈추고 보여 주는 상태 관리</t>
         </is>
       </c>
     </row>
@@ -1997,23 +2005,23 @@
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>과목별 실습: 교과 수업에 맞춘 앱 만들기</t>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>[체육] 종목별 경기 점수판 (수학) (영어)</t>
+          <t>[정보] 설치 없이 쓰는 파이썬 연습장 (수학) (과학)</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -2026,70 +2034,81 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="J44" s="7" t="inlineStr"/>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: 브라우저 안에서 파이썬을 실행하는 외부 실행 환경(Pyodide) 연결</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>업무자동화</t>
+          <t>수업자동화</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr"/>
       <c r="E45" s="7" t="inlineStr">
         <is>
+          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (사회)</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
           <t>바이브 코딩이란?</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 개념 (패러다임의 변화)
 개발 과정 (요구분석-설계-구현-테스트-배포-운영)
 필수 용어 (예: 라이브러리, 빌드, 디버깅, 배포 등)</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr"/>
-      <c r="H45" s="6" t="inlineStr"/>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트가 결과를 좌우한다 (bad vs good)
-마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
-        </is>
-      </c>
       <c r="G46" s="6" t="inlineStr"/>
       <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" s="6" t="inlineStr">
@@ -2116,30 +2135,23 @@
       <c r="D47" s="6" t="inlineStr"/>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr"/>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>수업 22</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
+          <t>프롬프트 기초</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트가 결과를 좌우한다 (bad vs good)
+마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="J47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -2158,22 +2170,30 @@
       <c r="D48" s="6" t="inlineStr"/>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>사례</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr"/>
-      <c r="H48" s="6" t="inlineStr"/>
+          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>수업 22</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>김형훈</t>
+        </is>
+      </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -2182,40 +2202,32 @@
         </is>
       </c>
       <c r="B49" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr"/>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>진급 반 인계 카드</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr"/>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
+          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>사례</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>2월</t>
-        </is>
-      </c>
+      <c r="J49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -2234,66 +2246,70 @@
       <c r="D50" s="6" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>조건을 반영한 자리 배치</t>
+          <t>진급 반 인계 카드</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
       <c r="G50" s="6" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>조건을 반영한 자리 배치</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>3월</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr"/>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>모둠 자동 편성기</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr"/>
-      <c r="G51" s="8" t="inlineStr"/>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2330,7 @@
       <c r="D52" s="8" t="inlineStr"/>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>학급 규칙 함께 정하기 투표판</t>
+          <t>모둠 자동 편성기</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr"/>
@@ -2331,7 +2347,7 @@
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>가안 · 3월 학급 세우기 활동</t>
+          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2368,7 @@
       <c r="D53" s="8" t="inlineStr"/>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>1인 1역 역할 배정표</t>
+          <t>학급 규칙 함께 정하기 투표판</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr"/>
@@ -2369,7 +2385,7 @@
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
+          <t>가안 · 3월 학급 세우기 활동</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2406,7 @@
       <c r="D54" s="8" t="inlineStr"/>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>전자칠판용 우리 반 일과 안내판</t>
+          <t>1인 1역 역할 배정표</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr"/>
@@ -2407,49 +2423,45 @@
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
+          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr"/>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>전자칠판용 우리 반 일과 안내판</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr"/>
+      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
           <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr"/>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>특별활동 자동 출석부</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>진정숙</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr">
-        <is>
-          <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
         </is>
       </c>
     </row>
@@ -2470,64 +2482,68 @@
       <c r="D56" s="6" t="inlineStr"/>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>청소 구역 점검판</t>
+          <t>특별활동 자동 출석부</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
       <c r="G56" s="6" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>청소 구역 점검판</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr"/>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>과제 제출 체크리스트</t>
-        </is>
-      </c>
-      <c r="F57" s="9" t="inlineStr"/>
-      <c r="G57" s="8" t="inlineStr"/>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
-        </is>
-      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -2546,7 +2562,7 @@
       <c r="D58" s="8" t="inlineStr"/>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>칭찬 포인트 보드</t>
+          <t>과제 제출 체크리스트</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr"/>
@@ -2563,7 +2579,7 @@
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
+          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2600,7 @@
       <c r="D59" s="8" t="inlineStr"/>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>학급 행사 D-day 게시판</t>
+          <t>칭찬 포인트 보드</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr"/>
@@ -2601,7 +2617,7 @@
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>가안</t>
+          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2638,7 @@
       <c r="D60" s="8" t="inlineStr"/>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>학급 문고 대출 기록표</t>
+          <t>학급 행사 D-day 게시판</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr"/>
@@ -2644,42 +2660,42 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr"/>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>겹치지 않는 학부모 상담 예약</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr"/>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>임부현</t>
-        </is>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr"/>
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr"/>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>학급 문고 대출 기록표</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr"/>
+      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -2698,66 +2714,66 @@
       <c r="D62" s="6" t="inlineStr"/>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>정원이 차면 자동 마감되는 신청서</t>
+          <t>겹치지 않는 학부모 상담 예약</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
       <c r="G62" s="6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr"/>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>정원이 차면 자동 마감되는 신청서</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
         <is>
           <t>방과후학교·학부모 연수</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>안내용 웹 가정통신문 만들기</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr"/>
-      <c r="G63" s="8" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2794,7 @@
       <c r="D64" s="8" t="inlineStr"/>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>참여 여부를 받는 가정통신문과 미응답 확인</t>
+          <t>안내용 웹 가정통신문 만들기</t>
         </is>
       </c>
       <c r="F64" s="9" t="inlineStr"/>
@@ -2795,7 +2811,7 @@
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>가안 · 구글 시트로 응답 수합</t>
+          <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2832,7 @@
       <c r="D65" s="8" t="inlineStr"/>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>공개수업 참관 신청서</t>
+          <t>참여 여부를 받는 가정통신문과 미응답 확인</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr"/>
@@ -2833,7 +2849,7 @@
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>가안 · 시간대별 정원 표시</t>
+          <t>가안 · 구글 시트로 응답 수합</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2870,7 @@
       <c r="D66" s="8" t="inlineStr"/>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>상담 전 사전 질문지</t>
+          <t>공개수업 참관 신청서</t>
         </is>
       </c>
       <c r="F66" s="9" t="inlineStr"/>
@@ -2871,47 +2887,47 @@
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
+          <t>가안 · 시간대별 정원 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr"/>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>상담 전 사전 질문지</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr"/>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
           <t>가안 · 상담 예약(4-1)과 이어지는 실습</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B67" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr"/>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>회신서 미제출자 확인기</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr"/>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -2930,18 +2946,18 @@
       <c r="D68" s="6" t="inlineStr"/>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>QR로 받는 교직원 연수 서명부</t>
+          <t>회신서 미제출자 확인기</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
@@ -2968,13 +2984,13 @@
       <c r="D69" s="6" t="inlineStr"/>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>부서 통합 외부인 방문대장</t>
+          <t>QR로 받는 교직원 연수 서명부</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -3006,64 +3022,64 @@
       <c r="D70" s="6" t="inlineStr"/>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>공문서 표기 점검기</t>
+          <t>부서 통합 외부인 방문대장</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
       <c r="G70" s="6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>행정 업무: 서류와 수합 줄이기</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr"/>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>공문서 표기 점검기</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J70" s="7" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr"/>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>행사 물품 수요 조사 집계기</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr"/>
-      <c r="G71" s="8" t="inlineStr"/>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 반별 수량을 모아 합계표로</t>
-        </is>
-      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -3082,7 +3098,7 @@
       <c r="D72" s="8" t="inlineStr"/>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>특별실·기자재 예약판</t>
+          <t>행사 물품 수요 조사 집계기</t>
         </is>
       </c>
       <c r="F72" s="9" t="inlineStr"/>
@@ -3099,49 +3115,45 @@
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
+          <t>가안 · 반별 수량을 모아 합계표로</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>행정 업무: 서류와 수합 줄이기</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr"/>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>특별실·기자재 예약판</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
           <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr"/>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>단원 끝 학생 자기평가 카드</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr"/>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J73" s="7" t="inlineStr">
-        <is>
-          <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
         </is>
       </c>
     </row>
@@ -3162,66 +3174,70 @@
       <c r="D74" s="6" t="inlineStr"/>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>방학 중 안부 체크인</t>
+          <t>단원 끝 학생 자기평가 카드</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
       <c r="G74" s="6" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr"/>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>방학 중 안부 체크인</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
         <is>
           <t>7월</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr"/>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>관찰 기록으로 단원 평어 초안 만들기</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr"/>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3258,7 @@
       <c r="D76" s="8" t="inlineStr"/>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>수행평가 채점 기준표(루브릭) 채점기</t>
+          <t>관찰 기록으로 단원 평어 초안 만들기</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr"/>
@@ -3259,7 +3275,7 @@
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강</t>
+          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3296,7 @@
       <c r="D77" s="8" t="inlineStr"/>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>문항별 정답률 분석표</t>
+          <t>수행평가 채점 기준표(루브릭) 채점기</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
@@ -3297,7 +3313,7 @@
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
+          <t>가안 · 평가·기록 보강</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3334,7 @@
       <c r="D78" s="8" t="inlineStr"/>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>생활기록부 글자 수·표현 점검기</t>
+          <t>문항별 정답률 분석표</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr"/>
@@ -3335,50 +3351,52 @@
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
+          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr"/>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>생활기록부 글자 수·표현 점검기</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="inlineStr">
+        <is>
           <t>가안 · 평가·기록 보강 · 바이트 수와 쓰지 않는 표현을 표시, 내용은 외부로 보내지 않음</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr"/>
-      <c r="C79" s="11" t="inlineStr"/>
-      <c r="D79" s="10" t="inlineStr"/>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>발표 모드</t>
-        </is>
-      </c>
-      <c r="F79" s="11" t="inlineStr"/>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>강현수</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="J79" s="11" t="inlineStr">
-        <is>
-          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>업무자동화</t>
+          <t>수업자동화</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr"/>
@@ -3386,18 +3404,18 @@
       <c r="D80" s="10" t="inlineStr"/>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>기기대여대장</t>
+          <t>발표 모드</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -3407,7 +3425,7 @@
       </c>
       <c r="J80" s="11" t="inlineStr">
         <is>
-          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
+          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
         </is>
       </c>
     </row>
@@ -3422,13 +3440,13 @@
       <c r="D81" s="10" t="inlineStr"/>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>스마트 시간표 교체</t>
+          <t>기기대여대장</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -3443,7 +3461,7 @@
       </c>
       <c r="J81" s="11" t="inlineStr">
         <is>
-          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
+          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
         </is>
       </c>
     </row>
@@ -3458,18 +3476,18 @@
       <c r="D82" s="10" t="inlineStr"/>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>준비물, 전달사항 알림장 사이트</t>
+          <t>스마트 시간표 교체</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>이지상</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -3479,7 +3497,7 @@
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
+          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
         </is>
       </c>
     </row>
@@ -3494,18 +3512,18 @@
       <c r="D83" s="10" t="inlineStr"/>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>키워드 레이더</t>
+          <t>준비물, 전달사항 알림장 사이트</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>이지상</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -3515,7 +3533,7 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
+          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
         </is>
       </c>
     </row>
@@ -3530,13 +3548,13 @@
       <c r="D84" s="10" t="inlineStr"/>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>부장회의록 및 주간계획</t>
+          <t>키워드 레이더</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -3551,7 +3569,7 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
+          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
         </is>
       </c>
     </row>
@@ -3566,18 +3584,18 @@
       <c r="D85" s="10" t="inlineStr"/>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>우리반 출석부</t>
+          <t>부장회의록 및 주간계획</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>이승엽</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -3587,7 +3605,7 @@
       </c>
       <c r="J85" s="11" t="inlineStr">
         <is>
-          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
+          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
         </is>
       </c>
     </row>
@@ -3602,18 +3620,18 @@
       <c r="D86" s="10" t="inlineStr"/>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>학부모 상담 기록요약</t>
+          <t>우리반 출석부</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
@@ -3623,7 +3641,7 @@
       </c>
       <c r="J86" s="11" t="inlineStr">
         <is>
-          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
+          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
         </is>
       </c>
     </row>
@@ -3638,42 +3656,66 @@
       <c r="D87" s="10" t="inlineStr"/>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>반 편성 조건 점검기</t>
+          <t>학부모 상담 기록요약</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
       <c r="G87" s="10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="J87" s="11" t="inlineStr">
+        <is>
+          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr"/>
+      <c r="C88" s="11" t="inlineStr"/>
+      <c r="D88" s="10" t="inlineStr"/>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>반 편성 조건 점검기</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="inlineStr"/>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H87" s="10" t="inlineStr">
+      <c r="H88" s="10" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
+      <c r="I88" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J87" s="11" t="inlineStr">
+      <c r="J88" s="11" t="inlineStr">
         <is>
           <t>특수 배려·분리 요청 같은 민감 정보를 다루고 LLM API가 필요함. 제안자도 다음 회의에서 논의하기로 남겨 둠</t>
         </is>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="n"/>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="7" t="n"/>
-      <c r="D88" s="6" t="n"/>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="n"/>
-      <c r="G88" s="6" t="n"/>
-      <c r="H88" s="6" t="n"/>
-      <c r="I88" s="6" t="n"/>
-      <c r="J88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>
@@ -3903,6 +3945,18 @@
       <c r="I107" s="6" t="n"/>
       <c r="J107" s="7" t="n"/>
     </row>
+    <row r="108">
+      <c r="A108" s="6" t="n"/>
+      <c r="B108" s="6" t="n"/>
+      <c r="C108" s="7" t="n"/>
+      <c r="D108" s="6" t="n"/>
+      <c r="E108" s="7" t="n"/>
+      <c r="F108" s="7" t="n"/>
+      <c r="G108" s="6" t="n"/>
+      <c r="H108" s="6" t="n"/>
+      <c r="I108" s="6" t="n"/>
+      <c r="J108" s="7" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B7:J7"/>
@@ -3913,10 +3967,10 @@
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A11:A107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A11:A108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
-    <dataValidation sqref="I11:I107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I11:I108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -1333,7 +1333,7 @@
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>[국어] 낚시 제목 감별 카드 (사회) (정보)</t>
+          <t>[국어] 낚시 제목 감별 카드 (사회) (도덕) (정보) (영어)</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문단 번호 읽기판 (영어) (사회)</t>
+          <t>[국어] 문단 번호 읽기판 (영어) (사회) (과학) (한문)</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
@@ -1409,7 +1409,7 @@
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>[국어] 다섯 칸으로 쓰는 시 설계도 (영어) (음악)</t>
+          <t>[국어] 다섯 칸으로 쓰는 시 설계도 (영어) (음악) (미술)</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
@@ -1447,7 +1447,7 @@
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>[국어] 끌어다 놓는 품사 분류 바구니 (영어) (과학)</t>
+          <t>[국어] 끌어다 놓는 품사 분류 바구니 (영어) (과학) (실과) (기술·가정)</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
@@ -1489,7 +1489,7 @@
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>[국어] 모둠 토의 진행판 (사회) (도덕)</t>
+          <t>[국어] 모둠 토의 진행판 (사회) (도덕) (과학) (진로)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
@@ -1531,7 +1531,7 @@
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (사회)</t>
+          <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (제2외국어) (정보)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
@@ -1569,7 +1569,7 @@
       <c r="D33" s="8" t="inlineStr"/>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>[영어] 듣고 따라 말하는 영어 문장 카드 (국어)</t>
+          <t>[영어] 듣고 따라 말하는 영어 문장 카드 (제2외국어) (국어) (한문)</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr"/>
@@ -1607,7 +1607,7 @@
       <c r="D34" s="8" t="inlineStr"/>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>[수학] 함수 그래프가 움직이는 계수 탐구판 (과학) (정보)</t>
+          <t>[수학] 함수 그래프가 움직이는 계수 탐구판 (물리) (경제) (정보)</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr"/>
@@ -1645,7 +1645,7 @@
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학)</t>
+          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학) (경제)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
@@ -1687,7 +1687,7 @@
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>[사회] 선사시대 시간 탐사 게임 (과학) (국어)</t>
+          <t>[사회] 선사시대 시간 탐사 게임 (역사) (지구과학) (미술)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
@@ -1763,7 +1763,7 @@
       <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>[국어] 내 말로 만드는 품사 문제 출제기 (영어)</t>
+          <t>[국어] 내 말로 만드는 품사 문제 출제기 (영어) (제2외국어) (한문)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
@@ -1805,7 +1805,7 @@
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문장 구조 분석기 (영어)</t>
+          <t>[국어] 문장 구조 분석기 (영어) (제2외국어)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
@@ -1847,7 +1847,7 @@
       <c r="D40" s="6" t="inlineStr"/>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학)</t>
+          <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학) (역사) (도덕)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
@@ -1889,7 +1889,7 @@
       <c r="D41" s="6" t="inlineStr"/>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>[과학] 화학 결합 실험실 (수학) (정보)</t>
+          <t>[과학] 화학 결합 실험실 (물리) (지구과학) (수학)</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
@@ -1931,7 +1931,7 @@
       <c r="D42" s="6" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>[과학] 기체 법칙 탐구 실험실 (수학)</t>
+          <t>[과학] 기체 법칙 탐구 실험실 (수학) (물리)</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
@@ -1973,7 +1973,7 @@
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>[정보] 정렬 알고리즘 실험실 (수학)</t>
+          <t>[정보] 정렬 알고리즘 실험실 (수학) (실과)</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
       <c r="D45" s="6" t="inlineStr"/>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (사회)</t>
+          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (한국사) (통합교과)</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr"/>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -506,19 +506,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,34 +568,46 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>세부 내용</t>
+          <t>파트 설명</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>꼭지 아래에 보일 항목. 한 칸 안에서 줄을 바꿔(Alt+Enter) 하나씩 적기</t>
+          <t>PART 제목 아래에 보일 설명(사용 도구 등). 그 파트의 첫 꼭지 행에만 적으면 됨</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>바탕 아이디어 번호</t>
+          <t>세부 내용</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>같은 권의 아이디어 번호를 쉼표로 (예: 21, 22). 다른 권 아이디어는 '수업 14', '업무 7'처럼</t>
+          <t>꼭지 아래에 보일 항목. 한 칸 안에서 줄을 바꿔(Alt+Enter) 하나씩 적기</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>바탕 아이디어 번호</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>같은 권의 아이디어 번호를 쉼표로 (예: 21, 22). 다른 권 아이디어는 '수업 14', '업무 7'처럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>확정 / 검토 중 / 초안 / 가안 / 보류 / 재검토 — ‘재검토’ 행은 목차에서 빠지고 ‘재검토 아이디어’에 비고(이유)와 함께 표시</t>
         </is>
@@ -618,35 +631,40 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>파트 설명</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>꼭지 번호</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>꼭지 제목</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>세부 내용</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>바탕 아이디어 번호</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>저자</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -669,29 +687,30 @@
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>프롬프트 기초</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>프롬프트가 결과를 좌우한다
 마크다운 기초</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>검토 중</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -707,27 +726,28 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩이란?</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 개념 (패러다임의 변화)
 개발 과정 (요구분석-설계-구현-테스트-배포-운영)
 필수 용어 (예: 라이브러리, 빌드, 디버깅, 배포 등)</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr"/>
       <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -743,26 +763,27 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>프롬프트 기초</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>프롬프트가 결과를 좌우한다 (bad vs good)
 마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -778,29 +799,30 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
         </is>
@@ -820,25 +842,26 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>사례</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -854,29 +877,34 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>사용 도구: ChatGPT의 Codex 활용</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>[공통] 성취기준으로 지도안·학습지 초안 만들기</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
@@ -896,29 +924,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>[공통] 학생용·교사용 학습지 한 번에 찍어내기</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -934,29 +963,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>[공통] 활동 순서와 남은 시간을 띄우는 수업 전광판</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>이은덕</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -972,29 +1002,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>[공통] 모둠 활동 소음 신호등</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
         <is>
           <t>전광판(2-1)과 한 꼭지로 합칠지 검토</t>
         </is>
@@ -1014,29 +1045,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>[공통] 질문·발표자를 뽑는 캡슐 뽑기 기계</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr"/>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1052,29 +1084,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>[공통] 답 대신 질문하는 수업 챗봇 만들기</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
         </is>
@@ -1094,29 +1127,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>[공통] 과제에 붙이는 AI 사용 내역 카드</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1132,29 +1166,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>[공통] 한 권 읽기 독서일지</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
         <is>
           <t>참여 코드·학급별 기록 저장(DB)이 필요한 심화 실습</t>
         </is>
@@ -1174,29 +1209,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>[공통] 구글 폼 응답을 전자칠판에 띄우기</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1212,29 +1248,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>[공통] 활동 사진 반별 제출함</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>구글 앱스 스크립트 실습(clasp 자동 업로드는 빼고 진행)</t>
         </is>
@@ -1254,29 +1291,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>[공통] 단원 용어 플래시 학습 게임</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>이은덕</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr"/>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1292,29 +1330,30 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>[공통] 개념 빙고판 30장 자동 생성기</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr"/>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1330,29 +1369,34 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>사용 도구: ChatGPT의 Codex 활용</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>[국어] 낚시 제목 감별 카드 (사회) (도덕) (정보) (영어)</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr"/>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1368,29 +1412,30 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr"/>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>[국어] 문단 번호 읽기판 (영어) (사회) (과학) (한문)</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr"/>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1406,29 +1451,30 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>[국어] 다섯 칸으로 쓰는 시 설계도 (영어) (음악) (미술)</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr"/>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1444,29 +1490,30 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>[국어] 끌어다 놓는 품사 분류 바구니 (영어) (과학) (실과) (기술·가정)</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr">
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>기본편. 같은 주제의 심화편은 PART 4 ‘품사 문제 출제기’</t>
         </is>
@@ -1486,29 +1533,30 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>[국어] 모둠 토의 진행판 (사회) (도덕) (과학) (진로)</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
         <is>
           <t>다른 교과 토의·토론으로 확장 가능</t>
         </is>
@@ -1528,29 +1576,30 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (제2외국어) (정보)</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J32" s="7" t="inlineStr"/>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -1566,25 +1615,26 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr"/>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>[영어] 듣고 따라 말하는 영어 문장 카드 (제2외국어) (국어) (한문)</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr"/>
-      <c r="G33" s="8" t="inlineStr"/>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>가안 · 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
         </is>
@@ -1604,25 +1654,26 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr"/>
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>[수학] 함수 그래프가 움직이는 계수 탐구판 (물리) (경제) (정보)</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr"/>
-      <c r="G34" s="8" t="inlineStr"/>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
         </is>
@@ -1642,29 +1693,30 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학) (경제)</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>김진혁</t>
         </is>
       </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
         </is>
@@ -1684,29 +1736,30 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>[사회] 선사시대 시간 탐사 게임 (역사) (지구과학) (미술)</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr"/>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>이은덕</t>
         </is>
       </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr"/>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -1722,29 +1775,30 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>[체육] 종목별 경기 점수판 (수학) (영어)</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr"/>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>이은덕</t>
         </is>
       </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr"/>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1760,29 +1814,34 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>사용 도구: ChatGPT의 Codex로 만들고, 구글 앱스 스크립트 또는 OpenAI API를 붙여서 실습</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>[국어] 내 말로 만드는 품사 문제 출제기 (영어) (제2외국어) (한문)</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
         <is>
           <t>심화 이유: AI API(OpenAI)로 학생 글에서 문제를 만듦 / 기본편은 PART 3 ‘품사 분류 바구니’</t>
         </is>
@@ -1802,29 +1861,30 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>[국어] 문장 구조 분석기 (영어) (제2외국어)</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>심화 이유: AI API(Gemini)로 문장을 분석함</t>
         </is>
@@ -1844,29 +1904,30 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학) (역사) (도덕)</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>심화 이유: AI API 연결과 ‘답 대신 되묻기’ 프롬프트 설계가 필요함</t>
         </is>
@@ -1886,29 +1947,30 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>[과학] 화학 결합 실험실 (물리) (지구과학) (수학)</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>강현수</t>
         </is>
       </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>심화 이유: 전자 이동·공유를 과학적으로 맞게 움직이는 애니메이션 구현</t>
         </is>
@@ -1928,29 +1990,30 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>[과학] 기체 법칙 탐구 실험실 (수학) (물리)</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>강현수</t>
         </is>
       </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
         <is>
           <t>심화 이유: 압력·부피·온도 관계를 입자 움직임으로 시뮬레이션 / 화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
         </is>
@@ -1970,29 +2033,30 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>[정보] 정렬 알고리즘 실험실 (수학) (실과)</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr"/>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr">
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>이은덕</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>심화 이유: 정렬 과정을 단계별로 멈추고 보여 주는 상태 관리</t>
         </is>
@@ -2012,29 +2076,30 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>[정보] 설치 없이 쓰는 파이썬 연습장 (수학) (과학)</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>이은덕</t>
         </is>
       </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>심화 이유: 브라우저 안에서 파이썬을 실행하는 외부 실행 환경(Pyodide) 연결</t>
         </is>
@@ -2054,29 +2119,30 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (한국사) (통합교과)</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr"/>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>진정숙</t>
         </is>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J45" s="7" t="inlineStr">
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
         </is>
@@ -2096,27 +2162,28 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩이란?</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 개념 (패러다임의 변화)
 개발 과정 (요구분석-설계-구현-테스트-배포-운영)
 필수 용어 (예: 라이브러리, 빌드, 디버깅, 배포 등)</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr"/>
       <c r="H46" s="6" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -2132,26 +2199,27 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>프롬프트 기초</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>프롬프트가 결과를 좌우한다 (bad vs good)
 마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr"/>
       <c r="H47" s="6" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J47" s="7" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -2167,29 +2235,30 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr"/>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
         <is>
           <t>수업 22</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="I48" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J48" s="7" t="inlineStr">
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
         </is>
@@ -2209,25 +2278,26 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr"/>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>사례</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr"/>
       <c r="H49" s="6" t="inlineStr"/>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -2243,29 +2313,30 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr"/>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>진급 반 인계 카드</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr"/>
-      <c r="G50" s="6" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
         <is>
           <t>2월</t>
         </is>
@@ -2285,29 +2356,30 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr"/>
-      <c r="E51" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>조건을 반영한 자리 배치</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr"/>
-      <c r="G51" s="6" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
@@ -2327,25 +2399,26 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr"/>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr"/>
+      <c r="E52" s="8" t="inlineStr"/>
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>모둠 자동 편성기</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr"/>
-      <c r="G52" s="8" t="inlineStr"/>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr"/>
+      <c r="H52" s="8" t="inlineStr"/>
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J52" s="9" t="inlineStr">
+      <c r="K52" s="9" t="inlineStr">
         <is>
           <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
         </is>
@@ -2365,25 +2438,26 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr"/>
-      <c r="E53" s="9" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr"/>
+      <c r="E53" s="8" t="inlineStr"/>
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>학급 규칙 함께 정하기 투표판</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr"/>
-      <c r="G53" s="8" t="inlineStr"/>
-      <c r="H53" s="8" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="J53" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr">
+      <c r="K53" s="9" t="inlineStr">
         <is>
           <t>가안 · 3월 학급 세우기 활동</t>
         </is>
@@ -2403,25 +2477,26 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D54" s="8" t="inlineStr"/>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr"/>
+      <c r="E54" s="8" t="inlineStr"/>
+      <c r="F54" s="9" t="inlineStr">
         <is>
           <t>1인 1역 역할 배정표</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr"/>
-      <c r="G54" s="8" t="inlineStr"/>
-      <c r="H54" s="8" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr">
+      <c r="K54" s="9" t="inlineStr">
         <is>
           <t>가안 · 역할 목록과 명단으로 배정·조회</t>
         </is>
@@ -2441,25 +2516,26 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr"/>
-      <c r="E55" s="9" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr"/>
+      <c r="E55" s="8" t="inlineStr"/>
+      <c r="F55" s="9" t="inlineStr">
         <is>
           <t>전자칠판용 우리 반 일과 안내판</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr"/>
-      <c r="G55" s="8" t="inlineStr"/>
-      <c r="H55" s="8" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J55" s="9" t="inlineStr">
+      <c r="K55" s="9" t="inlineStr">
         <is>
           <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
         </is>
@@ -2479,29 +2555,30 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr"/>
-      <c r="E56" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>특별활동 자동 출석부</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr"/>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>진정숙</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
         </is>
@@ -2521,29 +2598,30 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr"/>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>청소 구역 점검판</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr"/>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr"/>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -2559,25 +2637,26 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr"/>
-      <c r="E58" s="9" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr"/>
+      <c r="E58" s="8" t="inlineStr"/>
+      <c r="F58" s="9" t="inlineStr">
         <is>
           <t>과제 제출 체크리스트</t>
         </is>
       </c>
-      <c r="F58" s="9" t="inlineStr"/>
-      <c r="G58" s="8" t="inlineStr"/>
-      <c r="H58" s="8" t="inlineStr">
+      <c r="G58" s="9" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="J58" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J58" s="9" t="inlineStr">
+      <c r="K58" s="9" t="inlineStr">
         <is>
           <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
         </is>
@@ -2597,25 +2676,26 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr"/>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr"/>
+      <c r="E59" s="8" t="inlineStr"/>
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>칭찬 포인트 보드</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr"/>
-      <c r="G59" s="8" t="inlineStr"/>
-      <c r="H59" s="8" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="J59" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
         </is>
@@ -2635,25 +2715,26 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr"/>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr"/>
+      <c r="E60" s="8" t="inlineStr"/>
+      <c r="F60" s="9" t="inlineStr">
         <is>
           <t>학급 행사 D-day 게시판</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr"/>
-      <c r="G60" s="8" t="inlineStr"/>
-      <c r="H60" s="8" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="J60" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J60" s="9" t="inlineStr">
+      <c r="K60" s="9" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
@@ -2673,25 +2754,26 @@
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D61" s="8" t="inlineStr"/>
-      <c r="E61" s="9" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr"/>
+      <c r="E61" s="8" t="inlineStr"/>
+      <c r="F61" s="9" t="inlineStr">
         <is>
           <t>학급 문고 대출 기록표</t>
         </is>
       </c>
-      <c r="F61" s="9" t="inlineStr"/>
-      <c r="G61" s="8" t="inlineStr"/>
-      <c r="H61" s="8" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr"/>
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="J61" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J61" s="9" t="inlineStr">
+      <c r="K61" s="9" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
@@ -2711,29 +2793,30 @@
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr"/>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr"/>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>겹치지 않는 학부모 상담 예약</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr"/>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -2749,29 +2832,30 @@
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr"/>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr"/>
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>정원이 차면 자동 마감되는 신청서</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr"/>
-      <c r="G63" s="6" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="I63" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="inlineStr">
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
         <is>
           <t>방과후학교·학부모 연수</t>
         </is>
@@ -2791,25 +2875,26 @@
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr"/>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr"/>
+      <c r="E64" s="8" t="inlineStr"/>
+      <c r="F64" s="9" t="inlineStr">
         <is>
           <t>안내용 웹 가정통신문 만들기</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr"/>
-      <c r="G64" s="8" t="inlineStr"/>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="G64" s="9" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="J64" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J64" s="9" t="inlineStr">
+      <c r="K64" s="9" t="inlineStr">
         <is>
           <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
         </is>
@@ -2829,25 +2914,26 @@
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr"/>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="8" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr">
         <is>
           <t>참여 여부를 받는 가정통신문과 미응답 확인</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr"/>
-      <c r="G65" s="8" t="inlineStr"/>
-      <c r="H65" s="8" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="J65" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr">
+      <c r="K65" s="9" t="inlineStr">
         <is>
           <t>가안 · 구글 시트로 응답 수합</t>
         </is>
@@ -2867,25 +2953,26 @@
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr"/>
-      <c r="E66" s="9" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr"/>
+      <c r="E66" s="8" t="inlineStr"/>
+      <c r="F66" s="9" t="inlineStr">
         <is>
           <t>공개수업 참관 신청서</t>
         </is>
       </c>
-      <c r="F66" s="9" t="inlineStr"/>
-      <c r="G66" s="8" t="inlineStr"/>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="G66" s="9" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="J66" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J66" s="9" t="inlineStr">
+      <c r="K66" s="9" t="inlineStr">
         <is>
           <t>가안 · 시간대별 정원 표시</t>
         </is>
@@ -2905,25 +2992,26 @@
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr"/>
-      <c r="E67" s="9" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr"/>
+      <c r="F67" s="9" t="inlineStr">
         <is>
           <t>상담 전 사전 질문지</t>
         </is>
       </c>
-      <c r="F67" s="9" t="inlineStr"/>
-      <c r="G67" s="8" t="inlineStr"/>
-      <c r="H67" s="8" t="inlineStr">
+      <c r="G67" s="9" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
+      <c r="J67" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J67" s="9" t="inlineStr">
+      <c r="K67" s="9" t="inlineStr">
         <is>
           <t>가안 · 상담 예약(4-1)과 이어지는 실습</t>
         </is>
@@ -2943,29 +3031,30 @@
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr"/>
-      <c r="E68" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>회신서 미제출자 확인기</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr"/>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr"/>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -2981,29 +3070,30 @@
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr"/>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr"/>
+      <c r="E69" s="6" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>QR로 받는 교직원 연수 서명부</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr"/>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>이승엽</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J69" s="7" t="inlineStr"/>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -3019,29 +3109,30 @@
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr"/>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr"/>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>부서 통합 외부인 방문대장</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr"/>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H70" s="6" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>이승엽</t>
         </is>
       </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J70" s="7" t="inlineStr"/>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -3057,29 +3148,30 @@
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr"/>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr"/>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>공문서 표기 점검기</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr"/>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr"/>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -3095,25 +3187,26 @@
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr"/>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr"/>
+      <c r="E72" s="8" t="inlineStr"/>
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t>행사 물품 수요 조사 집계기</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="8" t="inlineStr"/>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="G72" s="9" t="inlineStr"/>
+      <c r="H72" s="8" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="J72" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J72" s="9" t="inlineStr">
+      <c r="K72" s="9" t="inlineStr">
         <is>
           <t>가안 · 반별 수량을 모아 합계표로</t>
         </is>
@@ -3133,25 +3226,26 @@
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr"/>
-      <c r="E73" s="9" t="inlineStr">
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="8" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>특별실·기자재 예약판</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr"/>
-      <c r="G73" s="8" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr">
+      <c r="G73" s="9" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="J73" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J73" s="9" t="inlineStr">
+      <c r="K73" s="9" t="inlineStr">
         <is>
           <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
         </is>
@@ -3171,29 +3265,30 @@
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr"/>
-      <c r="E74" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr"/>
+      <c r="E74" s="6" t="inlineStr"/>
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>단원 끝 학생 자기평가 카드</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr"/>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J74" s="7" t="inlineStr">
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
         <is>
           <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
         </is>
@@ -3213,29 +3308,30 @@
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr"/>
-      <c r="E75" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr"/>
+      <c r="E75" s="6" t="inlineStr"/>
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>방학 중 안부 체크인</t>
         </is>
       </c>
-      <c r="F75" s="7" t="inlineStr"/>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr">
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
@@ -3255,25 +3351,26 @@
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr"/>
-      <c r="E76" s="9" t="inlineStr">
+      <c r="D76" s="9" t="inlineStr"/>
+      <c r="E76" s="8" t="inlineStr"/>
+      <c r="F76" s="9" t="inlineStr">
         <is>
           <t>관찰 기록으로 단원 평어 초안 만들기</t>
         </is>
       </c>
-      <c r="F76" s="9" t="inlineStr"/>
-      <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="G76" s="9" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="J76" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J76" s="9" t="inlineStr">
+      <c r="K76" s="9" t="inlineStr">
         <is>
           <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
         </is>
@@ -3293,25 +3390,26 @@
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr"/>
-      <c r="E77" s="9" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr"/>
+      <c r="F77" s="9" t="inlineStr">
         <is>
           <t>수행평가 채점 기준표(루브릭) 채점기</t>
         </is>
       </c>
-      <c r="F77" s="9" t="inlineStr"/>
-      <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I77" s="8" t="inlineStr">
+      <c r="J77" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J77" s="9" t="inlineStr">
+      <c r="K77" s="9" t="inlineStr">
         <is>
           <t>가안 · 평가·기록 보강</t>
         </is>
@@ -3331,25 +3429,26 @@
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr"/>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr"/>
+      <c r="E78" s="8" t="inlineStr"/>
+      <c r="F78" s="9" t="inlineStr">
         <is>
           <t>문항별 정답률 분석표</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr"/>
-      <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr"/>
+      <c r="H78" s="8" t="inlineStr"/>
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="J78" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J78" s="9" t="inlineStr">
+      <c r="K78" s="9" t="inlineStr">
         <is>
           <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
         </is>
@@ -3369,25 +3468,26 @@
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr"/>
-      <c r="E79" s="9" t="inlineStr">
+      <c r="D79" s="9" t="inlineStr"/>
+      <c r="E79" s="8" t="inlineStr"/>
+      <c r="F79" s="9" t="inlineStr">
         <is>
           <t>생활기록부 글자 수·표현 점검기</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr"/>
-      <c r="G79" s="8" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="J79" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="J79" s="9" t="inlineStr">
+      <c r="K79" s="9" t="inlineStr">
         <is>
           <t>가안 · 평가·기록 보강 · 바이트 수와 쓰지 않는 표현을 표시, 내용은 외부로 보내지 않음</t>
         </is>
@@ -3401,29 +3501,30 @@
       </c>
       <c r="B80" s="10" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr"/>
-      <c r="D80" s="10" t="inlineStr"/>
-      <c r="E80" s="11" t="inlineStr">
+      <c r="D80" s="11" t="inlineStr"/>
+      <c r="E80" s="10" t="inlineStr"/>
+      <c r="F80" s="11" t="inlineStr">
         <is>
           <t>발표 모드</t>
         </is>
       </c>
-      <c r="F80" s="11" t="inlineStr"/>
-      <c r="G80" s="10" t="inlineStr">
+      <c r="G80" s="11" t="inlineStr"/>
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H80" s="10" t="inlineStr">
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>강현수</t>
         </is>
       </c>
-      <c r="I80" s="10" t="inlineStr">
+      <c r="J80" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J80" s="11" t="inlineStr">
+      <c r="K80" s="11" t="inlineStr">
         <is>
           <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
         </is>
@@ -3437,29 +3538,30 @@
       </c>
       <c r="B81" s="10" t="inlineStr"/>
       <c r="C81" s="11" t="inlineStr"/>
-      <c r="D81" s="10" t="inlineStr"/>
-      <c r="E81" s="11" t="inlineStr">
+      <c r="D81" s="11" t="inlineStr"/>
+      <c r="E81" s="10" t="inlineStr"/>
+      <c r="F81" s="11" t="inlineStr">
         <is>
           <t>기기대여대장</t>
         </is>
       </c>
-      <c r="F81" s="11" t="inlineStr"/>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="G81" s="11" t="inlineStr"/>
+      <c r="H81" s="10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H81" s="10" t="inlineStr">
+      <c r="I81" s="10" t="inlineStr">
         <is>
           <t>진정숙</t>
         </is>
       </c>
-      <c r="I81" s="10" t="inlineStr">
+      <c r="J81" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J81" s="11" t="inlineStr">
+      <c r="K81" s="11" t="inlineStr">
         <is>
           <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
         </is>
@@ -3473,29 +3575,30 @@
       </c>
       <c r="B82" s="10" t="inlineStr"/>
       <c r="C82" s="11" t="inlineStr"/>
-      <c r="D82" s="10" t="inlineStr"/>
-      <c r="E82" s="11" t="inlineStr">
+      <c r="D82" s="11" t="inlineStr"/>
+      <c r="E82" s="10" t="inlineStr"/>
+      <c r="F82" s="11" t="inlineStr">
         <is>
           <t>스마트 시간표 교체</t>
         </is>
       </c>
-      <c r="F82" s="11" t="inlineStr"/>
-      <c r="G82" s="10" t="inlineStr">
+      <c r="G82" s="11" t="inlineStr"/>
+      <c r="H82" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H82" s="10" t="inlineStr">
+      <c r="I82" s="10" t="inlineStr">
         <is>
           <t>진정숙</t>
         </is>
       </c>
-      <c r="I82" s="10" t="inlineStr">
+      <c r="J82" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J82" s="11" t="inlineStr">
+      <c r="K82" s="11" t="inlineStr">
         <is>
           <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
         </is>
@@ -3509,29 +3612,30 @@
       </c>
       <c r="B83" s="10" t="inlineStr"/>
       <c r="C83" s="11" t="inlineStr"/>
-      <c r="D83" s="10" t="inlineStr"/>
-      <c r="E83" s="11" t="inlineStr">
+      <c r="D83" s="11" t="inlineStr"/>
+      <c r="E83" s="10" t="inlineStr"/>
+      <c r="F83" s="11" t="inlineStr">
         <is>
           <t>준비물, 전달사항 알림장 사이트</t>
         </is>
       </c>
-      <c r="F83" s="11" t="inlineStr"/>
-      <c r="G83" s="10" t="inlineStr">
+      <c r="G83" s="11" t="inlineStr"/>
+      <c r="H83" s="10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H83" s="10" t="inlineStr">
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>이지상</t>
         </is>
       </c>
-      <c r="I83" s="10" t="inlineStr">
+      <c r="J83" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J83" s="11" t="inlineStr">
+      <c r="K83" s="11" t="inlineStr">
         <is>
           <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
         </is>
@@ -3545,29 +3649,30 @@
       </c>
       <c r="B84" s="10" t="inlineStr"/>
       <c r="C84" s="11" t="inlineStr"/>
-      <c r="D84" s="10" t="inlineStr"/>
-      <c r="E84" s="11" t="inlineStr">
+      <c r="D84" s="11" t="inlineStr"/>
+      <c r="E84" s="10" t="inlineStr"/>
+      <c r="F84" s="11" t="inlineStr">
         <is>
           <t>키워드 레이더</t>
         </is>
       </c>
-      <c r="F84" s="11" t="inlineStr"/>
-      <c r="G84" s="10" t="inlineStr">
+      <c r="G84" s="11" t="inlineStr"/>
+      <c r="H84" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H84" s="10" t="inlineStr">
+      <c r="I84" s="10" t="inlineStr">
         <is>
           <t>이승엽</t>
         </is>
       </c>
-      <c r="I84" s="10" t="inlineStr">
+      <c r="J84" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J84" s="11" t="inlineStr">
+      <c r="K84" s="11" t="inlineStr">
         <is>
           <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
         </is>
@@ -3581,29 +3686,30 @@
       </c>
       <c r="B85" s="10" t="inlineStr"/>
       <c r="C85" s="11" t="inlineStr"/>
-      <c r="D85" s="10" t="inlineStr"/>
-      <c r="E85" s="11" t="inlineStr">
+      <c r="D85" s="11" t="inlineStr"/>
+      <c r="E85" s="10" t="inlineStr"/>
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>부장회의록 및 주간계획</t>
         </is>
       </c>
-      <c r="F85" s="11" t="inlineStr"/>
-      <c r="G85" s="10" t="inlineStr">
+      <c r="G85" s="11" t="inlineStr"/>
+      <c r="H85" s="10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H85" s="10" t="inlineStr">
+      <c r="I85" s="10" t="inlineStr">
         <is>
           <t>이승엽</t>
         </is>
       </c>
-      <c r="I85" s="10" t="inlineStr">
+      <c r="J85" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J85" s="11" t="inlineStr">
+      <c r="K85" s="11" t="inlineStr">
         <is>
           <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
         </is>
@@ -3617,29 +3723,30 @@
       </c>
       <c r="B86" s="10" t="inlineStr"/>
       <c r="C86" s="11" t="inlineStr"/>
-      <c r="D86" s="10" t="inlineStr"/>
-      <c r="E86" s="11" t="inlineStr">
+      <c r="D86" s="11" t="inlineStr"/>
+      <c r="E86" s="10" t="inlineStr"/>
+      <c r="F86" s="11" t="inlineStr">
         <is>
           <t>우리반 출석부</t>
         </is>
       </c>
-      <c r="F86" s="11" t="inlineStr"/>
-      <c r="G86" s="10" t="inlineStr">
+      <c r="G86" s="11" t="inlineStr"/>
+      <c r="H86" s="10" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H86" s="10" t="inlineStr">
+      <c r="I86" s="10" t="inlineStr">
         <is>
           <t>진정숙</t>
         </is>
       </c>
-      <c r="I86" s="10" t="inlineStr">
+      <c r="J86" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J86" s="11" t="inlineStr">
+      <c r="K86" s="11" t="inlineStr">
         <is>
           <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
         </is>
@@ -3653,29 +3760,30 @@
       </c>
       <c r="B87" s="10" t="inlineStr"/>
       <c r="C87" s="11" t="inlineStr"/>
-      <c r="D87" s="10" t="inlineStr"/>
-      <c r="E87" s="11" t="inlineStr">
+      <c r="D87" s="11" t="inlineStr"/>
+      <c r="E87" s="10" t="inlineStr"/>
+      <c r="F87" s="11" t="inlineStr">
         <is>
           <t>학부모 상담 기록요약</t>
         </is>
       </c>
-      <c r="F87" s="11" t="inlineStr"/>
-      <c r="G87" s="10" t="inlineStr">
+      <c r="G87" s="11" t="inlineStr"/>
+      <c r="H87" s="10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H87" s="10" t="inlineStr">
+      <c r="I87" s="10" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
+      <c r="J87" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J87" s="11" t="inlineStr">
+      <c r="K87" s="11" t="inlineStr">
         <is>
           <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
         </is>
@@ -3689,29 +3797,30 @@
       </c>
       <c r="B88" s="10" t="inlineStr"/>
       <c r="C88" s="11" t="inlineStr"/>
-      <c r="D88" s="10" t="inlineStr"/>
-      <c r="E88" s="11" t="inlineStr">
+      <c r="D88" s="11" t="inlineStr"/>
+      <c r="E88" s="10" t="inlineStr"/>
+      <c r="F88" s="11" t="inlineStr">
         <is>
           <t>반 편성 조건 점검기</t>
         </is>
       </c>
-      <c r="F88" s="11" t="inlineStr"/>
-      <c r="G88" s="10" t="inlineStr">
+      <c r="G88" s="11" t="inlineStr"/>
+      <c r="H88" s="10" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H88" s="10" t="inlineStr">
+      <c r="I88" s="10" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="I88" s="10" t="inlineStr">
+      <c r="J88" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="J88" s="11" t="inlineStr">
+      <c r="K88" s="11" t="inlineStr">
         <is>
           <t>특수 배려·분리 요청 같은 민감 정보를 다루고 LLM API가 필요함. 제안자도 다음 회의에서 논의하기로 남겨 둠</t>
         </is>
@@ -3721,256 +3830,277 @@
       <c r="A89" s="6" t="n"/>
       <c r="B89" s="6" t="n"/>
       <c r="C89" s="7" t="n"/>
-      <c r="D89" s="6" t="n"/>
-      <c r="E89" s="7" t="n"/>
+      <c r="D89" s="7" t="n"/>
+      <c r="E89" s="6" t="n"/>
       <c r="F89" s="7" t="n"/>
-      <c r="G89" s="6" t="n"/>
+      <c r="G89" s="7" t="n"/>
       <c r="H89" s="6" t="n"/>
       <c r="I89" s="6" t="n"/>
-      <c r="J89" s="7" t="n"/>
+      <c r="J89" s="6" t="n"/>
+      <c r="K89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n"/>
       <c r="B90" s="6" t="n"/>
       <c r="C90" s="7" t="n"/>
-      <c r="D90" s="6" t="n"/>
-      <c r="E90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
+      <c r="E90" s="6" t="n"/>
       <c r="F90" s="7" t="n"/>
-      <c r="G90" s="6" t="n"/>
+      <c r="G90" s="7" t="n"/>
       <c r="H90" s="6" t="n"/>
       <c r="I90" s="6" t="n"/>
-      <c r="J90" s="7" t="n"/>
+      <c r="J90" s="6" t="n"/>
+      <c r="K90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
       <c r="B91" s="6" t="n"/>
       <c r="C91" s="7" t="n"/>
-      <c r="D91" s="6" t="n"/>
-      <c r="E91" s="7" t="n"/>
+      <c r="D91" s="7" t="n"/>
+      <c r="E91" s="6" t="n"/>
       <c r="F91" s="7" t="n"/>
-      <c r="G91" s="6" t="n"/>
+      <c r="G91" s="7" t="n"/>
       <c r="H91" s="6" t="n"/>
       <c r="I91" s="6" t="n"/>
-      <c r="J91" s="7" t="n"/>
+      <c r="J91" s="6" t="n"/>
+      <c r="K91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n"/>
       <c r="B92" s="6" t="n"/>
       <c r="C92" s="7" t="n"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="7" t="n"/>
+      <c r="D92" s="7" t="n"/>
+      <c r="E92" s="6" t="n"/>
       <c r="F92" s="7" t="n"/>
-      <c r="G92" s="6" t="n"/>
+      <c r="G92" s="7" t="n"/>
       <c r="H92" s="6" t="n"/>
       <c r="I92" s="6" t="n"/>
-      <c r="J92" s="7" t="n"/>
+      <c r="J92" s="6" t="n"/>
+      <c r="K92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
       <c r="B93" s="6" t="n"/>
       <c r="C93" s="7" t="n"/>
-      <c r="D93" s="6" t="n"/>
-      <c r="E93" s="7" t="n"/>
+      <c r="D93" s="7" t="n"/>
+      <c r="E93" s="6" t="n"/>
       <c r="F93" s="7" t="n"/>
-      <c r="G93" s="6" t="n"/>
+      <c r="G93" s="7" t="n"/>
       <c r="H93" s="6" t="n"/>
       <c r="I93" s="6" t="n"/>
-      <c r="J93" s="7" t="n"/>
+      <c r="J93" s="6" t="n"/>
+      <c r="K93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
       <c r="B94" s="6" t="n"/>
       <c r="C94" s="7" t="n"/>
-      <c r="D94" s="6" t="n"/>
-      <c r="E94" s="7" t="n"/>
+      <c r="D94" s="7" t="n"/>
+      <c r="E94" s="6" t="n"/>
       <c r="F94" s="7" t="n"/>
-      <c r="G94" s="6" t="n"/>
+      <c r="G94" s="7" t="n"/>
       <c r="H94" s="6" t="n"/>
       <c r="I94" s="6" t="n"/>
-      <c r="J94" s="7" t="n"/>
+      <c r="J94" s="6" t="n"/>
+      <c r="K94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
       <c r="B95" s="6" t="n"/>
       <c r="C95" s="7" t="n"/>
-      <c r="D95" s="6" t="n"/>
-      <c r="E95" s="7" t="n"/>
+      <c r="D95" s="7" t="n"/>
+      <c r="E95" s="6" t="n"/>
       <c r="F95" s="7" t="n"/>
-      <c r="G95" s="6" t="n"/>
+      <c r="G95" s="7" t="n"/>
       <c r="H95" s="6" t="n"/>
       <c r="I95" s="6" t="n"/>
-      <c r="J95" s="7" t="n"/>
+      <c r="J95" s="6" t="n"/>
+      <c r="K95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n"/>
       <c r="B96" s="6" t="n"/>
       <c r="C96" s="7" t="n"/>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="7" t="n"/>
+      <c r="D96" s="7" t="n"/>
+      <c r="E96" s="6" t="n"/>
       <c r="F96" s="7" t="n"/>
-      <c r="G96" s="6" t="n"/>
+      <c r="G96" s="7" t="n"/>
       <c r="H96" s="6" t="n"/>
       <c r="I96" s="6" t="n"/>
-      <c r="J96" s="7" t="n"/>
+      <c r="J96" s="6" t="n"/>
+      <c r="K96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
       <c r="B97" s="6" t="n"/>
       <c r="C97" s="7" t="n"/>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="7" t="n"/>
+      <c r="D97" s="7" t="n"/>
+      <c r="E97" s="6" t="n"/>
       <c r="F97" s="7" t="n"/>
-      <c r="G97" s="6" t="n"/>
+      <c r="G97" s="7" t="n"/>
       <c r="H97" s="6" t="n"/>
       <c r="I97" s="6" t="n"/>
-      <c r="J97" s="7" t="n"/>
+      <c r="J97" s="6" t="n"/>
+      <c r="K97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n"/>
       <c r="B98" s="6" t="n"/>
       <c r="C98" s="7" t="n"/>
-      <c r="D98" s="6" t="n"/>
-      <c r="E98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="6" t="n"/>
       <c r="F98" s="7" t="n"/>
-      <c r="G98" s="6" t="n"/>
+      <c r="G98" s="7" t="n"/>
       <c r="H98" s="6" t="n"/>
       <c r="I98" s="6" t="n"/>
-      <c r="J98" s="7" t="n"/>
+      <c r="J98" s="6" t="n"/>
+      <c r="K98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
       <c r="B99" s="6" t="n"/>
       <c r="C99" s="7" t="n"/>
-      <c r="D99" s="6" t="n"/>
-      <c r="E99" s="7" t="n"/>
+      <c r="D99" s="7" t="n"/>
+      <c r="E99" s="6" t="n"/>
       <c r="F99" s="7" t="n"/>
-      <c r="G99" s="6" t="n"/>
+      <c r="G99" s="7" t="n"/>
       <c r="H99" s="6" t="n"/>
       <c r="I99" s="6" t="n"/>
-      <c r="J99" s="7" t="n"/>
+      <c r="J99" s="6" t="n"/>
+      <c r="K99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n"/>
       <c r="B100" s="6" t="n"/>
       <c r="C100" s="7" t="n"/>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="7" t="n"/>
+      <c r="D100" s="7" t="n"/>
+      <c r="E100" s="6" t="n"/>
       <c r="F100" s="7" t="n"/>
-      <c r="G100" s="6" t="n"/>
+      <c r="G100" s="7" t="n"/>
       <c r="H100" s="6" t="n"/>
       <c r="I100" s="6" t="n"/>
-      <c r="J100" s="7" t="n"/>
+      <c r="J100" s="6" t="n"/>
+      <c r="K100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
       <c r="B101" s="6" t="n"/>
       <c r="C101" s="7" t="n"/>
-      <c r="D101" s="6" t="n"/>
-      <c r="E101" s="7" t="n"/>
+      <c r="D101" s="7" t="n"/>
+      <c r="E101" s="6" t="n"/>
       <c r="F101" s="7" t="n"/>
-      <c r="G101" s="6" t="n"/>
+      <c r="G101" s="7" t="n"/>
       <c r="H101" s="6" t="n"/>
       <c r="I101" s="6" t="n"/>
-      <c r="J101" s="7" t="n"/>
+      <c r="J101" s="6" t="n"/>
+      <c r="K101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n"/>
       <c r="B102" s="6" t="n"/>
       <c r="C102" s="7" t="n"/>
-      <c r="D102" s="6" t="n"/>
-      <c r="E102" s="7" t="n"/>
+      <c r="D102" s="7" t="n"/>
+      <c r="E102" s="6" t="n"/>
       <c r="F102" s="7" t="n"/>
-      <c r="G102" s="6" t="n"/>
+      <c r="G102" s="7" t="n"/>
       <c r="H102" s="6" t="n"/>
       <c r="I102" s="6" t="n"/>
-      <c r="J102" s="7" t="n"/>
+      <c r="J102" s="6" t="n"/>
+      <c r="K102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n"/>
       <c r="B103" s="6" t="n"/>
       <c r="C103" s="7" t="n"/>
-      <c r="D103" s="6" t="n"/>
-      <c r="E103" s="7" t="n"/>
+      <c r="D103" s="7" t="n"/>
+      <c r="E103" s="6" t="n"/>
       <c r="F103" s="7" t="n"/>
-      <c r="G103" s="6" t="n"/>
+      <c r="G103" s="7" t="n"/>
       <c r="H103" s="6" t="n"/>
       <c r="I103" s="6" t="n"/>
-      <c r="J103" s="7" t="n"/>
+      <c r="J103" s="6" t="n"/>
+      <c r="K103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n"/>
       <c r="B104" s="6" t="n"/>
       <c r="C104" s="7" t="n"/>
-      <c r="D104" s="6" t="n"/>
-      <c r="E104" s="7" t="n"/>
+      <c r="D104" s="7" t="n"/>
+      <c r="E104" s="6" t="n"/>
       <c r="F104" s="7" t="n"/>
-      <c r="G104" s="6" t="n"/>
+      <c r="G104" s="7" t="n"/>
       <c r="H104" s="6" t="n"/>
       <c r="I104" s="6" t="n"/>
-      <c r="J104" s="7" t="n"/>
+      <c r="J104" s="6" t="n"/>
+      <c r="K104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n"/>
       <c r="B105" s="6" t="n"/>
       <c r="C105" s="7" t="n"/>
-      <c r="D105" s="6" t="n"/>
-      <c r="E105" s="7" t="n"/>
+      <c r="D105" s="7" t="n"/>
+      <c r="E105" s="6" t="n"/>
       <c r="F105" s="7" t="n"/>
-      <c r="G105" s="6" t="n"/>
+      <c r="G105" s="7" t="n"/>
       <c r="H105" s="6" t="n"/>
       <c r="I105" s="6" t="n"/>
-      <c r="J105" s="7" t="n"/>
+      <c r="J105" s="6" t="n"/>
+      <c r="K105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n"/>
       <c r="B106" s="6" t="n"/>
       <c r="C106" s="7" t="n"/>
-      <c r="D106" s="6" t="n"/>
-      <c r="E106" s="7" t="n"/>
+      <c r="D106" s="7" t="n"/>
+      <c r="E106" s="6" t="n"/>
       <c r="F106" s="7" t="n"/>
-      <c r="G106" s="6" t="n"/>
+      <c r="G106" s="7" t="n"/>
       <c r="H106" s="6" t="n"/>
       <c r="I106" s="6" t="n"/>
-      <c r="J106" s="7" t="n"/>
+      <c r="J106" s="6" t="n"/>
+      <c r="K106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n"/>
       <c r="B107" s="6" t="n"/>
       <c r="C107" s="7" t="n"/>
-      <c r="D107" s="6" t="n"/>
-      <c r="E107" s="7" t="n"/>
+      <c r="D107" s="7" t="n"/>
+      <c r="E107" s="6" t="n"/>
       <c r="F107" s="7" t="n"/>
-      <c r="G107" s="6" t="n"/>
+      <c r="G107" s="7" t="n"/>
       <c r="H107" s="6" t="n"/>
       <c r="I107" s="6" t="n"/>
-      <c r="J107" s="7" t="n"/>
+      <c r="J107" s="6" t="n"/>
+      <c r="K107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n"/>
       <c r="B108" s="6" t="n"/>
       <c r="C108" s="7" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="7" t="n"/>
+      <c r="D108" s="7" t="n"/>
+      <c r="E108" s="6" t="n"/>
       <c r="F108" s="7" t="n"/>
-      <c r="G108" s="6" t="n"/>
+      <c r="G108" s="7" t="n"/>
       <c r="H108" s="6" t="n"/>
       <c r="I108" s="6" t="n"/>
-      <c r="J108" s="7" t="n"/>
+      <c r="J108" s="6" t="n"/>
+      <c r="K108" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B4:J4"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B2:J2"/>
+  <mergeCells count="7">
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B5:K5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A11:A108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
-    <dataValidation sqref="I11:I108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J11:J108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -726,7 +726,11 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩 이론</t>
+        </is>
+      </c>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -2162,7 +2166,11 @@
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩 이론</t>
+        </is>
+      </c>
       <c r="E46" s="6" t="inlineStr"/>
       <c r="F46" s="7" t="inlineStr">
         <is>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -520,6 +520,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="44" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -580,257 +581,197 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>세부 내용</t>
+          <t>대체 가능</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>꼭지 아래에 보일 항목. 한 칸 안에서 줄을 바꿔(Alt+Enter) 하나씩 적기</t>
+          <t>재검토 행에만: 수준을 맞추면 어떤 가안 꼭지를 대신할 수 있는지</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>바탕 아이디어 번호</t>
+          <t>세부 내용</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>같은 권의 아이디어 번호를 쉼표로 (예: 21, 22). 다른 권 아이디어는 '수업 14', '업무 7'처럼</t>
+          <t>꼭지 아래에 보일 항목. 한 칸 안에서 줄을 바꿔(Alt+Enter) 하나씩 적기</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>바탕 아이디어 번호</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>같은 권의 아이디어 번호를 쉼표로 (예: 21, 22). 다른 권 아이디어는 '수업 14', '업무 7'처럼</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>확정 / 검토 중 / 초안 / 가안 / 보류 / 재검토 — ‘재검토’ 행은 목차에서 빠지고 ‘재검토 아이디어’에 비고(이유)와 함께 표시</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>권</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>파트 번호</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>파트 제목</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>파트 설명</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>꼭지 번호</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>꼭지 제목</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>세부 내용</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>바탕 아이디어 번호</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>저자</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>대체 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>예시</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>프롬프트 기초</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>프롬프트가 결과를 좌우한다
 마크다운 기초</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>검토 중</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 이론</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩이란?</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 개념 (패러다임의 변화)
 개발 과정 (요구분석-설계-구현-테스트-배포-운영)
 필수 용어 (예: 라이브러리, 빌드, 디버깅, 배포 등)</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트가 결과를 좌우한다 (bad vs good)
-마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
       <c r="J13" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -850,12 +791,13 @@
       <c r="E14" s="6" t="inlineStr"/>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+          <t>프롬프트 기초</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>사례</t>
+          <t>프롬프트가 결과를 좌우한다 (bad vs good)
+마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
@@ -866,6 +808,7 @@
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -874,28 +817,24 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>사용 도구: ChatGPT의 Codex 활용</t>
-        </is>
-      </c>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>[공통] 성취기준으로 지도안·학습지 초안 만들기</t>
+          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -910,9 +849,10 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
-        </is>
-      </c>
+          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -921,37 +861,34 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>[공통] 학생용·교사용 학습지 한 번에 찍어내기</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
+          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>사례</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr"/>
       <c r="J16" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -967,22 +904,26 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>사용 도구: ChatGPT의 Codex 활용</t>
+        </is>
+      </c>
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>[공통] 활동 순서와 남은 시간을 띄우는 수업 전광판</t>
+          <t>[공통] 성취기준으로 지도안·학습지 초안 만들기</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr"/>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -990,7 +931,12 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr"/>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1010,18 +956,18 @@
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>[공통] 모둠 활동 소음 신호등</t>
+          <t>[공통] 학생용·교사용 학습지 한 번에 찍어내기</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
@@ -1029,11 +975,8 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>전광판(2-1)과 한 꼭지로 합칠지 검토</t>
-        </is>
-      </c>
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1053,18 +996,18 @@
       <c r="E19" s="6" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>[공통] 질문·발표자를 뽑는 캡슐 뽑기 기계</t>
+          <t>[공통] 활동 순서와 남은 시간을 띄우는 수업 전광판</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
@@ -1073,6 +1016,7 @@
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1092,18 +1036,18 @@
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>[공통] 답 대신 질문하는 수업 챗봇 만들기</t>
+          <t>[공통] 모둠 활동 소음 신호등</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>임부현</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
@@ -1113,9 +1057,10 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
-        </is>
-      </c>
+          <t>전광판(2-1)과 한 꼭지로 합칠지 검토</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1135,18 +1080,18 @@
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>[공통] 과제에 붙이는 AI 사용 내역 카드</t>
+          <t>[공통] 질문·발표자를 뽑는 캡슐 뽑기 기계</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>임부현</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
@@ -1155,6 +1100,7 @@
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1174,13 +1120,13 @@
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>[공통] 한 권 읽기 독서일지</t>
+          <t>[공통] 답 대신 질문하는 수업 챗봇 만들기</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -1195,9 +1141,10 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>참여 코드·학급별 기록 저장(DB)이 필요한 심화 실습</t>
-        </is>
-      </c>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1217,13 +1164,13 @@
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>[공통] 구글 폼 응답을 전자칠판에 띄우기</t>
+          <t>[공통] 과제에 붙이는 AI 사용 내역 카드</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -1237,6 +1184,7 @@
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1256,13 +1204,13 @@
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>[공통] 활동 사진 반별 제출함</t>
+          <t>[공통] 한 권 읽기 독서일지</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1277,9 +1225,10 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>구글 앱스 스크립트 실습(clasp 자동 업로드는 빼고 진행)</t>
-        </is>
-      </c>
+          <t>참여 코드·학급별 기록 저장(DB)이 필요한 심화 실습</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -1299,18 +1248,18 @@
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>[공통] 단원 용어 플래시 학습 게임</t>
+          <t>[공통] 구글 폼 응답을 전자칠판에 띄우기</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
@@ -1319,6 +1268,7 @@
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1338,18 +1288,18 @@
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>[공통] 개념 빙고판 30장 자동 생성기</t>
+          <t>[공통] 활동 사진 반별 제출함</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
@@ -1357,7 +1307,12 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>구글 앱스 스크립트 실습(clasp 자동 업로드는 빼고 진행)</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1366,33 +1321,29 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>사용 도구: ChatGPT의 Codex 활용</t>
-        </is>
-      </c>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>[국어] 낚시 제목 감별 카드 (사회) (도덕) (정보) (영어)</t>
+          <t>[공통] 단원 용어 플래시 학습 게임</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -1401,6 +1352,7 @@
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1409,29 +1361,29 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문단 번호 읽기판 (영어) (사회) (과학) (한문)</t>
+          <t>[공통] 개념 빙고판 30장 자동 생성기</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>임부현</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
@@ -1440,6 +1392,7 @@
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -1455,17 +1408,21 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>사용 도구: ChatGPT의 Codex 활용</t>
+        </is>
+      </c>
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>[국어] 다섯 칸으로 쓰는 시 설계도 (영어) (음악) (미술)</t>
+          <t>[국어] 낚시 제목 감별 카드 (사회) (도덕) (정보) (영어)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -1479,6 +1436,7 @@
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1498,13 +1456,13 @@
       <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>[국어] 끌어다 놓는 품사 분류 바구니 (영어) (과학) (실과) (기술·가정)</t>
+          <t>[국어] 문단 번호 읽기판 (영어) (사회) (과학) (한문)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr"/>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -1517,11 +1475,8 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>기본편. 같은 주제의 심화편은 PART 4 ‘품사 문제 출제기’</t>
-        </is>
-      </c>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -1541,13 +1496,13 @@
       <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>[국어] 모둠 토의 진행판 (사회) (도덕) (과학) (진로)</t>
+          <t>[국어] 다섯 칸으로 쓰는 시 설계도 (영어) (음악) (미술)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr"/>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -1560,11 +1515,8 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>다른 교과 토의·토론으로 확장 가능</t>
-        </is>
-      </c>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -1584,186 +1536,195 @@
       <c r="E32" s="6" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (제2외국어) (정보)</t>
+          <t>[국어] 끌어다 놓는 품사 분류 바구니 (영어) (과학) (실과) (기술·가정)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr"/>
       <c r="H32" s="6" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>김형훈</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>기본편. 같은 주제의 심화편은 PART 4 ‘품사 문제 출제기’</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>수업자동화</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>[국어] 모둠 토의 진행판 (사회) (도덕) (과학) (진로)</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>김형훈</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>다른 교과 토의·토론으로 확장 가능</t>
+        </is>
+      </c>
+      <c r="L33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>수업자동화</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (제2외국어) (정보)</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
+      <c r="B35" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr"/>
-      <c r="E33" s="8" t="inlineStr"/>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>[영어] 듣고 따라 말하는 영어 문장 카드 (제2외국어) (국어) (한문)</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="8" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>가안 · 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="L35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>수업자동화</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B36" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr"/>
+      <c r="E36" s="8" t="inlineStr"/>
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>[수학] 함수 그래프가 움직이는 계수 탐구판 (물리) (경제) (정보)</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학) (경제)</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>김진혁</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="6" t="inlineStr"/>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>[사회] 선사시대 시간 탐사 게임 (역사) (지구과학) (미술)</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>이은덕</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -1783,18 +1744,18 @@
       <c r="E37" s="6" t="inlineStr"/>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>[체육] 종목별 경기 점수판 (수학) (영어)</t>
+          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학) (경제)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr"/>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>김진혁</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
@@ -1802,7 +1763,12 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
+        </is>
+      </c>
+      <c r="L37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1811,33 +1777,29 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>사용 도구: ChatGPT의 Codex로 만들고, 구글 앱스 스크립트 또는 OpenAI API를 붙여서 실습</t>
-        </is>
-      </c>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr"/>
       <c r="E38" s="6" t="inlineStr"/>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>[국어] 내 말로 만드는 품사 문제 출제기 (영어) (제2외국어) (한문)</t>
+          <t>[사회] 선사시대 시간 탐사 게임 (역사) (지구과학) (미술)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr"/>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
@@ -1845,11 +1807,8 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K38" s="7" t="inlineStr">
-        <is>
-          <t>심화 이유: AI API(OpenAI)로 학생 글에서 문제를 만듦 / 기본편은 PART 3 ‘품사 분류 바구니’</t>
-        </is>
-      </c>
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -1858,29 +1817,29 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr"/>
       <c r="E39" s="6" t="inlineStr"/>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문장 구조 분석기 (영어) (제2외국어)</t>
+          <t>[체육] 종목별 경기 점수판 (수학) (영어)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr"/>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
@@ -1888,11 +1847,8 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
-        <is>
-          <t>심화 이유: AI API(Gemini)로 문장을 분석함</t>
-        </is>
-      </c>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -1908,17 +1864,21 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>사용 도구: ChatGPT의 Codex로 만들고, 구글 앱스 스크립트 또는 OpenAI API를 붙여서 실습</t>
+        </is>
+      </c>
       <c r="E40" s="6" t="inlineStr"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학) (역사) (도덕)</t>
+          <t>[국어] 내 말로 만드는 품사 문제 출제기 (영어) (제2외국어) (한문)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr"/>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -1933,9 +1893,10 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: AI API 연결과 ‘답 대신 되묻기’ 프롬프트 설계가 필요함</t>
-        </is>
-      </c>
+          <t>심화 이유: AI API(OpenAI)로 학생 글에서 문제를 만듦 / 기본편은 PART 3 ‘품사 분류 바구니’</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -1955,18 +1916,18 @@
       <c r="E41" s="6" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>[과학] 화학 결합 실험실 (물리) (지구과학) (수학)</t>
+          <t>[국어] 문장 구조 분석기 (영어) (제2외국어)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>강현수</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
@@ -1976,9 +1937,10 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 전자 이동·공유를 과학적으로 맞게 움직이는 애니메이션 구현</t>
-        </is>
-      </c>
+          <t>심화 이유: AI API(Gemini)로 문장을 분석함</t>
+        </is>
+      </c>
+      <c r="L41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -1998,18 +1960,18 @@
       <c r="E42" s="6" t="inlineStr"/>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>[과학] 기체 법칙 탐구 실험실 (수학) (물리)</t>
+          <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학) (역사) (도덕)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr"/>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>강현수</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
@@ -2019,9 +1981,10 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 압력·부피·온도 관계를 입자 움직임으로 시뮬레이션 / 화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
-        </is>
-      </c>
+          <t>심화 이유: AI API 연결과 ‘답 대신 되묻기’ 프롬프트 설계가 필요함</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -2041,18 +2004,18 @@
       <c r="E43" s="6" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>[정보] 정렬 알고리즘 실험실 (수학) (실과)</t>
+          <t>[과학] 화학 결합 실험실 (물리) (지구과학) (수학)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr"/>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
@@ -2062,9 +2025,10 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 정렬 과정을 단계별로 멈추고 보여 주는 상태 관리</t>
-        </is>
-      </c>
+          <t>심화 이유: 전자 이동·공유를 과학적으로 맞게 움직이는 애니메이션 구현</t>
+        </is>
+      </c>
+      <c r="L43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -2084,18 +2048,18 @@
       <c r="E44" s="6" t="inlineStr"/>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>[정보] 설치 없이 쓰는 파이썬 연습장 (수학) (과학)</t>
+          <t>[과학] 기체 법칙 탐구 실험실 (수학) (물리)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
@@ -2105,9 +2069,10 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 브라우저 안에서 파이썬을 실행하는 외부 실행 환경(Pyodide) 연결</t>
-        </is>
-      </c>
+          <t>심화 이유: 압력·부피·온도 관계를 입자 움직임으로 시뮬레이션 / 화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -2127,18 +2092,18 @@
       <c r="E45" s="6" t="inlineStr"/>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (한국사) (통합교과)</t>
+          <t>[정보] 정렬 알고리즘 실험실 (수학) (실과)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
@@ -2148,129 +2113,140 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
-        </is>
-      </c>
+          <t>심화 이유: 정렬 과정을 단계별로 멈추고 보여 주는 상태 관리</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>업무자동화</t>
+          <t>수업자동화</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩 이론</t>
-        </is>
-      </c>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr"/>
       <c r="E46" s="6" t="inlineStr"/>
       <c r="F46" s="7" t="inlineStr">
         <is>
+          <t>[정보] 설치 없이 쓰는 파이썬 연습장 (수학) (과학)</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>이은덕</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: 브라우저 안에서 파이썬을 실행하는 외부 실행 환경(Pyodide) 연결</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>수업자동화</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (한국사) (통합교과)</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K47" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
+        </is>
+      </c>
+      <c r="L47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩 이론</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
           <t>바이브 코딩이란?</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 개념 (패러다임의 변화)
 개발 과정 (요구분석-설계-구현-테스트-배포-운영)
 필수 용어 (예: 라이브러리, 빌드, 디버깅, 배포 등)</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr"/>
-      <c r="E47" s="6" t="inlineStr"/>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트가 결과를 좌우한다 (bad vs good)
-마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr"/>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr"/>
-      <c r="E48" s="6" t="inlineStr"/>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>수업 22</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
       <c r="J48" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -2290,12 +2266,13 @@
       <c r="E49" s="6" t="inlineStr"/>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+          <t>프롬프트 기초</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>사례</t>
+          <t>프롬프트가 결과를 좌우한다 (bad vs good)
+마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr"/>
@@ -2306,6 +2283,7 @@
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -2314,29 +2292,29 @@
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr"/>
       <c r="E50" s="6" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>진급 반 인계 카드</t>
+          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr"/>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>수업 22</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>석희철</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
@@ -2346,9 +2324,10 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>2월</t>
-        </is>
-      </c>
+          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -2357,119 +2336,122 @@
         </is>
       </c>
       <c r="B51" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr"/>
       <c r="E51" s="6" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
+          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>사례</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>진급 반 인계 카드</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
           <t>조건을 반영한 자리 배치</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="6" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr"/>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>모둠 자동 편성기</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr"/>
-      <c r="H52" s="8" t="inlineStr"/>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K52" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr"/>
-      <c r="E53" s="8" t="inlineStr"/>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>학급 규칙 함께 정하기 투표판</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr"/>
-      <c r="H53" s="8" t="inlineStr"/>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K53" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 3월 학급 세우기 활동</t>
-        </is>
-      </c>
+      <c r="L53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -2489,7 +2471,7 @@
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>1인 1역 역할 배정표</t>
+          <t>모둠 자동 편성기</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr"/>
@@ -2506,9 +2488,10 @@
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
-        </is>
-      </c>
+          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -2528,7 +2511,7 @@
       <c r="E55" s="8" t="inlineStr"/>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>전자칠판용 우리 반 일과 안내판</t>
+          <t>학급 규칙 함께 정하기 투표판</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr"/>
@@ -2545,169 +2528,174 @@
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
+          <t>가안 · 3월 학급 세우기 활동</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr"/>
+      <c r="E56" s="8" t="inlineStr"/>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>1인 1역 역할 배정표</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr"/>
+      <c r="H56" s="8" t="inlineStr"/>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr"/>
+      <c r="E57" s="8" t="inlineStr"/>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>전자칠판용 우리 반 일과 안내판</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
           <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="L57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B58" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr"/>
-      <c r="E56" s="6" t="inlineStr"/>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>특별활동 자동 출석부</t>
         </is>
       </c>
-      <c r="G56" s="7" t="inlineStr"/>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>진정숙</t>
         </is>
       </c>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K56" s="7" t="inlineStr">
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
         <is>
           <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="L58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B59" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr"/>
-      <c r="E57" s="6" t="inlineStr"/>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr"/>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>청소 구역 점검판</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="inlineStr"/>
-      <c r="E58" s="8" t="inlineStr"/>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>과제 제출 체크리스트</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr"/>
-      <c r="H58" s="8" t="inlineStr"/>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J58" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K58" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr"/>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>칭찬 포인트 보드</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr"/>
-      <c r="H59" s="8" t="inlineStr"/>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J59" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K59" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
-        </is>
-      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -2727,7 +2715,7 @@
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>학급 행사 D-day 게시판</t>
+          <t>과제 제출 체크리스트</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr"/>
@@ -2744,9 +2732,10 @@
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>가안</t>
-        </is>
-      </c>
+          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -2766,7 +2755,7 @@
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>학급 문고 대출 기록표</t>
+          <t>칭찬 포인트 보드</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
@@ -2783,169 +2772,174 @@
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
+          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr"/>
+      <c r="E62" s="8" t="inlineStr"/>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>학급 행사 D-day 게시판</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr"/>
+      <c r="H62" s="8" t="inlineStr"/>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
           <t>가안</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B63" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr"/>
+      <c r="E63" s="8" t="inlineStr"/>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>학급 문고 대출 기록표</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr"/>
-      <c r="E62" s="6" t="inlineStr"/>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr"/>
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>겹치지 않는 학부모 상담 예약</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr"/>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr"/>
+      <c r="L64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B65" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="6" t="inlineStr"/>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr"/>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>정원이 차면 자동 마감되는 신청서</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I63" s="6" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K63" s="7" t="inlineStr">
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
         <is>
           <t>방과후학교·학부모 연수</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr"/>
-      <c r="E64" s="8" t="inlineStr"/>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>안내용 웹 가정통신문 만들기</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr"/>
-      <c r="H64" s="8" t="inlineStr"/>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J64" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr"/>
-      <c r="E65" s="8" t="inlineStr"/>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>참여 여부를 받는 가정통신문과 미응답 확인</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr"/>
-      <c r="H65" s="8" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K65" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 구글 시트로 응답 수합</t>
-        </is>
-      </c>
+      <c r="L65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -2965,7 +2959,7 @@
       <c r="E66" s="8" t="inlineStr"/>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>공개수업 참관 신청서</t>
+          <t>안내용 웹 가정통신문 만들기</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr"/>
@@ -2982,9 +2976,10 @@
       </c>
       <c r="K66" s="9" t="inlineStr">
         <is>
-          <t>가안 · 시간대별 정원 표시</t>
-        </is>
-      </c>
+          <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -3004,7 +2999,7 @@
       <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>상담 전 사전 질문지</t>
+          <t>참여 여부를 받는 가정통신문과 미응답 확인</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr"/>
@@ -3021,87 +3016,90 @@
       </c>
       <c r="K67" s="9" t="inlineStr">
         <is>
+          <t>가안 · 구글 시트로 응답 수합</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr"/>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>공개수업 참관 신청서</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 시간대별 정원 표시</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="8" t="inlineStr"/>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>상담 전 사전 질문지</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
           <t>가안 · 상담 예약(4-1)과 이어지는 실습</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr"/>
-      <c r="E68" s="6" t="inlineStr"/>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>회신서 미제출자 확인기</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K68" s="7" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C69" s="7" t="inlineStr">
-        <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr"/>
-      <c r="E69" s="6" t="inlineStr"/>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>QR로 받는 교직원 연수 서명부</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>이승엽</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -3121,18 +3119,18 @@
       <c r="E70" s="6" t="inlineStr"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>부서 통합 외부인 방문대장</t>
+          <t>회신서 미제출자 확인기</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr"/>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
@@ -3141,6 +3139,7 @@
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr"/>
+      <c r="L70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -3160,268 +3159,275 @@
       <c r="E71" s="6" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>공문서 표기 점검기</t>
+          <t>QR로 받는 교직원 연수 서명부</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>행정 업무: 서류와 수합 줄이기</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr"/>
+      <c r="E72" s="6" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>부서 통합 외부인 방문대장</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr"/>
+      <c r="L72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>행정 업무: 서류와 수합 줄이기</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr"/>
+      <c r="E73" s="6" t="inlineStr"/>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>공문서 표기 점검기</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr"/>
+      <c r="L73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B72" s="8" t="n">
+      <c r="B74" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr"/>
-      <c r="F72" s="9" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr"/>
+      <c r="E74" s="8" t="inlineStr"/>
+      <c r="F74" s="9" t="inlineStr">
         <is>
           <t>행사 물품 수요 조사 집계기</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr"/>
-      <c r="H72" s="8" t="inlineStr"/>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="G74" s="9" t="inlineStr"/>
+      <c r="H74" s="8" t="inlineStr"/>
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="J72" s="8" t="inlineStr">
+      <c r="J74" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="K72" s="9" t="inlineStr">
+      <c r="K74" s="9" t="inlineStr">
         <is>
           <t>가안 · 반별 수량을 모아 합계표로</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
+      <c r="L74" s="9" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B73" s="8" t="n">
+      <c r="B75" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr"/>
-      <c r="E73" s="8" t="inlineStr"/>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="8" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr">
         <is>
           <t>특별실·기자재 예약판</t>
         </is>
       </c>
-      <c r="G73" s="9" t="inlineStr"/>
-      <c r="H73" s="8" t="inlineStr"/>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="G75" s="9" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr"/>
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="J73" s="8" t="inlineStr">
+      <c r="J75" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="K73" s="9" t="inlineStr">
+      <c r="K75" s="9" t="inlineStr">
         <is>
           <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="L75" s="9" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n">
+      <c r="B76" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr"/>
-      <c r="E74" s="6" t="inlineStr"/>
-      <c r="F74" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr"/>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>단원 끝 학생 자기평가 카드</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J74" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K74" s="7" t="inlineStr">
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
         <is>
           <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
         </is>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="L76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B75" s="6" t="n">
+      <c r="B77" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr"/>
-      <c r="E75" s="6" t="inlineStr"/>
-      <c r="F75" s="7" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr"/>
+      <c r="E77" s="6" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>방학 중 안부 체크인</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="I77" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K75" s="7" t="inlineStr">
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B76" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
-        </is>
-      </c>
-      <c r="D76" s="9" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr"/>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>관찰 기록으로 단원 평어 초안 만들기</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="inlineStr"/>
-      <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K76" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="8" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>수행평가 채점 기준표(루브릭) 채점기</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="8" t="inlineStr"/>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J77" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K77" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 평가·기록 보강</t>
-        </is>
-      </c>
+      <c r="L77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -3441,7 +3447,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>문항별 정답률 분석표</t>
+          <t>관찰 기록으로 단원 평어 초안 만들기</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr"/>
@@ -3458,9 +3464,10 @@
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
-        </is>
-      </c>
+          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
@@ -3480,7 +3487,7 @@
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>생활기록부 글자 수·표현 점검기</t>
+          <t>수행평가 채점 기준표(루브릭) 채점기</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr"/>
@@ -3497,88 +3504,95 @@
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
+          <t>가안 · 평가·기록 보강</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="8" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>문항별 정답률 분석표</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr"/>
+      <c r="E81" s="8" t="inlineStr"/>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>생활기록부 글자 수·표현 점검기</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
           <t>가안 · 평가·기록 보강 · 바이트 수와 쓰지 않는 표현을 표시, 내용은 외부로 보내지 않음</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B80" s="10" t="inlineStr"/>
-      <c r="C80" s="11" t="inlineStr"/>
-      <c r="D80" s="11" t="inlineStr"/>
-      <c r="E80" s="10" t="inlineStr"/>
-      <c r="F80" s="11" t="inlineStr">
-        <is>
-          <t>발표 모드</t>
-        </is>
-      </c>
-      <c r="G80" s="11" t="inlineStr"/>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
-        <is>
-          <t>강현수</t>
-        </is>
-      </c>
-      <c r="J80" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K80" s="11" t="inlineStr">
-        <is>
-          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B81" s="10" t="inlineStr"/>
-      <c r="C81" s="11" t="inlineStr"/>
-      <c r="D81" s="11" t="inlineStr"/>
-      <c r="E81" s="10" t="inlineStr"/>
-      <c r="F81" s="11" t="inlineStr">
-        <is>
-          <t>기기대여대장</t>
-        </is>
-      </c>
-      <c r="G81" s="11" t="inlineStr"/>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>진정숙</t>
-        </is>
-      </c>
-      <c r="J81" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K81" s="11" t="inlineStr">
-        <is>
-          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
-        </is>
-      </c>
+      <c r="L81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>업무자동화</t>
+          <t>수업자동화</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr"/>
@@ -3587,18 +3601,18 @@
       <c r="E82" s="10" t="inlineStr"/>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>스마트 시간표 교체</t>
+          <t>발표 모드</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr"/>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="J82" s="10" t="inlineStr">
@@ -3608,9 +3622,10 @@
       </c>
       <c r="K82" s="11" t="inlineStr">
         <is>
-          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
-        </is>
-      </c>
+          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
+        </is>
+      </c>
+      <c r="L82" s="11" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -3624,18 +3639,18 @@
       <c r="E83" s="10" t="inlineStr"/>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>준비물, 전달사항 알림장 사이트</t>
+          <t>기기대여대장</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr"/>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>이지상</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="J83" s="10" t="inlineStr">
@@ -3645,7 +3660,12 @@
       </c>
       <c r="K83" s="11" t="inlineStr">
         <is>
-          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
+          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>‘학급 문고 대출 기록표’(가안) 대신 — 로그인·관리자 모드를 빼고 대여·반납 기록 한 가지 기능으로 줄이면</t>
         </is>
       </c>
     </row>
@@ -3661,18 +3681,18 @@
       <c r="E84" s="10" t="inlineStr"/>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>키워드 레이더</t>
+          <t>스마트 시간표 교체</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
@@ -3682,7 +3702,12 @@
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
+          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
+        </is>
+      </c>
+      <c r="L84" s="11" t="inlineStr">
+        <is>
+          <t>‘전자칠판용 우리 반 일과 안내판’(가안) 대신 — 전교 시간표 대신 우리 반 시간표 변경만 안내하는 화면으로 줄이면</t>
         </is>
       </c>
     </row>
@@ -3698,18 +3723,18 @@
       <c r="E85" s="10" t="inlineStr"/>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>부장회의록 및 주간계획</t>
+          <t>준비물, 전달사항 알림장 사이트</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>이지상</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr">
@@ -3719,7 +3744,12 @@
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
+          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
+        </is>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>‘안내용 웹 가정통신문 만들기’(가안) 대신 — 회원가입·댓글·첨부를 빼고 전달사항·준비물을 한 화면에 올리는 안내 페이지로 줄이면</t>
         </is>
       </c>
     </row>
@@ -3735,18 +3765,18 @@
       <c r="E86" s="10" t="inlineStr"/>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>우리반 출석부</t>
+          <t>키워드 레이더</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>이승엽</t>
         </is>
       </c>
       <c r="J86" s="10" t="inlineStr">
@@ -3756,9 +3786,10 @@
       </c>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
-        </is>
-      </c>
+          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
+        </is>
+      </c>
+      <c r="L86" s="11" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -3772,18 +3803,18 @@
       <c r="E87" s="10" t="inlineStr"/>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>학부모 상담 기록요약</t>
+          <t>부장회의록 및 주간계획</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>이승엽</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
@@ -3793,9 +3824,10 @@
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
-        </is>
-      </c>
+          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
+        </is>
+      </c>
+      <c r="L87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -3809,56 +3841,115 @@
       <c r="E88" s="10" t="inlineStr"/>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>반 편성 조건 점검기</t>
+          <t>우리반 출석부</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr"/>
       <c r="H88" s="10" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K88" s="11" t="inlineStr">
+        <is>
+          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
+        </is>
+      </c>
+      <c r="L88" s="11" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr"/>
+      <c r="C89" s="11" t="inlineStr"/>
+      <c r="D89" s="11" t="inlineStr"/>
+      <c r="E89" s="10" t="inlineStr"/>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>학부모 상담 기록요약</t>
+        </is>
+      </c>
+      <c r="G89" s="11" t="inlineStr"/>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
+        </is>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>‘상담 전 사전 질문지’(가안) 대신 — 외부 AI 없이 상담 메모를 항목별 칸에 나눠 정리하는 기록 양식으로 바꾸면</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr"/>
+      <c r="C90" s="11" t="inlineStr"/>
+      <c r="D90" s="11" t="inlineStr"/>
+      <c r="E90" s="10" t="inlineStr"/>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>반 편성 조건 점검기</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="inlineStr"/>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I88" s="10" t="inlineStr">
+      <c r="I90" s="10" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J88" s="10" t="inlineStr">
+      <c r="J90" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="K88" s="11" t="inlineStr">
+      <c r="K90" s="11" t="inlineStr">
         <is>
           <t>특수 배려·분리 요청 같은 민감 정보를 다루고 LLM API가 필요함. 제안자도 다음 회의에서 논의하기로 남겨 둠</t>
         </is>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="n"/>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="7" t="n"/>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="6" t="n"/>
-      <c r="I89" s="6" t="n"/>
-      <c r="J89" s="6" t="n"/>
-      <c r="K89" s="7" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="n"/>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="7" t="n"/>
-      <c r="G90" s="7" t="n"/>
-      <c r="H90" s="6" t="n"/>
-      <c r="I90" s="6" t="n"/>
-      <c r="J90" s="6" t="n"/>
-      <c r="K90" s="7" t="n"/>
+      <c r="L90" s="11" t="inlineStr">
+        <is>
+          <t>‘모둠 자동 편성기’(가안) 대신 — AI 없이, 이름 대신 번호로 성비·분리 조건만 점검하는 방식으로 줄이면</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
@@ -3872,6 +3963,7 @@
       <c r="I91" s="6" t="n"/>
       <c r="J91" s="6" t="n"/>
       <c r="K91" s="7" t="n"/>
+      <c r="L91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n"/>
@@ -3885,6 +3977,7 @@
       <c r="I92" s="6" t="n"/>
       <c r="J92" s="6" t="n"/>
       <c r="K92" s="7" t="n"/>
+      <c r="L92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -3898,6 +3991,7 @@
       <c r="I93" s="6" t="n"/>
       <c r="J93" s="6" t="n"/>
       <c r="K93" s="7" t="n"/>
+      <c r="L93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
@@ -3911,6 +4005,7 @@
       <c r="I94" s="6" t="n"/>
       <c r="J94" s="6" t="n"/>
       <c r="K94" s="7" t="n"/>
+      <c r="L94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
@@ -3924,6 +4019,7 @@
       <c r="I95" s="6" t="n"/>
       <c r="J95" s="6" t="n"/>
       <c r="K95" s="7" t="n"/>
+      <c r="L95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n"/>
@@ -3937,6 +4033,7 @@
       <c r="I96" s="6" t="n"/>
       <c r="J96" s="6" t="n"/>
       <c r="K96" s="7" t="n"/>
+      <c r="L96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
@@ -3950,6 +4047,7 @@
       <c r="I97" s="6" t="n"/>
       <c r="J97" s="6" t="n"/>
       <c r="K97" s="7" t="n"/>
+      <c r="L97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n"/>
@@ -3963,6 +4061,7 @@
       <c r="I98" s="6" t="n"/>
       <c r="J98" s="6" t="n"/>
       <c r="K98" s="7" t="n"/>
+      <c r="L98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
@@ -3976,6 +4075,7 @@
       <c r="I99" s="6" t="n"/>
       <c r="J99" s="6" t="n"/>
       <c r="K99" s="7" t="n"/>
+      <c r="L99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n"/>
@@ -3989,6 +4089,7 @@
       <c r="I100" s="6" t="n"/>
       <c r="J100" s="6" t="n"/>
       <c r="K100" s="7" t="n"/>
+      <c r="L100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
@@ -4002,6 +4103,7 @@
       <c r="I101" s="6" t="n"/>
       <c r="J101" s="6" t="n"/>
       <c r="K101" s="7" t="n"/>
+      <c r="L101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n"/>
@@ -4015,6 +4117,7 @@
       <c r="I102" s="6" t="n"/>
       <c r="J102" s="6" t="n"/>
       <c r="K102" s="7" t="n"/>
+      <c r="L102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n"/>
@@ -4028,6 +4131,7 @@
       <c r="I103" s="6" t="n"/>
       <c r="J103" s="6" t="n"/>
       <c r="K103" s="7" t="n"/>
+      <c r="L103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n"/>
@@ -4041,6 +4145,7 @@
       <c r="I104" s="6" t="n"/>
       <c r="J104" s="6" t="n"/>
       <c r="K104" s="7" t="n"/>
+      <c r="L104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n"/>
@@ -4054,6 +4159,7 @@
       <c r="I105" s="6" t="n"/>
       <c r="J105" s="6" t="n"/>
       <c r="K105" s="7" t="n"/>
+      <c r="L105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n"/>
@@ -4067,6 +4173,7 @@
       <c r="I106" s="6" t="n"/>
       <c r="J106" s="6" t="n"/>
       <c r="K106" s="7" t="n"/>
+      <c r="L106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n"/>
@@ -4080,6 +4187,7 @@
       <c r="I107" s="6" t="n"/>
       <c r="J107" s="6" t="n"/>
       <c r="K107" s="7" t="n"/>
+      <c r="L107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n"/>
@@ -4093,22 +4201,52 @@
       <c r="I108" s="6" t="n"/>
       <c r="J108" s="6" t="n"/>
       <c r="K108" s="7" t="n"/>
+      <c r="L108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="n"/>
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="7" t="n"/>
+      <c r="D109" s="7" t="n"/>
+      <c r="E109" s="6" t="n"/>
+      <c r="F109" s="7" t="n"/>
+      <c r="G109" s="7" t="n"/>
+      <c r="H109" s="6" t="n"/>
+      <c r="I109" s="6" t="n"/>
+      <c r="J109" s="6" t="n"/>
+      <c r="K109" s="7" t="n"/>
+      <c r="L109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="n"/>
+      <c r="B110" s="6" t="n"/>
+      <c r="C110" s="7" t="n"/>
+      <c r="D110" s="7" t="n"/>
+      <c r="E110" s="6" t="n"/>
+      <c r="F110" s="7" t="n"/>
+      <c r="G110" s="7" t="n"/>
+      <c r="H110" s="6" t="n"/>
+      <c r="I110" s="6" t="n"/>
+      <c r="J110" s="6" t="n"/>
+      <c r="K110" s="7" t="n"/>
+      <c r="L110" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B8:K8"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B5:K5"/>
+  <mergeCells count="8">
+    <mergeCell ref="B4:L4"/>
+    <mergeCell ref="B6:L6"/>
+    <mergeCell ref="B7:L7"/>
+    <mergeCell ref="B3:L3"/>
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B5:L5"/>
+    <mergeCell ref="B9:L9"/>
+    <mergeCell ref="B8:L8"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A11:A108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A13:A110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
-    <dataValidation sqref="J11:J108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J13:J110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -3567,10 +3567,17 @@
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>생활기록부 글자 수·표현 점검기</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr"/>
+          <t>생기부/세특 글자 수·표현 점검기</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>NEIS 기준 글자 수·바이트 계산, 항목별 제한 초과 표시
+기재 금지·유의 표현 형광펜 표시(목록은 교사가 수정)
+여러 학생에게 반복된 문장 찾기
+AI 문장 생성·윤문·외부 전송 없이 브라우저 안에서만 동작</t>
+        </is>
+      </c>
       <c r="H81" s="8" t="inlineStr"/>
       <c r="I81" s="8" t="inlineStr">
         <is>
@@ -3584,7 +3591,7 @@
       </c>
       <c r="K81" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 바이트 수와 쓰지 않는 표현을 표시, 내용은 외부로 보내지 않음</t>
+          <t>가안 · 평가·기록 보강 · 교육부 지침(AI는 보조만, AI 문장 그대로 기재 금지)에 맞춰 점검만 하고 수정은 교사가 결정</t>
         </is>
       </c>
       <c r="L81" s="9" t="inlineStr"/>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -3567,7 +3567,7 @@
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>생기부/세특 글자 수·표현 점검기</t>
+          <t>학교생활기록부/세부능력 및 특기사항 글자 수·표현 점검기</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -2383,7 +2383,7 @@
       <c r="E52" s="6" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>진급 반 인계 카드</t>
+          <t>[Codex] 진급 반 인계 카드</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr"/>
@@ -2427,7 +2427,7 @@
       <c r="E53" s="6" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>조건을 반영한 자리 배치</t>
+          <t>[Codex] 조건을 반영한 자리 배치</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
       <c r="E54" s="8" t="inlineStr"/>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>모둠 자동 편성기</t>
+          <t>[Codex] 모둠 자동 편성기</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr"/>
@@ -2511,7 +2511,7 @@
       <c r="E55" s="8" t="inlineStr"/>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>학급 규칙 함께 정하기 투표판</t>
+          <t>[Codex] 1인 1역 역할 배정표</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr"/>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>가안 · 3월 학급 세우기 활동</t>
+          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr"/>
@@ -2551,7 +2551,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>1인 1역 역할 배정표</t>
+          <t>[Codex] 전자칠판용 우리 반 일과 안내판</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr"/>
@@ -2568,50 +2568,54 @@
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
+          <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B57" s="8" t="n">
+      <c r="B57" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr"/>
-      <c r="E57" s="8" t="inlineStr"/>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>전자칠판용 우리 반 일과 안내판</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr"/>
-      <c r="H57" s="8" t="inlineStr"/>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J57" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K57" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
-        </is>
-      </c>
-      <c r="L57" s="9" t="inlineStr"/>
+      <c r="D57" s="7" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>[Codex] 특별활동 자동 출석부</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -2631,18 +2635,18 @@
       <c r="E58" s="6" t="inlineStr"/>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>특별활동 자동 출석부</t>
+          <t>[Codex] 청소 구역 점검판</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
@@ -2650,52 +2654,48 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
-        </is>
-      </c>
+      <c r="K58" s="7" t="inlineStr"/>
       <c r="L58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr"/>
-      <c r="E59" s="6" t="inlineStr"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>청소 구역 점검판</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr"/>
-      <c r="L59" s="7" t="inlineStr"/>
+      <c r="D59" s="9" t="inlineStr"/>
+      <c r="E59" s="8" t="inlineStr"/>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>[Codex] 과제 제출 체크리스트</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -2715,7 +2715,7 @@
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="9" t="inlineStr">
         <is>
-          <t>과제 제출 체크리스트</t>
+          <t>[Codex] 칭찬 포인트 보드</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr"/>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
+          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
         </is>
       </c>
       <c r="L60" s="9" t="inlineStr"/>
@@ -2755,7 +2755,7 @@
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>칭찬 포인트 보드</t>
+          <t>[Codex] 학급 행사 D-day 게시판</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
+          <t>가안</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>학급 행사 D-day 게시판</t>
+          <t>[Codex] 학급 문고 대출 기록표</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr"/>
@@ -2835,7 +2835,7 @@
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>학급 문고 대출 기록표</t>
+          <t>[Codex+DB] 학급 규칙 함께 정하기 투표판</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr"/>
@@ -2852,50 +2852,50 @@
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
+          <t>가안 · 3월 학급 세우기 활동</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr"/>
+      <c r="E64" s="8" t="inlineStr"/>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>[Codex] 안내용 웹 가정통신문 만들기</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="L63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr"/>
-      <c r="E64" s="6" t="inlineStr"/>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>겹치지 않는 학부모 상담 예약</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>임부현</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K64" s="7" t="inlineStr"/>
-      <c r="L64" s="7" t="inlineStr"/>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -2915,71 +2915,71 @@
       <c r="E65" s="6" t="inlineStr"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>정원이 차면 자동 마감되는 신청서</t>
+          <t>[Codex+DB] 겹치지 않는 학부모 상담 예약</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr"/>
+      <c r="E66" s="6" t="inlineStr"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>[Codex+DB] 정원이 차면 자동 마감되는 신청서</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I66" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr">
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
         <is>
           <t>방과후학교·학부모 연수</t>
         </is>
       </c>
-      <c r="L65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>안내용 웹 가정통신문 만들기</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J66" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K66" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
-        </is>
-      </c>
-      <c r="L66" s="9" t="inlineStr"/>
+      <c r="L66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -2999,7 +2999,7 @@
       <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>참여 여부를 받는 가정통신문과 미응답 확인</t>
+          <t>[Codex+DB] 참여 여부를 받는 가정통신문과 미응답 확인</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       <c r="E68" s="8" t="inlineStr"/>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>공개수업 참관 신청서</t>
+          <t>[Codex+DB] 공개수업 참관 신청서</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr"/>
@@ -3079,7 +3079,7 @@
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>상담 전 사전 질문지</t>
+          <t>[Codex+DB] 상담 전 사전 질문지</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr"/>
@@ -3119,7 +3119,7 @@
       <c r="E70" s="6" t="inlineStr"/>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>회신서 미제출자 확인기</t>
+          <t>[Codex] 회신서 미제출자 확인기</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr"/>
@@ -3159,18 +3159,18 @@
       <c r="E71" s="6" t="inlineStr"/>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>QR로 받는 교직원 연수 서명부</t>
+          <t>[Codex] 공문서 표기 점검기</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
@@ -3199,13 +3199,13 @@
       <c r="E72" s="6" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>부서 통합 외부인 방문대장</t>
+          <t>[Codex+DB] QR로 받는 교직원 연수 서명부</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
@@ -3239,18 +3239,18 @@
       <c r="E73" s="6" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>공문서 표기 점검기</t>
+          <t>[Codex+DB] 부서 통합 외부인 방문대장</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>석희철</t>
+          <t>이승엽</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
@@ -3279,7 +3279,7 @@
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>행사 물품 수요 조사 집계기</t>
+          <t>[Codex+DB] 행사 물품 수요 조사 집계기</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
       <c r="E75" s="8" t="inlineStr"/>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>특별실·기자재 예약판</t>
+          <t>[Codex+DB] 특별실·기자재 예약판</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr"/>
@@ -3342,92 +3342,84 @@
       <c r="L75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n">
+      <c r="B76" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr"/>
-      <c r="E76" s="6" t="inlineStr"/>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>단원 끝 학생 자기평가 카드</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J76" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K76" s="7" t="inlineStr">
-        <is>
-          <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
-        </is>
-      </c>
-      <c r="L76" s="7" t="inlineStr"/>
+      <c r="D76" s="9" t="inlineStr"/>
+      <c r="E76" s="8" t="inlineStr"/>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>[Codex] 관찰 기록으로 단원 평어 초안 만들기</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B77" s="6" t="n">
+      <c r="B77" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr"/>
-      <c r="E77" s="6" t="inlineStr"/>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>방학 중 안부 체크인</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K77" s="7" t="inlineStr">
-        <is>
-          <t>7월</t>
-        </is>
-      </c>
-      <c r="L77" s="7" t="inlineStr"/>
+      <c r="D77" s="9" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr"/>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>[Codex] 수행평가 채점 기준표(루브릭) 채점기</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 평가·기록 보강</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -3447,7 +3439,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>관찰 기록으로 단원 평어 초안 만들기</t>
+          <t>[Codex] 문항별 정답률 분석표</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr"/>
@@ -3464,7 +3456,7 @@
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
+          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr"/>
@@ -3487,90 +3479,10 @@
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>수행평가 채점 기준표(루브릭) 채점기</t>
-        </is>
-      </c>
-      <c r="G79" s="9" t="inlineStr"/>
-      <c r="H79" s="8" t="inlineStr"/>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J79" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K79" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 평가·기록 보강</t>
-        </is>
-      </c>
-      <c r="L79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B80" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr"/>
-      <c r="E80" s="8" t="inlineStr"/>
-      <c r="F80" s="9" t="inlineStr">
-        <is>
-          <t>문항별 정답률 분석표</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr"/>
-      <c r="H80" s="8" t="inlineStr"/>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J80" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K80" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
-        </is>
-      </c>
-      <c r="L80" s="9" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>학교생활기록부/세부능력 및 특기사항 글자 수·표현 점검기</t>
-        </is>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
+          <t>[Codex] 학교생활기록부/세부능력 및 특기사항 글자 수·표현 점검기</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>NEIS 기준 글자 수·바이트 계산, 항목별 제한 초과 표시
 기재 금지·유의 표현 형광펜 표시(목록은 교사가 수정)
@@ -3578,23 +3490,111 @@
 AI 문장 생성·윤문·외부 전송 없이 브라우저 안에서만 동작</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="J81" s="8" t="inlineStr">
+      <c r="J79" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="K79" s="9" t="inlineStr">
         <is>
           <t>가안 · 평가·기록 보강 · 교육부 지침(AI는 보조만, AI 문장 그대로 기재 금지)에 맞춰 점검만 하고 수정은 교사가 결정</t>
         </is>
       </c>
-      <c r="L81" s="9" t="inlineStr"/>
+      <c r="L79" s="9" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr"/>
+      <c r="E80" s="6" t="inlineStr"/>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>[Codex+DB] 단원 끝 학생 자기평가 카드</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
+        </is>
+      </c>
+      <c r="L80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr"/>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>[Codex+DB] 방학 중 안부 체크인</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>7월</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -2835,7 +2835,7 @@
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>[Codex+DB] 학급 규칙 함께 정하기 투표판</t>
+          <t>[Codex+구글 시트] 학급 규칙 함께 정하기 투표판</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr"/>
@@ -2915,7 +2915,7 @@
       <c r="E65" s="6" t="inlineStr"/>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>[Codex+DB] 겹치지 않는 학부모 상담 예약</t>
+          <t>[Codex+구글 시트] 겹치지 않는 학부모 상담 예약</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr"/>
@@ -2955,7 +2955,7 @@
       <c r="E66" s="6" t="inlineStr"/>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>[Codex+DB] 정원이 차면 자동 마감되는 신청서</t>
+          <t>[Codex+구글 시트] 정원이 차면 자동 마감되는 신청서</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
       <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>[Codex+DB] 참여 여부를 받는 가정통신문과 미응답 확인</t>
+          <t>[Codex+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       <c r="E68" s="8" t="inlineStr"/>
       <c r="F68" s="9" t="inlineStr">
         <is>
-          <t>[Codex+DB] 공개수업 참관 신청서</t>
+          <t>[Codex+구글 시트] 공개수업 참관 신청서</t>
         </is>
       </c>
       <c r="G68" s="9" t="inlineStr"/>
@@ -3079,7 +3079,7 @@
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>[Codex+DB] 상담 전 사전 질문지</t>
+          <t>[Codex+구글 시트] 상담 전 사전 질문지</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr"/>
@@ -3199,7 +3199,7 @@
       <c r="E72" s="6" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>[Codex+DB] QR로 받는 교직원 연수 서명부</t>
+          <t>[Codex+구글 시트] QR로 받는 교직원 연수 서명부</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
@@ -3239,7 +3239,7 @@
       <c r="E73" s="6" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>[Codex+DB] 부서 통합 외부인 방문대장</t>
+          <t>[Codex+구글 시트] 부서 통합 외부인 방문대장</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
@@ -3279,7 +3279,7 @@
       <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>[Codex+DB] 행사 물품 수요 조사 집계기</t>
+          <t>[Codex+구글 시트] 행사 물품 수요 조사 집계기</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
       <c r="E75" s="8" t="inlineStr"/>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>[Codex+DB] 특별실·기자재 예약판</t>
+          <t>[Codex+구글 시트] 특별실·기자재 예약판</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       <c r="E80" s="6" t="inlineStr"/>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>[Codex+DB] 단원 끝 학생 자기평가 카드</t>
+          <t>[Codex+구글 시트] 단원 끝 학생 자기평가 카드</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
       <c r="E81" s="6" t="inlineStr"/>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>[Codex+DB] 방학 중 안부 체크인</t>
+          <t>[Codex+Firebase] 방학 중 안부 체크인</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr"/>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -897,45 +897,36 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>사용 도구: ChatGPT의 Codex 활용</t>
-        </is>
-      </c>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>[공통] 성취기준으로 지도안·학습지 초안 만들기</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
+          <t>실습 도구 준비하기: 설치하고 미리 보기</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>ChatGPT 계정·요금제 확인과 Codex 시작하기
+Codex로 만든 HTML 파일을 브라우저에서 열어 미리 보기
+구글 앱스 스크립트 편집기 열어 보기 (PART 4)
+OpenAI API 키 발급과 사용 비용 확인 (PART 4)</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
       <c r="J17" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="K17" s="7" t="inlineStr"/>
       <c r="L17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
@@ -952,17 +943,21 @@
           <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>사용 도구: ChatGPT의 Codex 활용</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>[공통] 학생용·교사용 학습지 한 번에 찍어내기</t>
+          <t>[공통] 성취기준으로 지도안·학습지 초안 만들기</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -975,7 +970,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr"/>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+        </is>
+      </c>
       <c r="L18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
@@ -996,18 +995,18 @@
       <c r="E19" s="6" t="inlineStr"/>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>[공통] 활동 순서와 남은 시간을 띄우는 수업 전광판</t>
+          <t>[공통] 학생용·교사용 학습지 한 번에 찍어내기</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
@@ -1036,18 +1035,18 @@
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>[공통] 모둠 활동 소음 신호등</t>
+          <t>[공통] 활동 순서와 남은 시간을 띄우는 수업 전광판</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
@@ -1055,11 +1054,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>전광판(2-1)과 한 꼭지로 합칠지 검토</t>
-        </is>
-      </c>
+      <c r="K20" s="7" t="inlineStr"/>
       <c r="L20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1080,13 +1075,13 @@
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>[공통] 질문·발표자를 뽑는 캡슐 뽑기 기계</t>
+          <t>[공통] 모둠 활동 소음 신호등</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1099,7 +1094,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>전광판(2-1)과 한 꼭지로 합칠지 검토</t>
+        </is>
+      </c>
       <c r="L21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1120,18 +1119,18 @@
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>[공통] 답 대신 질문하는 수업 챗봇 만들기</t>
+          <t>[공통] 질문·발표자를 뽑는 캡슐 뽑기 기계</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>임부현</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
@@ -1139,11 +1138,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
-        <is>
-          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="K22" s="7" t="inlineStr"/>
       <c r="L22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1164,13 +1159,13 @@
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>[공통] 과제에 붙이는 AI 사용 내역 카드</t>
+          <t>[공통] 답 대신 질문하는 수업 챗봇 만들기</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -1183,7 +1178,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>AI API 필요: API 키 발급·비용·배포 과정을 실습에 넣을지 결정 필요</t>
+        </is>
+      </c>
       <c r="L23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1204,13 +1203,13 @@
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>[공통] 한 권 읽기 독서일지</t>
+          <t>[공통] 과제에 붙이는 AI 사용 내역 카드</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1223,11 +1222,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>참여 코드·학급별 기록 저장(DB)이 필요한 심화 실습</t>
-        </is>
-      </c>
+      <c r="K24" s="7" t="inlineStr"/>
       <c r="L24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1248,13 +1243,13 @@
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>[공통] 구글 폼 응답을 전자칠판에 띄우기</t>
+          <t>[공통] 한 권 읽기 독서일지</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -1267,7 +1262,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>참여 코드·학급별 기록 저장(DB)이 필요한 심화 실습</t>
+        </is>
+      </c>
       <c r="L25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1288,13 +1287,13 @@
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>[공통] 활동 사진 반별 제출함</t>
+          <t>[공통] 구글 폼 응답을 전자칠판에 띄우기</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -1307,11 +1306,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K26" s="7" t="inlineStr">
-        <is>
-          <t>구글 앱스 스크립트 실습(clasp 자동 업로드는 빼고 진행)</t>
-        </is>
-      </c>
+      <c r="K26" s="7" t="inlineStr"/>
       <c r="L26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1332,18 +1327,18 @@
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>[공통] 단원 용어 플래시 학습 게임</t>
+          <t>[공통] 활동 사진 반별 제출함</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
@@ -1351,7 +1346,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>구글 앱스 스크립트 실습(clasp 자동 업로드는 빼고 진행)</t>
+        </is>
+      </c>
       <c r="L27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1372,18 +1371,18 @@
       <c r="E28" s="6" t="inlineStr"/>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>[공통] 개념 빙고판 30장 자동 생성기</t>
+          <t>[공통] 단원 용어 플래시 학습 게임</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
@@ -1401,33 +1400,29 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>사용 도구: ChatGPT의 Codex 활용</t>
-        </is>
-      </c>
+          <t>공통 실습: 어느 교과에서나 쓰는 수업 도구 만들기</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr"/>
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>[국어] 낚시 제목 감별 카드 (사회) (도덕) (정보) (영어)</t>
+          <t>[공통] 개념 빙고판 30장 자동 생성기</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr"/>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>임부현</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -1452,17 +1447,21 @@
           <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>사용 도구: ChatGPT의 Codex 활용</t>
+        </is>
+      </c>
       <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문단 번호 읽기판 (영어) (사회) (과학) (한문)</t>
+          <t>[국어] 낚시 제목 감별 카드 (사회) (도덕) (정보) (영어)</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr"/>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -1496,13 +1495,13 @@
       <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>[국어] 다섯 칸으로 쓰는 시 설계도 (영어) (음악) (미술)</t>
+          <t>[국어] 문단 번호 읽기판 (영어) (사회) (과학) (한문)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr"/>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -1536,13 +1535,13 @@
       <c r="E32" s="6" t="inlineStr"/>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>[국어] 끌어다 놓는 품사 분류 바구니 (영어) (과학) (실과) (기술·가정)</t>
+          <t>[국어] 다섯 칸으로 쓰는 시 설계도 (영어) (음악) (미술)</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr"/>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
@@ -1555,11 +1554,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>기본편. 같은 주제의 심화편은 PART 4 ‘품사 문제 출제기’</t>
-        </is>
-      </c>
+      <c r="K32" s="7" t="inlineStr"/>
       <c r="L32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1580,13 +1575,13 @@
       <c r="E33" s="6" t="inlineStr"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>[국어] 모둠 토의 진행판 (사회) (도덕) (과학) (진로)</t>
+          <t>[국어] 끌어다 놓는 품사 분류 바구니 (영어) (과학) (실과) (기술·가정)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -1601,7 +1596,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>다른 교과 토의·토론으로 확장 가능</t>
+          <t>기본편. 같은 주제의 심화편은 PART 4 ‘품사 문제 출제기’</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr"/>
@@ -1624,67 +1619,71 @@
       <c r="E34" s="6" t="inlineStr"/>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (제2외국어) (정보)</t>
+          <t>[국어] 모둠 토의 진행판 (사회) (도덕) (과학) (진로)</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
       <c r="H34" s="6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>김형훈</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>다른 교과 토의·토론으로 확장 가능</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>수업자동화</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>[국어] 고쳐 쓴 부분이 보이는 비교판 (영어) (제2외국어) (정보)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>김형훈</t>
         </is>
       </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>[영어] 듣고 따라 말하는 영어 문장 카드 (제2외국어) (국어) (한문)</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="8" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J35" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
-        </is>
-      </c>
-      <c r="L35" s="9" t="inlineStr"/>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr"/>
+      <c r="L35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -1704,7 +1703,7 @@
       <c r="E36" s="8" t="inlineStr"/>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>[수학] 함수 그래프가 움직이는 계수 탐구판 (물리) (경제) (정보)</t>
+          <t>[영어] 듣고 따라 말하는 영어 문장 카드 (제2외국어) (국어) (한문)</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
@@ -1721,54 +1720,50 @@
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
+          <t>가안 · 영어 교과 꼭지가 없어 보강 · 브라우저 음성 읽기 기능으로 API 없이 실습</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>수업자동화</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>[수학] 함수 그래프가 움직이는 계수 탐구판 (물리) (경제) (정보)</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
           <t>가안 · 수학 활동 꼭지가 없어 보강 · 슬라이더로 계수를 바꾸는 단일 HTML 실습</t>
         </is>
       </c>
-      <c r="L36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학) (경제)</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>김진혁</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K37" s="7" t="inlineStr">
-        <is>
-          <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
-        </is>
-      </c>
-      <c r="L37" s="7" t="inlineStr"/>
+      <c r="L37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1788,18 +1783,18 @@
       <c r="E38" s="6" t="inlineStr"/>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>[사회] 선사시대 시간 탐사 게임 (역사) (지구과학) (미술)</t>
+          <t>[수학] 시험지에 바로 붙이는 함수 그래프 만들기 (과학) (경제)</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr"/>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>김진혁</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
@@ -1807,7 +1802,11 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K38" s="7" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>시험 출제용이라 업무자동화(평가)로 옮길지 검토</t>
+        </is>
+      </c>
       <c r="L38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1828,13 +1827,13 @@
       <c r="E39" s="6" t="inlineStr"/>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>[체육] 종목별 경기 점수판 (수학) (영어)</t>
+          <t>[사회] 선사시대 시간 탐사 게임 (역사) (지구과학) (미술)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr"/>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -1857,33 +1856,29 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>사용 도구: ChatGPT의 Codex로 만들고, 구글 앱스 스크립트 또는 OpenAI API를 붙여서 실습</t>
-        </is>
-      </c>
+          <t>과목별 기본: HTML 한 장으로 교과 앱 만들기</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr"/>
       <c r="E40" s="6" t="inlineStr"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>[국어] 내 말로 만드는 품사 문제 출제기 (영어) (제2외국어) (한문)</t>
+          <t>[체육] 종목별 경기 점수판 (수학) (영어)</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr"/>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>김형훈</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
@@ -1891,11 +1886,7 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr">
-        <is>
-          <t>심화 이유: AI API(OpenAI)로 학생 글에서 문제를 만듦 / 기본편은 PART 3 ‘품사 분류 바구니’</t>
-        </is>
-      </c>
+      <c r="K40" s="7" t="inlineStr"/>
       <c r="L40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1912,17 +1903,21 @@
           <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>사용 도구: ChatGPT의 Codex로 만들고, 구글 앱스 스크립트 또는 OpenAI API를 붙여서 실습</t>
+        </is>
+      </c>
       <c r="E41" s="6" t="inlineStr"/>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>[국어] 문장 구조 분석기 (영어) (제2외국어)</t>
+          <t>[국어] 내 말로 만드는 품사 문제 출제기 (영어) (제2외국어) (한문)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -1937,7 +1932,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: AI API(Gemini)로 문장을 분석함</t>
+          <t>심화 이유: AI API(OpenAI)로 학생 글에서 문제를 만듦 / 기본편은 PART 3 ‘품사 분류 바구니’</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr"/>
@@ -1960,13 +1955,13 @@
       <c r="E42" s="6" t="inlineStr"/>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학) (역사) (도덕)</t>
+          <t>[국어] 문장 구조 분석기 (영어) (제2외국어)</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr"/>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -1981,7 +1976,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: AI API 연결과 ‘답 대신 되묻기’ 프롬프트 설계가 필요함</t>
+          <t>심화 이유: AI API(Gemini)로 문장을 분석함</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr"/>
@@ -2004,18 +1999,18 @@
       <c r="E43" s="6" t="inlineStr"/>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>[과학] 화학 결합 실험실 (물리) (지구과학) (수학)</t>
+          <t>[국어] 근거를 되묻는 AI 읽기 코치 (사회) (과학) (역사) (도덕)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr"/>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>강현수</t>
+          <t>김형훈</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
@@ -2025,7 +2020,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 전자 이동·공유를 과학적으로 맞게 움직이는 애니메이션 구현</t>
+          <t>심화 이유: AI API 연결과 ‘답 대신 되묻기’ 프롬프트 설계가 필요함</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr"/>
@@ -2048,13 +2043,13 @@
       <c r="E44" s="6" t="inlineStr"/>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>[과학] 기체 법칙 탐구 실험실 (수학) (물리)</t>
+          <t>[과학] 화학 결합 실험실 (물리) (지구과학) (수학)</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -2069,7 +2064,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 압력·부피·온도 관계를 입자 움직임으로 시뮬레이션 / 화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
+          <t>심화 이유: 전자 이동·공유를 과학적으로 맞게 움직이는 애니메이션 구현</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr"/>
@@ -2092,18 +2087,18 @@
       <c r="E45" s="6" t="inlineStr"/>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>[정보] 정렬 알고리즘 실험실 (수학) (실과)</t>
+          <t>[과학] 기체 법칙 탐구 실험실 (수학) (물리)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>이은덕</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
@@ -2113,7 +2108,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 정렬 과정을 단계별로 멈추고 보여 주는 상태 관리</t>
+          <t>심화 이유: 압력·부피·온도 관계를 입자 움직임으로 시뮬레이션 / 화학 결합 실험실과 이어서 '실험실 만들기' 심화로 구성 가능</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr"/>
@@ -2136,13 +2131,13 @@
       <c r="E46" s="6" t="inlineStr"/>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>[정보] 설치 없이 쓰는 파이썬 연습장 (수학) (과학)</t>
+          <t>[정보] 정렬 알고리즘 실험실 (수학) (실과)</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
@@ -2157,7 +2152,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 브라우저 안에서 파이썬을 실행하는 외부 실행 환경(Pyodide) 연결</t>
+          <t>심화 이유: 정렬 과정을 단계별로 멈추고 보여 주는 상태 관리</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr"/>
@@ -2180,18 +2175,18 @@
       <c r="E47" s="6" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (한국사) (통합교과)</t>
+          <t>[정보] 설치 없이 쓰는 파이썬 연습장 (수학) (과학)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>이은덕</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
@@ -2201,7 +2196,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
+          <t>심화 이유: 브라우저 안에서 파이썬을 실행하는 외부 실행 환경(Pyodide) 연결</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr"/>
@@ -2209,72 +2204,79 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>업무자동화</t>
+          <t>수업자동화</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩 이론</t>
-        </is>
-      </c>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr"/>
       <c r="E48" s="6" t="inlineStr"/>
       <c r="F48" s="7" t="inlineStr">
         <is>
+          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (한국사) (통합교과)</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩 이론</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
           <t>바이브 코딩이란?</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 개념 (패러다임의 변화)
 개발 과정 (요구분석-설계-구현-테스트-배포-운영)
 필수 용어 (예: 라이브러리, 빌드, 디버깅, 배포 등)</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
-      <c r="I48" s="6" t="inlineStr"/>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr"/>
-      <c r="L48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr"/>
-      <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트가 결과를 좌우한다 (bad vs good)
-마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
-        </is>
-      </c>
       <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr">
@@ -2303,30 +2305,23 @@
       <c r="E50" s="6" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>수업 22</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
+          <t>프롬프트 기초</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트가 결과를 좌우한다 (bad vs good)
+마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="K50" s="7" t="inlineStr"/>
       <c r="L50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2347,22 +2342,30 @@
       <c r="E51" s="6" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>사례</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr"/>
-      <c r="I51" s="6" t="inlineStr"/>
+          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>수업 22</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>김형훈</t>
+        </is>
+      </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
+        </is>
+      </c>
       <c r="L51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2372,41 +2375,33 @@
         </is>
       </c>
       <c r="B52" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr"/>
       <c r="E52" s="6" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>[Codex] 진급 반 인계 카드</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr"/>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
+          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>사례</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
       <c r="J52" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K52" s="7" t="inlineStr">
-        <is>
-          <t>2월</t>
-        </is>
-      </c>
+      <c r="K52" s="7" t="inlineStr"/>
       <c r="L52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2416,122 +2411,125 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr"/>
       <c r="E53" s="6" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
+          <t>실습 도구 준비하기: 설치하고 미리 보기</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>ChatGPT 계정·요금제 확인과 Codex 시작하기
+Codex로 만든 HTML 파일을 브라우저에서 열어 미리 보기
+구글 시트와 앱스 스크립트 연결해 보기
+Firebase 프로젝트 만들어 보기 (방학 중 안부 체크인)</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>[Codex] 진급 반 인계 카드</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
           <t>[Codex] 조건을 반영한 자리 배치</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr"/>
-      <c r="E54" s="8" t="inlineStr"/>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>[Codex] 모둠 자동 편성기</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr"/>
-      <c r="H54" s="8" t="inlineStr"/>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J54" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K54" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
-        </is>
-      </c>
-      <c r="L54" s="9" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>[Codex] 1인 1역 역할 배정표</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr"/>
-      <c r="H55" s="8" t="inlineStr"/>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J55" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
-        </is>
-      </c>
-      <c r="L55" s="9" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -2551,7 +2549,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 전자칠판용 우리 반 일과 안내판</t>
+          <t>[Codex] 모둠 자동 편성기</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr"/>
@@ -2568,174 +2566,174 @@
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
+          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr"/>
+      <c r="E57" s="8" t="inlineStr"/>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>[Codex] 1인 1역 역할 배정표</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr"/>
+      <c r="E58" s="8" t="inlineStr"/>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>[Codex] 전자칠판용 우리 반 일과 안내판</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
           <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
         </is>
       </c>
-      <c r="L56" s="9" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="L58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B59" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr"/>
-      <c r="E57" s="6" t="inlineStr"/>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr"/>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>[Codex] 특별활동 자동 출석부</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I59" s="6" t="inlineStr">
         <is>
           <t>진정숙</t>
         </is>
       </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
         <is>
           <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
         </is>
       </c>
-      <c r="L57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="L59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B60" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr"/>
-      <c r="E58" s="6" t="inlineStr"/>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr"/>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>[Codex] 청소 구역 점검판</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K58" s="7" t="inlineStr"/>
-      <c r="L58" s="7" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr"/>
-      <c r="E59" s="8" t="inlineStr"/>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>[Codex] 과제 제출 체크리스트</t>
-        </is>
-      </c>
-      <c r="G59" s="9" t="inlineStr"/>
-      <c r="H59" s="8" t="inlineStr"/>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J59" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K59" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
-        </is>
-      </c>
-      <c r="L59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr"/>
-      <c r="E60" s="8" t="inlineStr"/>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>[Codex] 칭찬 포인트 보드</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr"/>
-      <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J60" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
-        </is>
-      </c>
-      <c r="L60" s="9" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -2755,7 +2753,7 @@
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 학급 행사 D-day 게시판</t>
+          <t>[Codex] 과제 제출 체크리스트</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
@@ -2772,7 +2770,7 @@
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>가안</t>
+          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr"/>
@@ -2795,7 +2793,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 학급 문고 대출 기록표</t>
+          <t>[Codex] 칭찬 포인트 보드</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr"/>
@@ -2812,7 +2810,7 @@
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>가안</t>
+          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr"/>
@@ -2835,7 +2833,7 @@
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 학급 규칙 함께 정하기 투표판</t>
+          <t>[Codex] 학급 행사 D-day 게시판</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr"/>
@@ -2852,7 +2850,7 @@
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
-          <t>가안 · 3월 학급 세우기 활동</t>
+          <t>가안</t>
         </is>
       </c>
       <c r="L63" s="9" t="inlineStr"/>
@@ -2864,18 +2862,18 @@
         </is>
       </c>
       <c r="B64" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr"/>
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 안내용 웹 가정통신문 만들기</t>
+          <t>[Codex] 학급 문고 대출 기록표</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr"/>
@@ -2892,174 +2890,174 @@
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr"/>
+      <c r="E65" s="8" t="inlineStr"/>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>[Codex+구글 시트] 학급 규칙 함께 정하기 투표판</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 3월 학급 세우기 활동</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr"/>
+      <c r="E66" s="8" t="inlineStr"/>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>[Codex] 안내용 웹 가정통신문 만들기</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
           <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
         </is>
       </c>
-      <c r="L64" s="9" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="L66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B67" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr"/>
-      <c r="E65" s="6" t="inlineStr"/>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr"/>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr">
         <is>
           <t>[Codex+구글 시트] 겹치지 않는 학부모 상담 예약</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I65" s="6" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K65" s="7" t="inlineStr"/>
-      <c r="L65" s="7" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B68" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr"/>
-      <c r="E66" s="6" t="inlineStr"/>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>[Codex+구글 시트] 정원이 차면 자동 마감되는 신청서</t>
         </is>
       </c>
-      <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I66" s="6" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K66" s="7" t="inlineStr">
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
         <is>
           <t>방과후학교·학부모 연수</t>
         </is>
       </c>
-      <c r="L66" s="7" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr"/>
-      <c r="E67" s="8" t="inlineStr"/>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>[Codex+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
-        </is>
-      </c>
-      <c r="G67" s="9" t="inlineStr"/>
-      <c r="H67" s="8" t="inlineStr"/>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K67" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 구글 시트로 응답 수합</t>
-        </is>
-      </c>
-      <c r="L67" s="9" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>[Codex+구글 시트] 공개수업 참관 신청서</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr"/>
-      <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J68" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 시간대별 정원 표시</t>
-        </is>
-      </c>
-      <c r="L68" s="9" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -3079,7 +3077,7 @@
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 상담 전 사전 질문지</t>
+          <t>[Codex+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr"/>
@@ -3096,90 +3094,90 @@
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
+          <t>가안 · 구글 시트로 응답 수합</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr"/>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>[Codex+구글 시트] 공개수업 참관 신청서</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 시간대별 정원 표시</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>[Codex+구글 시트] 상담 전 사전 질문지</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
           <t>가안 · 상담 예약(4-1)과 이어지는 실습</t>
         </is>
       </c>
-      <c r="L69" s="9" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
-        </is>
-      </c>
-      <c r="D70" s="7" t="inlineStr"/>
-      <c r="E70" s="6" t="inlineStr"/>
-      <c r="F70" s="7" t="inlineStr">
-        <is>
-          <t>[Codex] 회신서 미제출자 확인기</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr"/>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K70" s="7" t="inlineStr"/>
-      <c r="L70" s="7" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="6" t="inlineStr"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>[Codex] 공문서 표기 점검기</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr"/>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr"/>
-      <c r="L71" s="7" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -3199,18 +3197,18 @@
       <c r="E72" s="6" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] QR로 받는 교직원 연수 서명부</t>
+          <t>[Codex] 회신서 미제출자 확인기</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
@@ -3239,18 +3237,18 @@
       <c r="E73" s="6" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 부서 통합 외부인 방문대장</t>
+          <t>[Codex] 공문서 표기 점검기</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
@@ -3262,84 +3260,84 @@
       <c r="L73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="8" t="inlineStr">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B74" s="8" t="n">
+      <c r="B74" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C74" s="9" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr"/>
-      <c r="E74" s="8" t="inlineStr"/>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>[Codex+구글 시트] 행사 물품 수요 조사 집계기</t>
-        </is>
-      </c>
-      <c r="G74" s="9" t="inlineStr"/>
-      <c r="H74" s="8" t="inlineStr"/>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J74" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K74" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 반별 수량을 모아 합계표로</t>
-        </is>
-      </c>
-      <c r="L74" s="9" t="inlineStr"/>
+      <c r="D74" s="7" t="inlineStr"/>
+      <c r="E74" s="6" t="inlineStr"/>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>[Codex+구글 시트] QR로 받는 교직원 연수 서명부</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr"/>
+      <c r="L74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B75" s="8" t="n">
+      <c r="B75" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr"/>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>[Codex+구글 시트] 특별실·기자재 예약판</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J75" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K75" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
-        </is>
-      </c>
-      <c r="L75" s="9" t="inlineStr"/>
+      <c r="D75" s="7" t="inlineStr"/>
+      <c r="E75" s="6" t="inlineStr"/>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>[Codex+구글 시트] 부서 통합 외부인 방문대장</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -3348,18 +3346,18 @@
         </is>
       </c>
       <c r="B76" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
+          <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr"/>
       <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 관찰 기록으로 단원 평어 초안 만들기</t>
+          <t>[Codex+구글 시트] 행사 물품 수요 조사 집계기</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr"/>
@@ -3376,7 +3374,7 @@
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
+          <t>가안 · 반별 수량을 모아 합계표로</t>
         </is>
       </c>
       <c r="L76" s="9" t="inlineStr"/>
@@ -3388,18 +3386,18 @@
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
+          <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr"/>
       <c r="E77" s="8" t="inlineStr"/>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 수행평가 채점 기준표(루브릭) 채점기</t>
+          <t>[Codex+구글 시트] 특별실·기자재 예약판</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr"/>
@@ -3416,7 +3414,7 @@
       </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강</t>
+          <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr"/>
@@ -3439,7 +3437,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 문항별 정답률 분석표</t>
+          <t>[Codex] 관찰 기록으로 단원 평어 초안 만들기</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr"/>
@@ -3456,7 +3454,7 @@
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
+          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr"/>
@@ -3479,10 +3477,90 @@
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" s="9" t="inlineStr">
         <is>
+          <t>[Codex] 수행평가 채점 기준표(루브릭) 채점기</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 평가·기록 보강</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr"/>
+      <c r="E80" s="8" t="inlineStr"/>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>[Codex] 문항별 정답률 분석표</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr"/>
+      <c r="E81" s="8" t="inlineStr"/>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
           <t>[Codex] 학교생활기록부/세부능력 및 특기사항 글자 수·표현 점검기</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>NEIS 기준 글자 수·바이트 계산, 항목별 제한 초과 표시
 기재 금지·유의 표현 형광펜 표시(목록은 교사가 수정)
@@ -3490,196 +3568,116 @@
 AI 문장 생성·윤문·외부 전송 없이 브라우저 안에서만 동작</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr"/>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="J79" s="8" t="inlineStr">
+      <c r="J81" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="K79" s="9" t="inlineStr">
+      <c r="K81" s="9" t="inlineStr">
         <is>
           <t>가안 · 평가·기록 보강 · 교육부 지침(AI는 보조만, AI 문장 그대로 기재 금지)에 맞춰 점검만 하고 수정은 교사가 결정</t>
         </is>
       </c>
-      <c r="L79" s="9" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+      <c r="L81" s="9" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B80" s="6" t="n">
+      <c r="B82" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr"/>
-      <c r="E80" s="6" t="inlineStr"/>
-      <c r="F80" s="7" t="inlineStr">
+      <c r="D82" s="7" t="inlineStr"/>
+      <c r="E82" s="6" t="inlineStr"/>
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>[Codex+구글 시트] 단원 끝 학생 자기평가 카드</t>
         </is>
       </c>
-      <c r="G80" s="7" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J80" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K80" s="7" t="inlineStr">
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
         <is>
           <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
         </is>
       </c>
-      <c r="L80" s="7" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="L82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B81" s="6" t="n">
+      <c r="B83" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="6" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr"/>
+      <c r="E83" s="6" t="inlineStr"/>
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>[Codex+Firebase] 방학 중 안부 체크인</t>
         </is>
       </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K81" s="7" t="inlineStr">
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-      <c r="L81" s="7" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B82" s="10" t="inlineStr"/>
-      <c r="C82" s="11" t="inlineStr"/>
-      <c r="D82" s="11" t="inlineStr"/>
-      <c r="E82" s="10" t="inlineStr"/>
-      <c r="F82" s="11" t="inlineStr">
-        <is>
-          <t>발표 모드</t>
-        </is>
-      </c>
-      <c r="G82" s="11" t="inlineStr"/>
-      <c r="H82" s="10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>강현수</t>
-        </is>
-      </c>
-      <c r="J82" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K82" s="11" t="inlineStr">
-        <is>
-          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
-        </is>
-      </c>
-      <c r="L82" s="11" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="inlineStr"/>
-      <c r="C83" s="11" t="inlineStr"/>
-      <c r="D83" s="11" t="inlineStr"/>
-      <c r="E83" s="10" t="inlineStr"/>
-      <c r="F83" s="11" t="inlineStr">
-        <is>
-          <t>기기대여대장</t>
-        </is>
-      </c>
-      <c r="G83" s="11" t="inlineStr"/>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>진정숙</t>
-        </is>
-      </c>
-      <c r="J83" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K83" s="11" t="inlineStr">
-        <is>
-          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
-        </is>
-      </c>
-      <c r="L83" s="11" t="inlineStr">
-        <is>
-          <t>‘학급 문고 대출 기록표’(가안) 대신 — 로그인·관리자 모드를 빼고 대여·반납 기록 한 가지 기능으로 줄이면</t>
-        </is>
-      </c>
+      <c r="L83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>업무자동화</t>
+          <t>수업자동화</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr"/>
@@ -3688,18 +3686,18 @@
       <c r="E84" s="10" t="inlineStr"/>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>스마트 시간표 교체</t>
+          <t>발표 모드</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
@@ -3709,14 +3707,10 @@
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
-        </is>
-      </c>
-      <c r="L84" s="11" t="inlineStr">
-        <is>
-          <t>‘전자칠판용 우리 반 일과 안내판’(가안) 대신 — 전교 시간표 대신 우리 반 시간표 변경만 안내하는 화면으로 줄이면</t>
-        </is>
-      </c>
+          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
+        </is>
+      </c>
+      <c r="L84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -3730,18 +3724,18 @@
       <c r="E85" s="10" t="inlineStr"/>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>준비물, 전달사항 알림장 사이트</t>
+          <t>기기대여대장</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>이지상</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="J85" s="10" t="inlineStr">
@@ -3751,12 +3745,12 @@
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
+          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
         </is>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>‘안내용 웹 가정통신문 만들기’(가안) 대신 — 회원가입·댓글·첨부를 빼고 전달사항·준비물을 한 화면에 올리는 안내 페이지로 줄이면</t>
+          <t>‘학급 문고 대출 기록표’(가안) 대신 — 로그인·관리자 모드를 빼고 대여·반납 기록 한 가지 기능으로 줄이면</t>
         </is>
       </c>
     </row>
@@ -3772,18 +3766,18 @@
       <c r="E86" s="10" t="inlineStr"/>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>키워드 레이더</t>
+          <t>스마트 시간표 교체</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="J86" s="10" t="inlineStr">
@@ -3793,10 +3787,14 @@
       </c>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
-        </is>
-      </c>
-      <c r="L86" s="11" t="inlineStr"/>
+          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
+        </is>
+      </c>
+      <c r="L86" s="11" t="inlineStr">
+        <is>
+          <t>‘전자칠판용 우리 반 일과 안내판’(가안) 대신 — 전교 시간표 대신 우리 반 시간표 변경만 안내하는 화면으로 줄이면</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
@@ -3810,18 +3808,18 @@
       <c r="E87" s="10" t="inlineStr"/>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>부장회의록 및 주간계획</t>
+          <t>준비물, 전달사항 알림장 사이트</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>이지상</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
@@ -3831,10 +3829,14 @@
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
-        </is>
-      </c>
-      <c r="L87" s="11" t="inlineStr"/>
+          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
+        </is>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>‘안내용 웹 가정통신문 만들기’(가안) 대신 — 회원가입·댓글·첨부를 빼고 전달사항·준비물을 한 화면에 올리는 안내 페이지로 줄이면</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -3848,18 +3850,18 @@
       <c r="E88" s="10" t="inlineStr"/>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>우리반 출석부</t>
+          <t>키워드 레이더</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr"/>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>이승엽</t>
         </is>
       </c>
       <c r="J88" s="10" t="inlineStr">
@@ -3869,7 +3871,7 @@
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
+          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr"/>
@@ -3886,18 +3888,18 @@
       <c r="E89" s="10" t="inlineStr"/>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>학부모 상담 기록요약</t>
+          <t>부장회의록 및 주간계획</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>이승엽</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr">
@@ -3907,14 +3909,10 @@
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
-        </is>
-      </c>
-      <c r="L89" s="11" t="inlineStr">
-        <is>
-          <t>‘상담 전 사전 질문지’(가안) 대신 — 외부 AI 없이 상담 메모를 항목별 칸에 나눠 정리하는 기록 양식으로 바꾸면</t>
-        </is>
-      </c>
+          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
+        </is>
+      </c>
+      <c r="L89" s="11" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -3928,63 +3926,115 @@
       <c r="E90" s="10" t="inlineStr"/>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>반 편성 조건 점검기</t>
+          <t>우리반 출석부</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
       <c r="H90" s="10" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K90" s="11" t="inlineStr">
+        <is>
+          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
+        </is>
+      </c>
+      <c r="L90" s="11" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr"/>
+      <c r="C91" s="11" t="inlineStr"/>
+      <c r="D91" s="11" t="inlineStr"/>
+      <c r="E91" s="10" t="inlineStr"/>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>학부모 상담 기록요약</t>
+        </is>
+      </c>
+      <c r="G91" s="11" t="inlineStr"/>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
+        </is>
+      </c>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>‘상담 전 사전 질문지’(가안) 대신 — 외부 AI 없이 상담 메모를 항목별 칸에 나눠 정리하는 기록 양식으로 바꾸면</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr"/>
+      <c r="C92" s="11" t="inlineStr"/>
+      <c r="D92" s="11" t="inlineStr"/>
+      <c r="E92" s="10" t="inlineStr"/>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>반 편성 조건 점검기</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="inlineStr"/>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I90" s="10" t="inlineStr">
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J90" s="10" t="inlineStr">
+      <c r="J92" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="K90" s="11" t="inlineStr">
+      <c r="K92" s="11" t="inlineStr">
         <is>
           <t>특수 배려·분리 요청 같은 민감 정보를 다루고 LLM API가 필요함. 제안자도 다음 회의에서 논의하기로 남겨 둠</t>
         </is>
       </c>
-      <c r="L90" s="11" t="inlineStr">
+      <c r="L92" s="11" t="inlineStr">
         <is>
           <t>‘모둠 자동 편성기’(가안) 대신 — AI 없이, 이름 대신 번호로 성비·분리 조건만 점검하는 방식으로 줄이면</t>
         </is>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="n"/>
-      <c r="B91" s="6" t="n"/>
-      <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
-      <c r="E91" s="6" t="n"/>
-      <c r="F91" s="7" t="n"/>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="6" t="n"/>
-      <c r="I91" s="6" t="n"/>
-      <c r="J91" s="6" t="n"/>
-      <c r="K91" s="7" t="n"/>
-      <c r="L91" s="7" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="7" t="n"/>
-      <c r="G92" s="7" t="n"/>
-      <c r="H92" s="6" t="n"/>
-      <c r="I92" s="6" t="n"/>
-      <c r="J92" s="6" t="n"/>
-      <c r="K92" s="7" t="n"/>
-      <c r="L92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -4238,6 +4288,34 @@
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
     </row>
+    <row r="111">
+      <c r="A111" s="6" t="n"/>
+      <c r="B111" s="6" t="n"/>
+      <c r="C111" s="7" t="n"/>
+      <c r="D111" s="7" t="n"/>
+      <c r="E111" s="6" t="n"/>
+      <c r="F111" s="7" t="n"/>
+      <c r="G111" s="7" t="n"/>
+      <c r="H111" s="6" t="n"/>
+      <c r="I111" s="6" t="n"/>
+      <c r="J111" s="6" t="n"/>
+      <c r="K111" s="7" t="n"/>
+      <c r="L111" s="7" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="n"/>
+      <c r="B112" s="6" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+      <c r="E112" s="6" t="n"/>
+      <c r="F112" s="7" t="n"/>
+      <c r="G112" s="7" t="n"/>
+      <c r="H112" s="6" t="n"/>
+      <c r="I112" s="6" t="n"/>
+      <c r="J112" s="6" t="n"/>
+      <c r="K112" s="7" t="n"/>
+      <c r="L112" s="7" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B4:L4"/>
@@ -4250,10 +4328,10 @@
     <mergeCell ref="B8:L8"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A13:A110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A13:A112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
-    <dataValidation sqref="J13:J110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J13:J112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -913,8 +913,8 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>ChatGPT 계정·요금제 확인과 Codex 시작하기
-Codex로 만든 HTML 파일을 브라우저에서 열어 미리 보기
+          <t>챗GPT 계정·요금제 확인과 코딩 기능 시작하기
+챗GPT로 만든 HTML 파일을 브라우저에서 열어 미리 보기
 구글 앱스 스크립트 편집기 열어 보기 (PART 4)
 OpenAI API 키 발급과 사용 비용 확인 (PART 4)</t>
         </is>
@@ -945,7 +945,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>사용 도구: ChatGPT의 Codex 활용</t>
+          <t>사용 도구: 챗GPT 활용</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>사용 도구: ChatGPT의 Codex 활용</t>
+          <t>사용 도구: 챗GPT 활용</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>사용 도구: ChatGPT의 Codex로 만들고, 구글 앱스 스크립트 또는 OpenAI API를 붙여서 실습</t>
+          <t>사용 도구: 챗GPT로 만들고, 구글 앱스 스크립트 또는 OpenAI API를 붙여서 실습</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr"/>
@@ -2427,8 +2427,8 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>ChatGPT 계정·요금제 확인과 Codex 시작하기
-Codex로 만든 HTML 파일을 브라우저에서 열어 미리 보기
+          <t>챗GPT 계정·요금제 확인과 코딩 기능 시작하기
+챗GPT로 만든 HTML 파일을 브라우저에서 열어 미리 보기
 구글 시트와 앱스 스크립트 연결해 보기
 Firebase 프로젝트 만들어 보기 (방학 중 안부 체크인)</t>
         </is>
@@ -2461,7 +2461,7 @@
       <c r="E54" s="6" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>[Codex] 진급 반 인계 카드</t>
+          <t>[챗GPT] 진급 반 인계 카드</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
@@ -2505,7 +2505,7 @@
       <c r="E55" s="6" t="inlineStr"/>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>[Codex] 조건을 반영한 자리 배치</t>
+          <t>[챗GPT] 조건을 반영한 자리 배치</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr"/>
@@ -2549,7 +2549,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 모둠 자동 편성기</t>
+          <t>[챗GPT] 모둠 자동 편성기</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr"/>
@@ -2589,7 +2589,7 @@
       <c r="E57" s="8" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 1인 1역 역할 배정표</t>
+          <t>[챗GPT] 1인 1역 역할 배정표</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr"/>
@@ -2629,7 +2629,7 @@
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 전자칠판용 우리 반 일과 안내판</t>
+          <t>[챗GPT] 전자칠판용 우리 반 일과 안내판</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr"/>
@@ -2669,7 +2669,7 @@
       <c r="E59" s="6" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>[Codex] 특별활동 자동 출석부</t>
+          <t>[챗GPT] 특별활동 자동 출석부</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr"/>
@@ -2713,7 +2713,7 @@
       <c r="E60" s="6" t="inlineStr"/>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>[Codex] 청소 구역 점검판</t>
+          <t>[챗GPT] 청소 구역 점검판</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr"/>
@@ -2753,7 +2753,7 @@
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 과제 제출 체크리스트</t>
+          <t>[챗GPT] 과제 제출 체크리스트</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
@@ -2793,7 +2793,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 칭찬 포인트 보드</t>
+          <t>[챗GPT] 칭찬 포인트 보드</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 학급 행사 D-day 게시판</t>
+          <t>[챗GPT] 학급 행사 D-day 게시판</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr"/>
@@ -2873,7 +2873,7 @@
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 학급 문고 대출 기록표</t>
+          <t>[챗GPT] 학급 문고 대출 기록표</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr"/>
@@ -2913,7 +2913,7 @@
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 학급 규칙 함께 정하기 투표판</t>
+          <t>[챗GPT+구글 시트] 학급 규칙 함께 정하기 투표판</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       <c r="E66" s="8" t="inlineStr"/>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 안내용 웹 가정통신문 만들기</t>
+          <t>[챗GPT] 안내용 웹 가정통신문 만들기</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr"/>
@@ -2993,7 +2993,7 @@
       <c r="E67" s="6" t="inlineStr"/>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 겹치지 않는 학부모 상담 예약</t>
+          <t>[챗GPT+구글 시트] 겹치지 않는 학부모 상담 예약</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
@@ -3033,7 +3033,7 @@
       <c r="E68" s="6" t="inlineStr"/>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 정원이 차면 자동 마감되는 신청서</t>
+          <t>[챗GPT+구글 시트] 정원이 차면 자동 마감되는 신청서</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr"/>
@@ -3077,7 +3077,7 @@
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
+          <t>[챗GPT+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr"/>
@@ -3117,7 +3117,7 @@
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 공개수업 참관 신청서</t>
+          <t>[챗GPT+구글 시트] 공개수업 참관 신청서</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
       <c r="E71" s="8" t="inlineStr"/>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 상담 전 사전 질문지</t>
+          <t>[챗GPT+구글 시트] 상담 전 사전 질문지</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr"/>
@@ -3197,7 +3197,7 @@
       <c r="E72" s="6" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>[Codex] 회신서 미제출자 확인기</t>
+          <t>[챗GPT] 회신서 미제출자 확인기</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
@@ -3237,7 +3237,7 @@
       <c r="E73" s="6" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>[Codex] 공문서 표기 점검기</t>
+          <t>[챗GPT] 공문서 표기 점검기</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
@@ -3277,7 +3277,7 @@
       <c r="E74" s="6" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] QR로 받는 교직원 연수 서명부</t>
+          <t>[챗GPT+구글 시트] QR로 받는 교직원 연수 서명부</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       <c r="E75" s="6" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 부서 통합 외부인 방문대장</t>
+          <t>[챗GPT+구글 시트] 부서 통합 외부인 방문대장</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
       <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 행사 물품 수요 조사 집계기</t>
+          <t>[챗GPT+구글 시트] 행사 물품 수요 조사 집계기</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr"/>
@@ -3397,7 +3397,7 @@
       <c r="E77" s="8" t="inlineStr"/>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 특별실·기자재 예약판</t>
+          <t>[챗GPT+구글 시트] 특별실·기자재 예약판</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr"/>
@@ -3437,7 +3437,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 관찰 기록으로 단원 평어 초안 만들기</t>
+          <t>[챗GPT] 관찰 기록으로 단원 평어 초안 만들기</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr"/>
@@ -3477,7 +3477,7 @@
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 수행평가 채점 기준표(루브릭) 채점기</t>
+          <t>[챗GPT] 수행평가 채점 기준표(루브릭) 채점기</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr"/>
@@ -3517,7 +3517,7 @@
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 문항별 정답률 분석표</t>
+          <t>[챗GPT] 문항별 정답률 분석표</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr"/>
@@ -3557,7 +3557,7 @@
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>[Codex] 학교생활기록부/세부능력 및 특기사항 글자 수·표현 점검기</t>
+          <t>[챗GPT] 학교생활기록부/세부능력 및 특기사항 글자 수·표현 점검기</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
@@ -3604,7 +3604,7 @@
       <c r="E82" s="6" t="inlineStr"/>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>[Codex+구글 시트] 단원 끝 학생 자기평가 카드</t>
+          <t>[챗GPT+구글 시트] 단원 끝 학생 자기평가 카드</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
@@ -3648,7 +3648,7 @@
       <c r="E83" s="6" t="inlineStr"/>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>[Codex+Firebase] 방학 중 안부 체크인</t>
+          <t>[챗GPT+Firebase] 방학 중 안부 체크인</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr"/>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2204,79 +2204,72 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>수업자동화</t>
+          <t>업무자동화</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr"/>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩 이론</t>
+        </is>
+      </c>
       <c r="E48" s="6" t="inlineStr"/>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (한국사) (통합교과)</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>진정숙</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr">
-        <is>
-          <t>심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
-        </is>
-      </c>
-      <c r="L48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩 이론</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
           <t>바이브 코딩이란?</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 개념 (패러다임의 변화)
 개발 과정 (요구분석-설계-구현-테스트-배포-운영)
 필수 용어 (예: 라이브러리, 빌드, 디버깅, 배포 등)</t>
         </is>
       </c>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트 기초</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트가 결과를 좌우한다 (bad vs good)
+마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
+        </is>
+      </c>
       <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr">
@@ -2305,23 +2298,30 @@
       <c r="E50" s="6" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>프롬프트 기초</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트가 결과를 좌우한다 (bad vs good)
-마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr"/>
+          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>수업 22</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>김형훈</t>
+        </is>
+      </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr"/>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
+        </is>
+      </c>
       <c r="L50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2342,30 +2342,22 @@
       <c r="E51" s="6" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>수업 22</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
+          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>사례</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
       <c r="J51" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="K51" s="7" t="inlineStr"/>
       <c r="L51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2386,46 +2378,10 @@
       <c r="E52" s="6" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+          <t>실습 도구 준비하기: 설치하고 미리 보기</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>사례</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr"/>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr"/>
-      <c r="E53" s="6" t="inlineStr"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>실습 도구 준비하기: 설치하고 미리 보기</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>챗GPT 계정·요금제 확인과 코딩 기능 시작하기
 챗GPT로 만든 HTML 파일을 브라우저에서 열어 미리 보기
@@ -2433,14 +2389,58 @@
 Firebase 프로젝트 만들어 보기 (방학 중 안부 체크인)</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT] 진급 반 인계 카드</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
       <c r="L53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2461,13 +2461,13 @@
       <c r="E54" s="6" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT] 진급 반 인계 카드</t>
+          <t>[챗GPT] 조건을 반영한 자리 배치</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
@@ -2482,54 +2482,50 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>2월</t>
+          <t>3월</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr"/>
-      <c r="E55" s="6" t="inlineStr"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT] 조건을 반영한 자리 배치</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
-        <is>
-          <t>3월</t>
-        </is>
-      </c>
-      <c r="L55" s="7" t="inlineStr"/>
+      <c r="D55" s="9" t="inlineStr"/>
+      <c r="E55" s="8" t="inlineStr"/>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT] 모둠 자동 편성기</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -2549,7 +2545,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 모둠 자동 편성기</t>
+          <t>[챗GPT] 1인 1역 역할 배정표</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr"/>
@@ -2566,7 +2562,7 @@
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
+          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr"/>
@@ -2589,7 +2585,7 @@
       <c r="E57" s="8" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 1인 1역 역할 배정표</t>
+          <t>[챗GPT] 전자칠판용 우리 반 일과 안내판</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr"/>
@@ -2606,50 +2602,54 @@
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
+          <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B58" s="8" t="n">
+      <c r="B58" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr"/>
-      <c r="E58" s="8" t="inlineStr"/>
-      <c r="F58" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT] 전자칠판용 우리 반 일과 안내판</t>
-        </is>
-      </c>
-      <c r="G58" s="9" t="inlineStr"/>
-      <c r="H58" s="8" t="inlineStr"/>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J58" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K58" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
-        </is>
-      </c>
-      <c r="L58" s="9" t="inlineStr"/>
+      <c r="D58" s="7" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT] 특별활동 자동 출석부</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -2669,18 +2669,18 @@
       <c r="E59" s="6" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT] 특별활동 자동 출석부</t>
+          <t>[챗GPT] 청소 구역 점검판</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr"/>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
@@ -2688,52 +2688,48 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K59" s="7" t="inlineStr">
-        <is>
-          <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
-        </is>
-      </c>
+      <c r="K59" s="7" t="inlineStr"/>
       <c r="L59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr"/>
-      <c r="E60" s="6" t="inlineStr"/>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT] 청소 구역 점검판</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="inlineStr"/>
+      <c r="D60" s="9" t="inlineStr"/>
+      <c r="E60" s="8" t="inlineStr"/>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT] 과제 제출 체크리스트</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -2753,7 +2749,7 @@
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 과제 제출 체크리스트</t>
+          <t>[챗GPT] 칭찬 포인트 보드</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
@@ -2770,7 +2766,7 @@
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
+          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr"/>
@@ -2793,7 +2789,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 칭찬 포인트 보드</t>
+          <t>[챗GPT] 학급 행사 D-day 게시판</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr"/>
@@ -2810,7 +2806,7 @@
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
+          <t>가안</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr"/>
@@ -2833,7 +2829,7 @@
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 학급 행사 D-day 게시판</t>
+          <t>[챗GPT] 학급 문고 대출 기록표</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr"/>
@@ -2873,7 +2869,7 @@
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 학급 문고 대출 기록표</t>
+          <t>[챗GPT+구글 시트] 학급 규칙 함께 정하기 투표판</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr"/>
@@ -2890,7 +2886,7 @@
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>가안</t>
+          <t>가안 · 3월 학급 세우기 활동</t>
         </is>
       </c>
       <c r="L64" s="9" t="inlineStr"/>
@@ -2902,18 +2898,18 @@
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr"/>
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 학급 규칙 함께 정하기 투표판</t>
+          <t>[챗GPT] 안내용 웹 가정통신문 만들기</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr"/>
@@ -2930,50 +2926,50 @@
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>가안 · 3월 학급 세우기 활동</t>
+          <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B66" s="8" t="n">
+      <c r="B66" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr"/>
-      <c r="E66" s="8" t="inlineStr"/>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT] 안내용 웹 가정통신문 만들기</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="8" t="inlineStr"/>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J66" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K66" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
-        </is>
-      </c>
-      <c r="L66" s="9" t="inlineStr"/>
+      <c r="D66" s="7" t="inlineStr"/>
+      <c r="E66" s="6" t="inlineStr"/>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 겹치지 않는 학부모 상담 예약</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr"/>
+      <c r="L66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -2993,13 +2989,13 @@
       <c r="E67" s="6" t="inlineStr"/>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 겹치지 않는 학부모 상담 예약</t>
+          <t>[챗GPT+구글 시트] 정원이 차면 자동 마감되는 신청서</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
@@ -3012,52 +3008,52 @@
           <t>초안</t>
         </is>
       </c>
-      <c r="K67" s="7" t="inlineStr"/>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>방과후학교·학부모 연수</t>
+        </is>
+      </c>
       <c r="L67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B68" s="6" t="n">
+      <c r="B68" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr"/>
-      <c r="E68" s="6" t="inlineStr"/>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 정원이 차면 자동 마감되는 신청서</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>임부현</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
-        <is>
-          <t>방과후학교·학부모 연수</t>
-        </is>
-      </c>
-      <c r="L68" s="7" t="inlineStr"/>
+      <c r="D68" s="9" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr"/>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 구글 시트로 응답 수합</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -3077,7 +3073,7 @@
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
+          <t>[챗GPT+구글 시트] 공개수업 참관 신청서</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr"/>
@@ -3094,7 +3090,7 @@
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>가안 · 구글 시트로 응답 수합</t>
+          <t>가안 · 시간대별 정원 표시</t>
         </is>
       </c>
       <c r="L69" s="9" t="inlineStr"/>
@@ -3117,7 +3113,7 @@
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 공개수업 참관 신청서</t>
+          <t>[챗GPT+구글 시트] 상담 전 사전 질문지</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr"/>
@@ -3134,50 +3130,50 @@
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
-          <t>가안 · 시간대별 정원 표시</t>
+          <t>가안 · 상담 예약(4-1)과 이어지는 실습</t>
         </is>
       </c>
       <c r="L70" s="9" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="8" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B71" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr"/>
-      <c r="E71" s="8" t="inlineStr"/>
-      <c r="F71" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 상담 전 사전 질문지</t>
-        </is>
-      </c>
-      <c r="G71" s="9" t="inlineStr"/>
-      <c r="H71" s="8" t="inlineStr"/>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J71" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K71" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 상담 예약(4-1)과 이어지는 실습</t>
-        </is>
-      </c>
-      <c r="L71" s="9" t="inlineStr"/>
+      <c r="B71" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>행정 업무: 서류와 수합 줄이기</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr"/>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT] 회신서 미제출자 확인기</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr"/>
+      <c r="L71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -3197,13 +3193,13 @@
       <c r="E72" s="6" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT] 회신서 미제출자 확인기</t>
+          <t>[챗GPT] 공문서 표기 점검기</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
@@ -3237,18 +3233,18 @@
       <c r="E73" s="6" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT] 공문서 표기 점검기</t>
+          <t>[챗GPT+구글 시트] QR로 받는 교직원 연수 서명부</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>석희철</t>
+          <t>이승엽</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
@@ -3277,13 +3273,13 @@
       <c r="E74" s="6" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] QR로 받는 교직원 연수 서명부</t>
+          <t>[챗GPT+구글 시트] 부서 통합 외부인 방문대장</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
@@ -3300,44 +3296,44 @@
       <c r="L74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B75" s="6" t="n">
+      <c r="B75" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C75" s="7" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr"/>
-      <c r="E75" s="6" t="inlineStr"/>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 부서 통합 외부인 방문대장</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>이승엽</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K75" s="7" t="inlineStr"/>
-      <c r="L75" s="7" t="inlineStr"/>
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="8" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 행사 물품 수요 조사 집계기</t>
+        </is>
+      </c>
+      <c r="G75" s="9" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr"/>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J75" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 반별 수량을 모아 합계표로</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -3357,7 +3353,7 @@
       <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 행사 물품 수요 조사 집계기</t>
+          <t>[챗GPT+구글 시트] 특별실·기자재 예약판</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr"/>
@@ -3374,7 +3370,7 @@
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>가안 · 반별 수량을 모아 합계표로</t>
+          <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
         </is>
       </c>
       <c r="L76" s="9" t="inlineStr"/>
@@ -3386,18 +3382,18 @@
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr"/>
       <c r="E77" s="8" t="inlineStr"/>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 특별실·기자재 예약판</t>
+          <t>[챗GPT] 관찰 기록으로 단원 평어 초안 만들기</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr"/>
@@ -3414,7 +3410,7 @@
       </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
+          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr"/>
@@ -3437,7 +3433,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 관찰 기록으로 단원 평어 초안 만들기</t>
+          <t>[챗GPT] 수행평가 채점 기준표(루브릭) 채점기</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr"/>
@@ -3454,7 +3450,7 @@
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
+          <t>가안 · 평가·기록 보강</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr"/>
@@ -3477,7 +3473,7 @@
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 수행평가 채점 기준표(루브릭) 채점기</t>
+          <t>[챗GPT] 문항별 정답률 분석표</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr"/>
@@ -3494,7 +3490,7 @@
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강</t>
+          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr"/>
@@ -3517,50 +3513,10 @@
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 문항별 정답률 분석표</t>
-        </is>
-      </c>
-      <c r="G80" s="9" t="inlineStr"/>
-      <c r="H80" s="8" t="inlineStr"/>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J80" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K80" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
-        </is>
-      </c>
-      <c r="L80" s="9" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr"/>
-      <c r="E81" s="8" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
           <t>[챗GPT] 학교생활기록부/세부능력 및 특기사항 글자 수·표현 점검기</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="G80" s="9" t="inlineStr">
         <is>
           <t>NEIS 기준 글자 수·바이트 계산, 항목별 제한 초과 표시
 기재 금지·유의 표현 형광펜 표시(목록은 교사가 수정)
@@ -3568,23 +3524,67 @@
 AI 문장 생성·윤문·외부 전송 없이 브라우저 안에서만 동작</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="J81" s="8" t="inlineStr">
+      <c r="J80" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="K80" s="9" t="inlineStr">
         <is>
           <t>가안 · 평가·기록 보강 · 교육부 지침(AI는 보조만, AI 문장 그대로 기재 금지)에 맞춰 점검만 하고 수정은 교사가 결정</t>
         </is>
       </c>
-      <c r="L81" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr"/>
+      <c r="E81" s="6" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 단원 끝 학생 자기평가 카드</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -3604,13 +3604,13 @@
       <c r="E82" s="6" t="inlineStr"/>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 단원 끝 학생 자기평가 카드</t>
+          <t>[챗GPT+Firebase] 방학 중 안부 체크인</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -3625,59 +3625,53 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
+          <t>7월</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B83" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr"/>
-      <c r="E83" s="6" t="inlineStr"/>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT+Firebase] 방학 중 안부 체크인</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
-        <is>
-          <t>7월</t>
-        </is>
-      </c>
-      <c r="L83" s="7" t="inlineStr"/>
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>수업자동화</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr"/>
+      <c r="C83" s="11" t="inlineStr"/>
+      <c r="D83" s="11" t="inlineStr"/>
+      <c r="E83" s="10" t="inlineStr"/>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>발표 모드</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr"/>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>강현수</t>
+        </is>
+      </c>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr">
+        <is>
+          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>수업자동화</t>
+          <t>업무자동화</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr"/>
@@ -3686,18 +3680,18 @@
       <c r="E84" s="10" t="inlineStr"/>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>발표 모드</t>
+          <t>기기대여대장</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>강현수</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
@@ -3707,10 +3701,14 @@
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
-        </is>
-      </c>
-      <c r="L84" s="11" t="inlineStr"/>
+          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
+        </is>
+      </c>
+      <c r="L84" s="11" t="inlineStr">
+        <is>
+          <t>‘학급 문고 대출 기록표’(가안) 대신 — 로그인·관리자 모드를 빼고 대여·반납 기록 한 가지 기능으로 줄이면</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -3724,13 +3722,13 @@
       <c r="E85" s="10" t="inlineStr"/>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>기기대여대장</t>
+          <t>스마트 시간표 교체</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -3745,12 +3743,12 @@
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
+          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
         </is>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>‘학급 문고 대출 기록표’(가안) 대신 — 로그인·관리자 모드를 빼고 대여·반납 기록 한 가지 기능으로 줄이면</t>
+          <t>‘전자칠판용 우리 반 일과 안내판’(가안) 대신 — 전교 시간표 대신 우리 반 시간표 변경만 안내하는 화면으로 줄이면</t>
         </is>
       </c>
     </row>
@@ -3766,18 +3764,18 @@
       <c r="E86" s="10" t="inlineStr"/>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>스마트 시간표 교체</t>
+          <t>준비물, 전달사항 알림장 사이트</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>이지상</t>
         </is>
       </c>
       <c r="J86" s="10" t="inlineStr">
@@ -3787,12 +3785,12 @@
       </c>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
+          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
         </is>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>‘전자칠판용 우리 반 일과 안내판’(가안) 대신 — 전교 시간표 대신 우리 반 시간표 변경만 안내하는 화면으로 줄이면</t>
+          <t>‘안내용 웹 가정통신문 만들기’(가안) 대신 — 회원가입·댓글·첨부를 빼고 전달사항·준비물을 한 화면에 올리는 안내 페이지로 줄이면</t>
         </is>
       </c>
     </row>
@@ -3808,18 +3806,18 @@
       <c r="E87" s="10" t="inlineStr"/>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>준비물, 전달사항 알림장 사이트</t>
+          <t>키워드 레이더</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>이지상</t>
+          <t>이승엽</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
@@ -3829,14 +3827,10 @@
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
-        </is>
-      </c>
-      <c r="L87" s="11" t="inlineStr">
-        <is>
-          <t>‘안내용 웹 가정통신문 만들기’(가안) 대신 — 회원가입·댓글·첨부를 빼고 전달사항·준비물을 한 화면에 올리는 안내 페이지로 줄이면</t>
-        </is>
-      </c>
+          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
+        </is>
+      </c>
+      <c r="L87" s="11" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -3850,13 +3844,13 @@
       <c r="E88" s="10" t="inlineStr"/>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>키워드 레이더</t>
+          <t>부장회의록 및 주간계획</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr"/>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -3871,7 +3865,7 @@
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
+          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr"/>
@@ -3888,18 +3882,18 @@
       <c r="E89" s="10" t="inlineStr"/>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>부장회의록 및 주간계획</t>
+          <t>우리반 출석부</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr">
@@ -3909,7 +3903,7 @@
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
+          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
         </is>
       </c>
       <c r="L89" s="11" t="inlineStr"/>
@@ -3926,18 +3920,18 @@
       <c r="E90" s="10" t="inlineStr"/>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>우리반 출석부</t>
+          <t>학부모 상담 기록요약</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>임부현</t>
         </is>
       </c>
       <c r="J90" s="10" t="inlineStr">
@@ -3947,10 +3941,14 @@
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
-        </is>
-      </c>
-      <c r="L90" s="11" t="inlineStr"/>
+          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
+        </is>
+      </c>
+      <c r="L90" s="11" t="inlineStr">
+        <is>
+          <t>‘상담 전 사전 질문지’(가안) 대신 — 외부 AI 없이 상담 메모를 항목별 칸에 나눠 정리하는 기록 양식으로 바꾸면</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -3964,18 +3962,18 @@
       <c r="E91" s="10" t="inlineStr"/>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>학부모 상담 기록요약</t>
+          <t>반 편성 조건 점검기</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J91" s="10" t="inlineStr">
@@ -3985,56 +3983,28 @@
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
+          <t>특수 배려·분리 요청 같은 민감 정보를 다루고 LLM API가 필요함. 제안자도 다음 회의에서 논의하기로 남겨 둠</t>
         </is>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>‘상담 전 사전 질문지’(가안) 대신 — 외부 AI 없이 상담 메모를 항목별 칸에 나눠 정리하는 기록 양식으로 바꾸면</t>
+          <t>‘모둠 자동 편성기’(가안) 대신 — AI 없이, 이름 대신 번호로 성비·분리 조건만 점검하는 방식으로 줄이면</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="inlineStr"/>
-      <c r="C92" s="11" t="inlineStr"/>
-      <c r="D92" s="11" t="inlineStr"/>
-      <c r="E92" s="10" t="inlineStr"/>
-      <c r="F92" s="11" t="inlineStr">
-        <is>
-          <t>반 편성 조건 점검기</t>
-        </is>
-      </c>
-      <c r="G92" s="11" t="inlineStr"/>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I92" s="10" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J92" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K92" s="11" t="inlineStr">
-        <is>
-          <t>특수 배려·분리 요청 같은 민감 정보를 다루고 LLM API가 필요함. 제안자도 다음 회의에서 논의하기로 남겨 둠</t>
-        </is>
-      </c>
-      <c r="L92" s="11" t="inlineStr">
-        <is>
-          <t>‘모둠 자동 편성기’(가안) 대신 — AI 없이, 이름 대신 번호로 성비·분리 조건만 점검하는 방식으로 줄이면</t>
-        </is>
-      </c>
+      <c r="A92" s="6" t="n"/>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="7" t="n"/>
+      <c r="D92" s="7" t="n"/>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="7" t="n"/>
+      <c r="G92" s="7" t="n"/>
+      <c r="H92" s="6" t="n"/>
+      <c r="I92" s="6" t="n"/>
+      <c r="J92" s="6" t="n"/>
+      <c r="K92" s="7" t="n"/>
+      <c r="L92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -4302,20 +4272,6 @@
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
     </row>
-    <row r="112">
-      <c r="A112" s="6" t="n"/>
-      <c r="B112" s="6" t="n"/>
-      <c r="C112" s="7" t="n"/>
-      <c r="D112" s="7" t="n"/>
-      <c r="E112" s="6" t="n"/>
-      <c r="F112" s="7" t="n"/>
-      <c r="G112" s="7" t="n"/>
-      <c r="H112" s="6" t="n"/>
-      <c r="I112" s="6" t="n"/>
-      <c r="J112" s="6" t="n"/>
-      <c r="K112" s="7" t="n"/>
-      <c r="L112" s="7" t="n"/>
-    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B4:L4"/>
@@ -4328,10 +4284,10 @@
     <mergeCell ref="B8:L8"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A13:A112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A13:A111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
-    <dataValidation sqref="J13:J112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J13:J111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2204,72 +2204,79 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>업무자동화</t>
+          <t>수업자동화</t>
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩 이론</t>
-        </is>
-      </c>
+          <t>과목별 심화: AI와 시뮬레이션으로 교과 앱 키우기</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr"/>
       <c r="E48" s="6" t="inlineStr"/>
       <c r="F48" s="7" t="inlineStr">
         <is>
+          <t>[정보] 개념 허들 레이스 게임 (국어) (영어) (한국사) (통합교과)</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩 이론</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
           <t>바이브 코딩이란?</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 개념 (패러다임의 변화)
 개발 과정 (요구분석-설계-구현-테스트-배포-운영)
 필수 용어 (예: 라이브러리, 빌드, 디버깅, 배포 등)</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
-      <c r="I48" s="6" t="inlineStr"/>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K48" s="7" t="inlineStr"/>
-      <c r="L48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr"/>
-      <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트가 결과를 좌우한다 (bad vs good)
-마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
-        </is>
-      </c>
       <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr">
@@ -2298,30 +2305,23 @@
       <c r="E50" s="6" t="inlineStr"/>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>수업 22</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
+          <t>프롬프트 기초</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트가 결과를 좌우한다 (bad vs good)
+마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K50" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="K50" s="7" t="inlineStr"/>
       <c r="L50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2342,22 +2342,30 @@
       <c r="E51" s="6" t="inlineStr"/>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>사례</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr"/>
-      <c r="I51" s="6" t="inlineStr"/>
+          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>수업 22</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>김형훈</t>
+        </is>
+      </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
+        </is>
+      </c>
       <c r="L51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2378,10 +2386,46 @@
       <c r="E52" s="6" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
+          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>사례</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr"/>
+      <c r="I52" s="6" t="inlineStr"/>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
           <t>실습 도구 준비하기: 설치하고 미리 보기</t>
         </is>
       </c>
-      <c r="G52" s="7" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>챗GPT 계정·요금제 확인과 코딩 기능 시작하기
 챗GPT로 만든 HTML 파일을 브라우저에서 열어 미리 보기
@@ -2389,58 +2433,14 @@
 Firebase 프로젝트 만들어 보기 (방학 중 안부 체크인)</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr"/>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr"/>
-      <c r="E53" s="6" t="inlineStr"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT] 진급 반 인계 카드</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
+      <c r="H53" s="6" t="inlineStr"/>
+      <c r="I53" s="6" t="inlineStr"/>
       <c r="J53" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>2월</t>
-        </is>
-      </c>
+      <c r="K53" s="7" t="inlineStr"/>
       <c r="L53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2461,71 +2461,75 @@
       <c r="E54" s="6" t="inlineStr"/>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT] 조건을 반영한 자리 배치</t>
+          <t>[챗GPT] 진급 반 인계 카드</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
       <c r="H54" s="6" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>2월</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT] 조건을 반영한 자리 배치</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I55" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-      <c r="L54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr"/>
-      <c r="E55" s="8" t="inlineStr"/>
-      <c r="F55" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT] 모둠 자동 편성기</t>
-        </is>
-      </c>
-      <c r="G55" s="9" t="inlineStr"/>
-      <c r="H55" s="8" t="inlineStr"/>
-      <c r="I55" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J55" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
-        </is>
-      </c>
-      <c r="L55" s="9" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -2545,7 +2549,7 @@
       <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 1인 1역 역할 배정표</t>
+          <t>[챗GPT] 모둠 자동 편성기</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr"/>
@@ -2562,7 +2566,7 @@
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
+          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr"/>
@@ -2585,7 +2589,7 @@
       <c r="E57" s="8" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 전자칠판용 우리 반 일과 안내판</t>
+          <t>[챗GPT] 1인 1역 역할 배정표</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr"/>
@@ -2602,54 +2606,50 @@
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
+          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr"/>
+      <c r="E58" s="8" t="inlineStr"/>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT] 전자칠판용 우리 반 일과 안내판</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
           <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
         </is>
       </c>
-      <c r="L57" s="9" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr"/>
-      <c r="E58" s="6" t="inlineStr"/>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT] 특별활동 자동 출석부</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>진정숙</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K58" s="7" t="inlineStr">
-        <is>
-          <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
-        </is>
-      </c>
-      <c r="L58" s="7" t="inlineStr"/>
+      <c r="L58" s="9" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -2669,67 +2669,71 @@
       <c r="E59" s="6" t="inlineStr"/>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT] 청소 구역 점검판</t>
+          <t>[챗GPT] 특별활동 자동 출석부</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr"/>
       <c r="H59" s="6" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr"/>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT] 청소 구역 점검판</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr"/>
-      <c r="L59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B60" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C60" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="inlineStr"/>
-      <c r="E60" s="8" t="inlineStr"/>
-      <c r="F60" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT] 과제 제출 체크리스트</t>
-        </is>
-      </c>
-      <c r="G60" s="9" t="inlineStr"/>
-      <c r="H60" s="8" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J60" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
-        </is>
-      </c>
-      <c r="L60" s="9" t="inlineStr"/>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr"/>
+      <c r="L60" s="7" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -2749,7 +2753,7 @@
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 칭찬 포인트 보드</t>
+          <t>[챗GPT] 과제 제출 체크리스트</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
+          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr"/>
@@ -2789,7 +2793,7 @@
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 학급 행사 D-day 게시판</t>
+          <t>[챗GPT] 칭찬 포인트 보드</t>
         </is>
       </c>
       <c r="G62" s="9" t="inlineStr"/>
@@ -2806,7 +2810,7 @@
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
-          <t>가안</t>
+          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
         </is>
       </c>
       <c r="L62" s="9" t="inlineStr"/>
@@ -2829,7 +2833,7 @@
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 학급 문고 대출 기록표</t>
+          <t>[챗GPT] 학급 행사 D-day 게시판</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr"/>
@@ -2869,7 +2873,7 @@
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 학급 규칙 함께 정하기 투표판</t>
+          <t>[챗GPT] 학급 문고 대출 기록표</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr"/>
@@ -2886,7 +2890,7 @@
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>가안 · 3월 학급 세우기 활동</t>
+          <t>가안</t>
         </is>
       </c>
       <c r="L64" s="9" t="inlineStr"/>
@@ -2898,18 +2902,18 @@
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr"/>
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 안내용 웹 가정통신문 만들기</t>
+          <t>[챗GPT+구글 시트] 학급 규칙 함께 정하기 투표판</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr"/>
@@ -2926,50 +2930,50 @@
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
+          <t>가안 · 3월 학급 세우기 활동</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr"/>
+      <c r="E66" s="8" t="inlineStr"/>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT] 안내용 웹 가정통신문 만들기</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
           <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
         </is>
       </c>
-      <c r="L65" s="9" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr"/>
-      <c r="E66" s="6" t="inlineStr"/>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 겹치지 않는 학부모 상담 예약</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>임부현</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K66" s="7" t="inlineStr"/>
-      <c r="L66" s="7" t="inlineStr"/>
+      <c r="L66" s="9" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -2989,71 +2993,71 @@
       <c r="E67" s="6" t="inlineStr"/>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 정원이 차면 자동 마감되는 신청서</t>
+          <t>[챗GPT+구글 시트] 겹치지 않는 학부모 상담 예약</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 정원이 차면 자동 마감되는 신청서</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K67" s="7" t="inlineStr">
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
         <is>
           <t>방과후학교·학부모 연수</t>
         </is>
       </c>
-      <c r="L67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr"/>
-      <c r="E68" s="8" t="inlineStr"/>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
-        </is>
-      </c>
-      <c r="G68" s="9" t="inlineStr"/>
-      <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J68" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 구글 시트로 응답 수합</t>
-        </is>
-      </c>
-      <c r="L68" s="9" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -3073,7 +3077,7 @@
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 공개수업 참관 신청서</t>
+          <t>[챗GPT+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr"/>
@@ -3090,7 +3094,7 @@
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>가안 · 시간대별 정원 표시</t>
+          <t>가안 · 구글 시트로 응답 수합</t>
         </is>
       </c>
       <c r="L69" s="9" t="inlineStr"/>
@@ -3113,7 +3117,7 @@
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 상담 전 사전 질문지</t>
+          <t>[챗GPT+구글 시트] 공개수업 참관 신청서</t>
         </is>
       </c>
       <c r="G70" s="9" t="inlineStr"/>
@@ -3130,50 +3134,50 @@
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
+          <t>가안 · 시간대별 정원 표시</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 상담 전 사전 질문지</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
           <t>가안 · 상담 예약(4-1)과 이어지는 실습</t>
         </is>
       </c>
-      <c r="L70" s="9" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="6" t="inlineStr"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT] 회신서 미제출자 확인기</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr"/>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K71" s="7" t="inlineStr"/>
-      <c r="L71" s="7" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -3193,13 +3197,13 @@
       <c r="E72" s="6" t="inlineStr"/>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT] 공문서 표기 점검기</t>
+          <t>[챗GPT] 회신서 미제출자 확인기</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
@@ -3233,18 +3237,18 @@
       <c r="E73" s="6" t="inlineStr"/>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] QR로 받는 교직원 연수 서명부</t>
+          <t>[챗GPT] 공문서 표기 점검기</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
@@ -3273,13 +3277,13 @@
       <c r="E74" s="6" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 부서 통합 외부인 방문대장</t>
+          <t>[챗GPT+구글 시트] QR로 받는 교직원 연수 서명부</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
@@ -3296,44 +3300,44 @@
       <c r="L74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B75" s="8" t="n">
+      <c r="B75" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr"/>
-      <c r="E75" s="8" t="inlineStr"/>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 행사 물품 수요 조사 집계기</t>
-        </is>
-      </c>
-      <c r="G75" s="9" t="inlineStr"/>
-      <c r="H75" s="8" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J75" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K75" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 반별 수량을 모아 합계표로</t>
-        </is>
-      </c>
-      <c r="L75" s="9" t="inlineStr"/>
+      <c r="D75" s="7" t="inlineStr"/>
+      <c r="E75" s="6" t="inlineStr"/>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 부서 통합 외부인 방문대장</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -3353,7 +3357,7 @@
       <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 특별실·기자재 예약판</t>
+          <t>[챗GPT+구글 시트] 행사 물품 수요 조사 집계기</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr"/>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
+          <t>가안 · 반별 수량을 모아 합계표로</t>
         </is>
       </c>
       <c r="L76" s="9" t="inlineStr"/>
@@ -3382,18 +3386,18 @@
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
+          <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr"/>
       <c r="E77" s="8" t="inlineStr"/>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 관찰 기록으로 단원 평어 초안 만들기</t>
+          <t>[챗GPT+구글 시트] 특별실·기자재 예약판</t>
         </is>
       </c>
       <c r="G77" s="9" t="inlineStr"/>
@@ -3410,7 +3414,7 @@
       </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
+          <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr"/>
@@ -3433,7 +3437,7 @@
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 수행평가 채점 기준표(루브릭) 채점기</t>
+          <t>[챗GPT] 관찰 기록으로 단원 평어 초안 만들기</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr"/>
@@ -3450,7 +3454,7 @@
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강</t>
+          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr"/>
@@ -3473,7 +3477,7 @@
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 문항별 정답률 분석표</t>
+          <t>[챗GPT] 수행평가 채점 기준표(루브릭) 채점기</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr"/>
@@ -3490,7 +3494,7 @@
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
+          <t>가안 · 평가·기록 보강</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr"/>
@@ -3513,10 +3517,50 @@
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="9" t="inlineStr">
         <is>
+          <t>[챗GPT] 문항별 정답률 분석표</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr"/>
+      <c r="E81" s="8" t="inlineStr"/>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
           <t>[챗GPT] 학교생활기록부/세부능력 및 특기사항 글자 수·표현 점검기</t>
         </is>
       </c>
-      <c r="G80" s="9" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>NEIS 기준 글자 수·바이트 계산, 항목별 제한 초과 표시
 기재 금지·유의 표현 형광펜 표시(목록은 교사가 수정)
@@ -3524,67 +3568,23 @@
 AI 문장 생성·윤문·외부 전송 없이 브라우저 안에서만 동작</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr"/>
-      <c r="I80" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="J80" s="8" t="inlineStr">
+      <c r="J81" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K81" s="9" t="inlineStr">
         <is>
           <t>가안 · 평가·기록 보강 · 교육부 지침(AI는 보조만, AI 문장 그대로 기재 금지)에 맞춰 점검만 하고 수정은 교사가 결정</t>
         </is>
       </c>
-      <c r="L80" s="9" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B81" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="inlineStr"/>
-      <c r="E81" s="6" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 단원 끝 학생 자기평가 카드</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K81" s="7" t="inlineStr">
-        <is>
-          <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
-        </is>
-      </c>
-      <c r="L81" s="7" t="inlineStr"/>
+      <c r="L81" s="9" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -3604,74 +3604,80 @@
       <c r="E82" s="6" t="inlineStr"/>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT+Firebase] 방학 중 안부 체크인</t>
+          <t>[챗GPT+구글 시트] 단원 끝 학생 자기평가 카드</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>석희철</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
+        </is>
+      </c>
+      <c r="L82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr"/>
+      <c r="E83" s="6" t="inlineStr"/>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT+Firebase] 방학 중 안부 체크인</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J82" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K82" s="7" t="inlineStr">
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-      <c r="L82" s="7" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="inlineStr"/>
-      <c r="C83" s="11" t="inlineStr"/>
-      <c r="D83" s="11" t="inlineStr"/>
-      <c r="E83" s="10" t="inlineStr"/>
-      <c r="F83" s="11" t="inlineStr">
-        <is>
-          <t>발표 모드</t>
-        </is>
-      </c>
-      <c r="G83" s="11" t="inlineStr"/>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I83" s="10" t="inlineStr">
-        <is>
-          <t>강현수</t>
-        </is>
-      </c>
-      <c r="J83" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K83" s="11" t="inlineStr">
-        <is>
-          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
-        </is>
-      </c>
-      <c r="L83" s="11" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>업무자동화</t>
+          <t>수업자동화</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr"/>
@@ -3680,18 +3686,18 @@
       <c r="E84" s="10" t="inlineStr"/>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>기기대여대장</t>
+          <t>발표 모드</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr"/>
       <c r="H84" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="J84" s="10" t="inlineStr">
@@ -3701,14 +3707,10 @@
       </c>
       <c r="K84" s="11" t="inlineStr">
         <is>
-          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
-        </is>
-      </c>
-      <c r="L84" s="11" t="inlineStr">
-        <is>
-          <t>‘학급 문고 대출 기록표’(가안) 대신 — 로그인·관리자 모드를 빼고 대여·반납 기록 한 가지 기능으로 줄이면</t>
-        </is>
-      </c>
+          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
+        </is>
+      </c>
+      <c r="L84" s="11" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -3722,13 +3724,13 @@
       <c r="E85" s="10" t="inlineStr"/>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>스마트 시간표 교체</t>
+          <t>기기대여대장</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr"/>
       <c r="H85" s="10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr">
@@ -3743,12 +3745,12 @@
       </c>
       <c r="K85" s="11" t="inlineStr">
         <is>
-          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
+          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
         </is>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>‘전자칠판용 우리 반 일과 안내판’(가안) 대신 — 전교 시간표 대신 우리 반 시간표 변경만 안내하는 화면으로 줄이면</t>
+          <t>‘학급 문고 대출 기록표’(가안) 대신 — 로그인·관리자 모드를 빼고 대여·반납 기록 한 가지 기능으로 줄이면</t>
         </is>
       </c>
     </row>
@@ -3764,18 +3766,18 @@
       <c r="E86" s="10" t="inlineStr"/>
       <c r="F86" s="11" t="inlineStr">
         <is>
-          <t>준비물, 전달사항 알림장 사이트</t>
+          <t>스마트 시간표 교체</t>
         </is>
       </c>
       <c r="G86" s="11" t="inlineStr"/>
       <c r="H86" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>이지상</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="J86" s="10" t="inlineStr">
@@ -3785,12 +3787,12 @@
       </c>
       <c r="K86" s="11" t="inlineStr">
         <is>
-          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
+          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
         </is>
       </c>
       <c r="L86" s="11" t="inlineStr">
         <is>
-          <t>‘안내용 웹 가정통신문 만들기’(가안) 대신 — 회원가입·댓글·첨부를 빼고 전달사항·준비물을 한 화면에 올리는 안내 페이지로 줄이면</t>
+          <t>‘전자칠판용 우리 반 일과 안내판’(가안) 대신 — 전교 시간표 대신 우리 반 시간표 변경만 안내하는 화면으로 줄이면</t>
         </is>
       </c>
     </row>
@@ -3806,18 +3808,18 @@
       <c r="E87" s="10" t="inlineStr"/>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>키워드 레이더</t>
+          <t>준비물, 전달사항 알림장 사이트</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr"/>
       <c r="H87" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>이지상</t>
         </is>
       </c>
       <c r="J87" s="10" t="inlineStr">
@@ -3827,10 +3829,14 @@
       </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
-          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
-        </is>
-      </c>
-      <c r="L87" s="11" t="inlineStr"/>
+          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
+        </is>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>‘안내용 웹 가정통신문 만들기’(가안) 대신 — 회원가입·댓글·첨부를 빼고 전달사항·준비물을 한 화면에 올리는 안내 페이지로 줄이면</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -3844,13 +3850,13 @@
       <c r="E88" s="10" t="inlineStr"/>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>부장회의록 및 주간계획</t>
+          <t>키워드 레이더</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr"/>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
@@ -3865,7 +3871,7 @@
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
+          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr"/>
@@ -3882,18 +3888,18 @@
       <c r="E89" s="10" t="inlineStr"/>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>우리반 출석부</t>
+          <t>부장회의록 및 주간계획</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>진정숙</t>
+          <t>이승엽</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr">
@@ -3903,7 +3909,7 @@
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
+          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
         </is>
       </c>
       <c r="L89" s="11" t="inlineStr"/>
@@ -3920,18 +3926,18 @@
       <c r="E90" s="10" t="inlineStr"/>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>학부모 상담 기록요약</t>
+          <t>우리반 출석부</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="J90" s="10" t="inlineStr">
@@ -3941,14 +3947,10 @@
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
-        </is>
-      </c>
-      <c r="L90" s="11" t="inlineStr">
-        <is>
-          <t>‘상담 전 사전 질문지’(가안) 대신 — 외부 AI 없이 상담 메모를 항목별 칸에 나눠 정리하는 기록 양식으로 바꾸면</t>
-        </is>
-      </c>
+          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
+        </is>
+      </c>
+      <c r="L90" s="11" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -3962,49 +3964,77 @@
       <c r="E91" s="10" t="inlineStr"/>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>반 편성 조건 점검기</t>
+          <t>학부모 상담 기록요약</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K91" s="11" t="inlineStr">
+        <is>
+          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
+        </is>
+      </c>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>‘상담 전 사전 질문지’(가안) 대신 — 외부 AI 없이 상담 메모를 항목별 칸에 나눠 정리하는 기록 양식으로 바꾸면</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr"/>
+      <c r="C92" s="11" t="inlineStr"/>
+      <c r="D92" s="11" t="inlineStr"/>
+      <c r="E92" s="10" t="inlineStr"/>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>반 편성 조건 점검기</t>
+        </is>
+      </c>
+      <c r="G92" s="11" t="inlineStr"/>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I91" s="10" t="inlineStr">
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J91" s="10" t="inlineStr">
+      <c r="J92" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="K91" s="11" t="inlineStr">
+      <c r="K92" s="11" t="inlineStr">
         <is>
           <t>특수 배려·분리 요청 같은 민감 정보를 다루고 LLM API가 필요함. 제안자도 다음 회의에서 논의하기로 남겨 둠</t>
         </is>
       </c>
-      <c r="L91" s="11" t="inlineStr">
+      <c r="L92" s="11" t="inlineStr">
         <is>
           <t>‘모둠 자동 편성기’(가안) 대신 — AI 없이, 이름 대신 번호로 성비·분리 조건만 점검하는 방식으로 줄이면</t>
         </is>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="7" t="n"/>
-      <c r="G92" s="7" t="n"/>
-      <c r="H92" s="6" t="n"/>
-      <c r="I92" s="6" t="n"/>
-      <c r="J92" s="6" t="n"/>
-      <c r="K92" s="7" t="n"/>
-      <c r="L92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -4272,6 +4302,20 @@
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
     </row>
+    <row r="112">
+      <c r="A112" s="6" t="n"/>
+      <c r="B112" s="6" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+      <c r="E112" s="6" t="n"/>
+      <c r="F112" s="7" t="n"/>
+      <c r="G112" s="7" t="n"/>
+      <c r="H112" s="6" t="n"/>
+      <c r="I112" s="6" t="n"/>
+      <c r="J112" s="6" t="n"/>
+      <c r="K112" s="7" t="n"/>
+      <c r="L112" s="7" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B4:L4"/>
@@ -4284,10 +4328,10 @@
     <mergeCell ref="B8:L8"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A13:A111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A13:A112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
-    <dataValidation sqref="J13:J111" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J13:J112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -2240,7 +2240,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
+          <t>참고: 업무자동화를 맡고 계신 진정숙 선생님이 수업자동화 쪽에 아이디어로 제안해 주신 앱입니다. 수업자동화 선생님들이 참고하시면 좋겠습니다. / 심화 이유: 게임 루프와 여러 문제 방식, 기록 관리 / 실시간 랭킹은 서버가 필요해 기기 내 기록으로 단순화</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr"/>

--- a/엑셀양식/최종목차_가목차_초안.xlsx
+++ b/엑셀양식/최종목차_가목차_초안.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2248,124 +2248,145 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
+          <t>수업자동화</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>부록</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>빌드·배포: 만든 앱 완성하고 공유하기</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>빌드와 배포</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>부록 1</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>내가 만든 앱을 하나의 파일로 완성하기</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>빌드란? 흩어진 코드를 실행할 수 있는 결과물로 묶는 과정
+HTML 파일 하나로 정리해 저장하기
+다른 컴퓨터·전자칠판에서 열어 확인하기</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr"/>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>원래 용어: 빌드</t>
+        </is>
+      </c>
+      <c r="L49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>수업자동화</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>부록</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>빌드·배포: 만든 앱 완성하고 공유하기</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>부록 2</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>학생에게 링크로 나눠 주기</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>배포란? 만든 앱을 인터넷 주소로 올리는 과정
+무료로 웹에 올리기 (GitHub Pages, Netlify 등)
+QR 코드로 학생에게 나눠 주기
+고친 내용을 다시 올리기
+앱스 스크립트 앱을 웹 앱으로 배포하기 (PART 4)</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
+      <c r="I50" s="6" t="inlineStr"/>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>원래 용어: 배포</t>
+        </is>
+      </c>
+      <c r="L50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B51" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 이론</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩이란?</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>바이브 코딩 개념 (패러다임의 변화)
 개발 과정 (요구분석-설계-구현-테스트-배포-운영)
 필수 용어 (예: 라이브러리, 빌드, 디버깅, 배포 등)</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr"/>
-      <c r="I49" s="6" t="inlineStr"/>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr"/>
-      <c r="E50" s="6" t="inlineStr"/>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트가 결과를 좌우한다 (bad vs good)
-마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr"/>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K50" s="7" t="inlineStr"/>
-      <c r="L50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr"/>
-      <c r="E51" s="6" t="inlineStr"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>수업 22</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>김형훈</t>
-        </is>
-      </c>
+      <c r="H51" s="6" t="inlineStr"/>
+      <c r="I51" s="6" t="inlineStr"/>
       <c r="J51" s="6" t="inlineStr">
         <is>
           <t>초안</t>
         </is>
       </c>
-      <c r="K51" s="7" t="inlineStr">
-        <is>
-          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
-        </is>
-      </c>
+      <c r="K51" s="7" t="inlineStr"/>
       <c r="L51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2386,12 +2407,13 @@
       <c r="E52" s="6" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+          <t>프롬프트 기초</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>사례</t>
+          <t>프롬프트가 결과를 좌우한다 (bad vs good)
+마크다운 기초 (# ## ### - 1. ``` ` --- ** 등)</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr"/>
@@ -2422,10 +2444,90 @@
       <c r="E53" s="6" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr">
         <is>
+          <t>AI에게 질문으로 되물어 요청 문장 다듬기</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>수업 22</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>김형훈</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>프롬프트 기초에 이어 붙인 첫 실습 / AI API 필요: 실습에 API 키 과정을 넣을지 결정 필요</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>선생님들이 바이브 코딩을 해야 하는 이유</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>사례</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr"/>
+      <c r="I54" s="6" t="inlineStr"/>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>바이브 코딩의 기초: 만들기 전에 알아 두기</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
           <t>실습 도구 준비하기: 설치하고 미리 보기</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>챗GPT 계정·요금제 확인과 코딩 기능 시작하기
 챗GPT로 만든 HTML 파일을 브라우저에서 열어 미리 보기
@@ -2433,183 +2535,103 @@
 Firebase 프로젝트 만들어 보기 (방학 중 안부 체크인)</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B56" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr"/>
-      <c r="E54" s="6" t="inlineStr"/>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>[챗GPT] 진급 반 인계 카드</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K54" s="7" t="inlineStr">
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>2월</t>
         </is>
       </c>
-      <c r="L54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+      <c r="L56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B57" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr"/>
-      <c r="E55" s="6" t="inlineStr"/>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>[챗GPT] 조건을 반영한 자리 배치</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
+      <c r="I57" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr">
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
         <is>
           <t>3월</t>
         </is>
       </c>
-      <c r="L55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr"/>
-      <c r="E56" s="8" t="inlineStr"/>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT] 모둠 자동 편성기</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr"/>
-      <c r="H56" s="8" t="inlineStr"/>
-      <c r="I56" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J56" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K56" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
-        </is>
-      </c>
-      <c r="L56" s="9" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C57" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr"/>
-      <c r="E57" s="8" t="inlineStr"/>
-      <c r="F57" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT] 1인 1역 역할 배정표</t>
-        </is>
-      </c>
-      <c r="G57" s="9" t="inlineStr"/>
-      <c r="H57" s="8" t="inlineStr"/>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J57" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K57" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
-        </is>
-      </c>
-      <c r="L57" s="9" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -2629,7 +2651,7 @@
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 전자칠판용 우리 반 일과 안내판</t>
+          <t>[챗GPT] 모둠 자동 편성기</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr"/>
@@ -2646,174 +2668,174 @@
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
+          <t>가안 · 인원·성비 조건을 넣으면 모둠을 나눠 줌</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr"/>
+      <c r="E59" s="8" t="inlineStr"/>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT] 1인 1역 역할 배정표</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 역할 목록과 명단으로 배정·조회</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr"/>
+      <c r="E60" s="8" t="inlineStr"/>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT] 전자칠판용 우리 반 일과 안내판</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
           <t>가안 · 시간표·준비물·오늘 일정을 한 화면에</t>
         </is>
       </c>
-      <c r="L58" s="9" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="L60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B61" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr"/>
-      <c r="E59" s="6" t="inlineStr"/>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr"/>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>[챗GPT] 특별활동 자동 출석부</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="I61" s="6" t="inlineStr">
         <is>
           <t>진정숙</t>
         </is>
       </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K59" s="7" t="inlineStr">
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
         <is>
           <t>명단 업로드·클릭 출석·인쇄까지 한 화면</t>
         </is>
       </c>
-      <c r="L59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="L61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B62" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr"/>
-      <c r="E60" s="6" t="inlineStr"/>
-      <c r="F60" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr"/>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>[챗GPT] 청소 구역 점검판</t>
         </is>
       </c>
-      <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr"/>
-      <c r="E61" s="8" t="inlineStr"/>
-      <c r="F61" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT] 과제 제출 체크리스트</t>
-        </is>
-      </c>
-      <c r="G61" s="9" t="inlineStr"/>
-      <c r="H61" s="8" t="inlineStr"/>
-      <c r="I61" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J61" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
-        </is>
-      </c>
-      <c r="L61" s="9" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="inlineStr"/>
-      <c r="E62" s="8" t="inlineStr"/>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT] 칭찬 포인트 보드</t>
-        </is>
-      </c>
-      <c r="G62" s="9" t="inlineStr"/>
-      <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J62" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K62" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
-        </is>
-      </c>
-      <c r="L62" s="9" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr"/>
+      <c r="L62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -2833,7 +2855,7 @@
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 학급 행사 D-day 게시판</t>
+          <t>[챗GPT] 과제 제출 체크리스트</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr"/>
@@ -2850,7 +2872,7 @@
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
-          <t>가안</t>
+          <t>가안 · 명단을 클릭해 제출 여부를 기록하고 미제출자만 보기</t>
         </is>
       </c>
       <c r="L63" s="9" t="inlineStr"/>
@@ -2873,7 +2895,7 @@
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 학급 문고 대출 기록표</t>
+          <t>[챗GPT] 칭찬 포인트 보드</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr"/>
@@ -2890,7 +2912,7 @@
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>가안</t>
+          <t>가안 · 기존 도서에도 있는 주제라 차별화 방향 필요</t>
         </is>
       </c>
       <c r="L64" s="9" t="inlineStr"/>
@@ -2913,7 +2935,7 @@
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 학급 규칙 함께 정하기 투표판</t>
+          <t>[챗GPT] 학급 행사 D-day 게시판</t>
         </is>
       </c>
       <c r="G65" s="9" t="inlineStr"/>
@@ -2930,7 +2952,7 @@
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>가안 · 3월 학급 세우기 활동</t>
+          <t>가안</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr"/>
@@ -2942,18 +2964,18 @@
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr"/>
       <c r="E66" s="8" t="inlineStr"/>
       <c r="F66" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 안내용 웹 가정통신문 만들기</t>
+          <t>[챗GPT] 학급 문고 대출 기록표</t>
         </is>
       </c>
       <c r="G66" s="9" t="inlineStr"/>
@@ -2970,174 +2992,174 @@
       </c>
       <c r="K66" s="9" t="inlineStr">
         <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>학급 경영: 학급을 세우고 매일 운영하기</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr"/>
+      <c r="E67" s="8" t="inlineStr"/>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 학급 규칙 함께 정하기 투표판</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J67" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 3월 학급 세우기 활동</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr"/>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT] 안내용 웹 가정통신문 만들기</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
           <t>가안 · 한글 문서 대신 링크 하나로 보내는 안내문</t>
         </is>
       </c>
-      <c r="L66" s="9" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
+      <c r="L68" s="9" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B67" s="6" t="n">
+      <c r="B69" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="6" t="inlineStr"/>
-      <c r="F67" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr"/>
+      <c r="E69" s="6" t="inlineStr"/>
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>[챗GPT+구글 시트] 겹치지 않는 학부모 상담 예약</t>
         </is>
       </c>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I67" s="6" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K67" s="7" t="inlineStr"/>
-      <c r="L67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B68" s="6" t="n">
+      <c r="B70" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>학부모 소통: 상담과 신청 간편하게 받기</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr"/>
-      <c r="E68" s="6" t="inlineStr"/>
-      <c r="F68" s="7" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr"/>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>[챗GPT+구글 시트] 정원이 차면 자동 마감되는 신청서</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I68" s="6" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>임부현</t>
         </is>
       </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K68" s="7" t="inlineStr">
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
         <is>
           <t>방과후학교·학부모 연수</t>
         </is>
       </c>
-      <c r="L68" s="7" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="inlineStr"/>
-      <c r="E69" s="8" t="inlineStr"/>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
-        </is>
-      </c>
-      <c r="G69" s="9" t="inlineStr"/>
-      <c r="H69" s="8" t="inlineStr"/>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J69" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K69" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 구글 시트로 응답 수합</t>
-        </is>
-      </c>
-      <c r="L69" s="9" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="inlineStr"/>
-      <c r="E70" s="8" t="inlineStr"/>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 공개수업 참관 신청서</t>
-        </is>
-      </c>
-      <c r="G70" s="9" t="inlineStr"/>
-      <c r="H70" s="8" t="inlineStr"/>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 시간대별 정원 표시</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr"/>
+      <c r="L70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -3157,7 +3179,7 @@
       <c r="E71" s="8" t="inlineStr"/>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 상담 전 사전 질문지</t>
+          <t>[챗GPT+구글 시트] 참여 여부를 받는 가정통신문과 미응답 확인</t>
         </is>
       </c>
       <c r="G71" s="9" t="inlineStr"/>
@@ -3174,90 +3196,90 @@
       </c>
       <c r="K71" s="9" t="inlineStr">
         <is>
+          <t>가안 · 구글 시트로 응답 수합</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr"/>
+      <c r="E72" s="8" t="inlineStr"/>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 공개수업 참관 신청서</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr"/>
+      <c r="H72" s="8" t="inlineStr"/>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 시간대별 정원 표시</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>학부모 소통: 상담과 신청 간편하게 받기</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="8" t="inlineStr"/>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 상담 전 사전 질문지</t>
+        </is>
+      </c>
+      <c r="G73" s="9" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
           <t>가안 · 상담 예약(4-1)과 이어지는 실습</t>
         </is>
       </c>
-      <c r="L71" s="9" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr"/>
-      <c r="E72" s="6" t="inlineStr"/>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT] 회신서 미제출자 확인기</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K72" s="7" t="inlineStr"/>
-      <c r="L72" s="7" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>행정 업무: 서류와 수합 줄이기</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr"/>
-      <c r="E73" s="6" t="inlineStr"/>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>[챗GPT] 공문서 표기 점검기</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>석희철</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K73" s="7" t="inlineStr"/>
-      <c r="L73" s="7" t="inlineStr"/>
+      <c r="L73" s="9" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -3277,18 +3299,18 @@
       <c r="E74" s="6" t="inlineStr"/>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] QR로 받는 교직원 연수 서명부</t>
+          <t>[챗GPT] 회신서 미제출자 확인기</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
@@ -3317,18 +3339,18 @@
       <c r="E75" s="6" t="inlineStr"/>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>[챗GPT+구글 시트] 부서 통합 외부인 방문대장</t>
+          <t>[챗GPT] 공문서 표기 점검기</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>석희철</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
@@ -3340,84 +3362,84 @@
       <c r="L75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B76" s="8" t="n">
+      <c r="B76" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr"/>
-      <c r="E76" s="8" t="inlineStr"/>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 행사 물품 수요 조사 집계기</t>
-        </is>
-      </c>
-      <c r="G76" s="9" t="inlineStr"/>
-      <c r="H76" s="8" t="inlineStr"/>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K76" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 반별 수량을 모아 합계표로</t>
-        </is>
-      </c>
-      <c r="L76" s="9" t="inlineStr"/>
+      <c r="D76" s="7" t="inlineStr"/>
+      <c r="E76" s="6" t="inlineStr"/>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] QR로 받는 교직원 연수 서명부</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr"/>
+      <c r="L76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="8" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B77" s="8" t="n">
+      <c r="B77" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr"/>
-      <c r="E77" s="8" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>[챗GPT+구글 시트] 특별실·기자재 예약판</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr"/>
-      <c r="H77" s="8" t="inlineStr"/>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="J77" s="8" t="inlineStr">
-        <is>
-          <t>가안</t>
-        </is>
-      </c>
-      <c r="K77" s="9" t="inlineStr">
-        <is>
-          <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
-        </is>
-      </c>
-      <c r="L77" s="9" t="inlineStr"/>
+      <c r="D77" s="7" t="inlineStr"/>
+      <c r="E77" s="6" t="inlineStr"/>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>[챗GPT+구글 시트] 부서 통합 외부인 방문대장</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr"/>
+      <c r="L77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -3426,18 +3448,18 @@
         </is>
       </c>
       <c r="B78" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
+          <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr"/>
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 관찰 기록으로 단원 평어 초안 만들기</t>
+          <t>[챗GPT+구글 시트] 행사 물품 수요 조사 집계기</t>
         </is>
       </c>
       <c r="G78" s="9" t="inlineStr"/>
@@ -3454,7 +3476,7 @@
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
+          <t>가안 · 반별 수량을 모아 합계표로</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr"/>
@@ -3466,18 +3488,18 @@
         </is>
       </c>
       <c r="B79" s="8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>평가·학년 말: 기록하고 마무리하기</t>
+          <t>행정 업무: 서류와 수합 줄이기</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr"/>
       <c r="E79" s="8" t="inlineStr"/>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 수행평가 채점 기준표(루브릭) 채점기</t>
+          <t>[챗GPT+구글 시트] 특별실·기자재 예약판</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr"/>
@@ -3494,7 +3516,7 @@
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강</t>
+          <t>가안 · 요일·교시별로 겹치지 않게 예약</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr"/>
@@ -3517,7 +3539,7 @@
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>[챗GPT] 문항별 정답률 분석표</t>
+          <t>[챗GPT] 관찰 기록으로 단원 평어 초안 만들기</t>
         </is>
       </c>
       <c r="G80" s="9" t="inlineStr"/>
@@ -3534,7 +3556,7 @@
       </c>
       <c r="K80" s="9" t="inlineStr">
         <is>
-          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
+          <t>가안 · 평가·기록 보강 · 문장 조합 방식이면 AI API 없이 가능</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr"/>
@@ -3557,10 +3579,90 @@
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="9" t="inlineStr">
         <is>
+          <t>[챗GPT] 수행평가 채점 기준표(루브릭) 채점기</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 평가·기록 보강</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr"/>
+      <c r="E82" s="8" t="inlineStr"/>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>[챗GPT] 문항별 정답률 분석표</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="inlineStr"/>
+      <c r="H82" s="8" t="inlineStr"/>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="J82" s="8" t="inlineStr">
+        <is>
+          <t>가안</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="inlineStr">
+        <is>
+          <t>가안 · 평가·기록 보강 · 시험 결과를 붙여 넣으면 문항별 정답률</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>평가·학년 말: 기록하고 마무리하기</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr"/>
+      <c r="E83" s="8" t="inlineStr"/>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
           <t>[챗GPT] 학교생활기록부/세부능력 및 특기사항 글자 수·표현 점검기</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr">
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>NEIS 기준 글자 수·바이트 계산, 항목별 제한 초과 표시
 기재 금지·유의 표현 형광펜 표시(목록은 교사가 수정)
@@ -3568,280 +3670,218 @@
 AI 문장 생성·윤문·외부 전송 없이 브라우저 안에서만 동작</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr">
         <is>
           <t>미정</t>
         </is>
       </c>
-      <c r="J81" s="8" t="inlineStr">
+      <c r="J83" s="8" t="inlineStr">
         <is>
           <t>가안</t>
         </is>
       </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="K83" s="9" t="inlineStr">
         <is>
           <t>가안 · 평가·기록 보강 · 교육부 지침(AI는 보조만, AI 문장 그대로 기재 금지)에 맞춰 점검만 하고 수정은 교사가 결정</t>
         </is>
       </c>
-      <c r="L81" s="9" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="L83" s="9" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B82" s="6" t="n">
+      <c r="B84" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr"/>
-      <c r="E82" s="6" t="inlineStr"/>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr"/>
+      <c r="E84" s="6" t="inlineStr"/>
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>[챗GPT+구글 시트] 단원 끝 학생 자기평가 카드</t>
         </is>
       </c>
-      <c r="G82" s="7" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J82" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K82" s="7" t="inlineStr">
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
         <is>
           <t>평가·기록 아이디어가 이것 하나뿐 → 평어·성취도 평가 꼭지 보강 필요</t>
         </is>
       </c>
-      <c r="L82" s="7" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+      <c r="L84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B83" s="6" t="n">
+      <c r="B85" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>평가·학년 말: 기록하고 마무리하기</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr"/>
-      <c r="E83" s="6" t="inlineStr"/>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr"/>
+      <c r="E85" s="6" t="inlineStr"/>
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>[챗GPT+Firebase] 방학 중 안부 체크인</t>
         </is>
       </c>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="G85" s="7" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>초안</t>
-        </is>
-      </c>
-      <c r="K83" s="7" t="inlineStr">
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
         <is>
           <t>7월</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>수업자동화</t>
-        </is>
-      </c>
-      <c r="B84" s="10" t="inlineStr"/>
-      <c r="C84" s="11" t="inlineStr"/>
-      <c r="D84" s="11" t="inlineStr"/>
-      <c r="E84" s="10" t="inlineStr"/>
-      <c r="F84" s="11" t="inlineStr">
-        <is>
-          <t>발표 모드</t>
-        </is>
-      </c>
-      <c r="G84" s="11" t="inlineStr"/>
-      <c r="H84" s="10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>강현수</t>
-        </is>
-      </c>
-      <c r="J84" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K84" s="11" t="inlineStr">
-        <is>
-          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
-        </is>
-      </c>
-      <c r="L84" s="11" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="L85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr"/>
-      <c r="C85" s="11" t="inlineStr"/>
-      <c r="D85" s="11" t="inlineStr"/>
-      <c r="E85" s="10" t="inlineStr"/>
-      <c r="F85" s="11" t="inlineStr">
-        <is>
-          <t>기기대여대장</t>
-        </is>
-      </c>
-      <c r="G85" s="11" t="inlineStr"/>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I85" s="10" t="inlineStr">
-        <is>
-          <t>진정숙</t>
-        </is>
-      </c>
-      <c r="J85" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K85" s="11" t="inlineStr">
-        <is>
-          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
-        </is>
-      </c>
-      <c r="L85" s="11" t="inlineStr">
-        <is>
-          <t>‘학급 문고 대출 기록표’(가안) 대신 — 로그인·관리자 모드를 빼고 대여·반납 기록 한 가지 기능으로 줄이면</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>부록</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>빌드·배포: 만든 앱 완성하고 공유하기</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>빌드와 배포</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>부록 1</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>내가 만든 앱을 하나의 파일로 완성하기</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>빌드란? 흩어진 코드를 실행할 수 있는 결과물로 묶는 과정
+HTML 파일 하나로 정리해 저장하기
+다른 컴퓨터에서 열어 확인하기</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr"/>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>원래 용어: 빌드</t>
+        </is>
+      </c>
+      <c r="L86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>업무자동화</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr"/>
-      <c r="C86" s="11" t="inlineStr"/>
-      <c r="D86" s="11" t="inlineStr"/>
-      <c r="E86" s="10" t="inlineStr"/>
-      <c r="F86" s="11" t="inlineStr">
-        <is>
-          <t>스마트 시간표 교체</t>
-        </is>
-      </c>
-      <c r="G86" s="11" t="inlineStr"/>
-      <c r="H86" s="10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I86" s="10" t="inlineStr">
-        <is>
-          <t>진정숙</t>
-        </is>
-      </c>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K86" s="11" t="inlineStr">
-        <is>
-          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
-        </is>
-      </c>
-      <c r="L86" s="11" t="inlineStr">
-        <is>
-          <t>‘전자칠판용 우리 반 일과 안내판’(가안) 대신 — 전교 시간표 대신 우리 반 시간표 변경만 안내하는 화면으로 줄이면</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>업무자동화</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="inlineStr"/>
-      <c r="C87" s="11" t="inlineStr"/>
-      <c r="D87" s="11" t="inlineStr"/>
-      <c r="E87" s="10" t="inlineStr"/>
-      <c r="F87" s="11" t="inlineStr">
-        <is>
-          <t>준비물, 전달사항 알림장 사이트</t>
-        </is>
-      </c>
-      <c r="G87" s="11" t="inlineStr"/>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>이지상</t>
-        </is>
-      </c>
-      <c r="J87" s="10" t="inlineStr">
-        <is>
-          <t>재검토</t>
-        </is>
-      </c>
-      <c r="K87" s="11" t="inlineStr">
-        <is>
-          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
-        </is>
-      </c>
-      <c r="L87" s="11" t="inlineStr">
-        <is>
-          <t>‘안내용 웹 가정통신문 만들기’(가안) 대신 — 회원가입·댓글·첨부를 빼고 전달사항·준비물을 한 화면에 올리는 안내 페이지로 줄이면</t>
-        </is>
-      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>부록</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>빌드·배포: 만든 앱 완성하고 공유하기</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr"/>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>부록 2</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>학부모·동료 교사에게 링크로 공유하기</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>배포란? 만든 앱을 인터넷 주소로 올리는 과정
+무료로 웹에 올리기 (GitHub Pages, Netlify 등)
+구글 시트와 연결한 앱을 앱스 스크립트 웹 앱으로 배포하기
+가정통신문·메신저에 링크와 QR 코드 넣기
+고친 내용을 다시 올리기</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr"/>
+      <c r="I87" s="6" t="inlineStr"/>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>초안</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>원래 용어: 배포</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>업무자동화</t>
+          <t>수업자동화</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr"/>
@@ -3850,18 +3890,18 @@
       <c r="E88" s="10" t="inlineStr"/>
       <c r="F88" s="11" t="inlineStr">
         <is>
-          <t>키워드 레이더</t>
+          <t>발표 모드</t>
         </is>
       </c>
       <c r="G88" s="11" t="inlineStr"/>
       <c r="H88" s="10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>강현수</t>
         </is>
       </c>
       <c r="J88" s="10" t="inlineStr">
@@ -3871,7 +3911,7 @@
       </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
-          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
+          <t>학생 기기 화면을 한곳으로 모으고 제어하려면 실시간 서버와 기기 관리가 필요함. 제안자도 강제 전환은 막을 수 없다고 적음</t>
         </is>
       </c>
       <c r="L88" s="11" t="inlineStr"/>
@@ -3888,18 +3928,18 @@
       <c r="E89" s="10" t="inlineStr"/>
       <c r="F89" s="11" t="inlineStr">
         <is>
-          <t>부장회의록 및 주간계획</t>
+          <t>기기대여대장</t>
         </is>
       </c>
       <c r="G89" s="11" t="inlineStr"/>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr">
         <is>
-          <t>이승엽</t>
+          <t>진정숙</t>
         </is>
       </c>
       <c r="J89" s="10" t="inlineStr">
@@ -3909,10 +3949,14 @@
       </c>
       <c r="K89" s="11" t="inlineStr">
         <is>
-          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
-        </is>
-      </c>
-      <c r="L89" s="11" t="inlineStr"/>
+          <t>로그인·관리자 모드·대여 이력·연장 신청을 묶은 시스템. ‘한 줄에 기능 하나’ 원칙과 맞지 않아 실습 한 꼭지로 담기 어려움</t>
+        </is>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>‘학급 문고 대출 기록표’(가안) 대신 — 로그인·관리자 모드를 빼고 대여·반납 기록 한 가지 기능으로 줄이면</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -3926,13 +3970,13 @@
       <c r="E90" s="10" t="inlineStr"/>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>우리반 출석부</t>
+          <t>스마트 시간표 교체</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr"/>
       <c r="H90" s="10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr">
@@ -3947,10 +3991,14 @@
       </c>
       <c r="K90" s="11" t="inlineStr">
         <is>
-          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
-        </is>
-      </c>
-      <c r="L90" s="11" t="inlineStr"/>
+          <t>전교 시간표 데이터와 교사별 로그인, 대강 교사 탐색이 필요함. 학교마다 시간표 구조가 달라 따라 만들기 어려움</t>
+        </is>
+      </c>
+      <c r="L90" s="11" t="inlineStr">
+        <is>
+          <t>‘전자칠판용 우리 반 일과 안내판’(가안) 대신 — 전교 시간표 대신 우리 반 시간표 변경만 안내하는 화면으로 줄이면</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
@@ -3964,18 +4012,18 @@
       <c r="E91" s="10" t="inlineStr"/>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>학부모 상담 기록요약</t>
+          <t>준비물, 전달사항 알림장 사이트</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr"/>
       <c r="H91" s="10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr">
         <is>
-          <t>임부현</t>
+          <t>이지상</t>
         </is>
       </c>
       <c r="J91" s="10" t="inlineStr">
@@ -3985,12 +4033,12 @@
       </c>
       <c r="K91" s="11" t="inlineStr">
         <is>
-          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
+          <t>회원가입·승인·댓글·첨부파일까지 갖춘 서비스 규모. 실습보다는 완성 서비스에 가까움</t>
         </is>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>‘상담 전 사전 질문지’(가안) 대신 — 외부 AI 없이 상담 메모를 항목별 칸에 나눠 정리하는 기록 양식으로 바꾸면</t>
+          <t>‘안내용 웹 가정통신문 만들기’(가안) 대신 — 회원가입·댓글·첨부를 빼고 전달사항·준비물을 한 화면에 올리는 안내 페이지로 줄이면</t>
         </is>
       </c>
     </row>
@@ -4006,91 +4054,191 @@
       <c r="E92" s="10" t="inlineStr"/>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>반 편성 조건 점검기</t>
+          <t>키워드 레이더</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr"/>
       <c r="H92" s="10" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K92" s="11" t="inlineStr">
+        <is>
+          <t>매일 새벽 자동 수집하는 서버와 텔레그램 봇이 필요함. 웹앱 실습 범위 밖</t>
+        </is>
+      </c>
+      <c r="L92" s="11" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr"/>
+      <c r="C93" s="11" t="inlineStr"/>
+      <c r="D93" s="11" t="inlineStr"/>
+      <c r="E93" s="10" t="inlineStr"/>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>부장회의록 및 주간계획</t>
+        </is>
+      </c>
+      <c r="G93" s="11" t="inlineStr"/>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>이승엽</t>
+        </is>
+      </c>
+      <c r="J93" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K93" s="11" t="inlineStr">
+        <is>
+          <t>MS 온라인 엑셀의 Office 스크립트 전용. 책의 다른 실습 도구와 환경이 다름</t>
+        </is>
+      </c>
+      <c r="L93" s="11" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr"/>
+      <c r="C94" s="11" t="inlineStr"/>
+      <c r="D94" s="11" t="inlineStr"/>
+      <c r="E94" s="10" t="inlineStr"/>
+      <c r="F94" s="11" t="inlineStr">
+        <is>
+          <t>우리반 출석부</t>
+        </is>
+      </c>
+      <c r="G94" s="11" t="inlineStr"/>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I94" s="10" t="inlineStr">
+        <is>
+          <t>진정숙</t>
+        </is>
+      </c>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K94" s="11" t="inlineStr">
+        <is>
+          <t>병결 등 결석 사유 같은 민감 정보를 서버에 실시간으로 쌓는 구조. 개인정보 부담이 크고 #11 출석부와 겹침</t>
+        </is>
+      </c>
+      <c r="L94" s="11" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr"/>
+      <c r="C95" s="11" t="inlineStr"/>
+      <c r="D95" s="11" t="inlineStr"/>
+      <c r="E95" s="10" t="inlineStr"/>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>학부모 상담 기록요약</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr"/>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>임부현</t>
+        </is>
+      </c>
+      <c r="J95" s="10" t="inlineStr">
+        <is>
+          <t>재검토</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="inlineStr">
+        <is>
+          <t>상담 내용을 외부 AI(ChatGPT)로 보내 정리하는 구조라 학생·학부모 개인정보 문제가 생김</t>
+        </is>
+      </c>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>‘상담 전 사전 질문지’(가안) 대신 — 외부 AI 없이 상담 메모를 항목별 칸에 나눠 정리하는 기록 양식으로 바꾸면</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>업무자동화</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr"/>
+      <c r="C96" s="11" t="inlineStr"/>
+      <c r="D96" s="11" t="inlineStr"/>
+      <c r="E96" s="10" t="inlineStr"/>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>반 편성 조건 점검기</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr"/>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I92" s="10" t="inlineStr">
+      <c r="I96" s="10" t="inlineStr">
         <is>
           <t>석희철</t>
         </is>
       </c>
-      <c r="J92" s="10" t="inlineStr">
+      <c r="J96" s="10" t="inlineStr">
         <is>
           <t>재검토</t>
         </is>
       </c>
-      <c r="K92" s="11" t="inlineStr">
+      <c r="K96" s="11" t="inlineStr">
         <is>
           <t>특수 배려·분리 요청 같은 민감 정보를 다루고 LLM API가 필요함. 제안자도 다음 회의에서 논의하기로 남겨 둠</t>
         </is>
       </c>
-      <c r="L92" s="11" t="inlineStr">
+      <c r="L96" s="11" t="inlineStr">
         <is>
           <t>‘모둠 자동 편성기’(가안) 대신 — AI 없이, 이름 대신 번호로 성비·분리 조건만 점검하는 방식으로 줄이면</t>
         </is>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="n"/>
-      <c r="B93" s="6" t="n"/>
-      <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
-      <c r="E93" s="6" t="n"/>
-      <c r="F93" s="7" t="n"/>
-      <c r="G93" s="7" t="n"/>
-      <c r="H93" s="6" t="n"/>
-      <c r="I93" s="6" t="n"/>
-      <c r="J93" s="6" t="n"/>
-      <c r="K93" s="7" t="n"/>
-      <c r="L93" s="7" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="n"/>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
-      <c r="E94" s="6" t="n"/>
-      <c r="F94" s="7" t="n"/>
-      <c r="G94" s="7" t="n"/>
-      <c r="H94" s="6" t="n"/>
-      <c r="I94" s="6" t="n"/>
-      <c r="J94" s="6" t="n"/>
-      <c r="K94" s="7" t="n"/>
-      <c r="L94" s="7" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="n"/>
-      <c r="B95" s="6" t="n"/>
-      <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
-      <c r="E95" s="6" t="n"/>
-      <c r="F95" s="7" t="n"/>
-      <c r="G95" s="7" t="n"/>
-      <c r="H95" s="6" t="n"/>
-      <c r="I95" s="6" t="n"/>
-      <c r="J95" s="6" t="n"/>
-      <c r="K95" s="7" t="n"/>
-      <c r="L95" s="7" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="n"/>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
-      <c r="E96" s="6" t="n"/>
-      <c r="F96" s="7" t="n"/>
-      <c r="G96" s="7" t="n"/>
-      <c r="H96" s="6" t="n"/>
-      <c r="I96" s="6" t="n"/>
-      <c r="J96" s="6" t="n"/>
-      <c r="K96" s="7" t="n"/>
-      <c r="L96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
@@ -4316,6 +4464,62 @@
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
     </row>
+    <row r="113">
+      <c r="A113" s="6" t="n"/>
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="7" t="n"/>
+      <c r="D113" s="7" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="F113" s="7" t="n"/>
+      <c r="G113" s="7" t="n"/>
+      <c r="H113" s="6" t="n"/>
+      <c r="I113" s="6" t="n"/>
+      <c r="J113" s="6" t="n"/>
+      <c r="K113" s="7" t="n"/>
+      <c r="L113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="n"/>
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="7" t="n"/>
+      <c r="D114" s="7" t="n"/>
+      <c r="E114" s="6" t="n"/>
+      <c r="F114" s="7" t="n"/>
+      <c r="G114" s="7" t="n"/>
+      <c r="H114" s="6" t="n"/>
+      <c r="I114" s="6" t="n"/>
+      <c r="J114" s="6" t="n"/>
+      <c r="K114" s="7" t="n"/>
+      <c r="L114" s="7" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="n"/>
+      <c r="B115" s="6" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="7" t="n"/>
+      <c r="E115" s="6" t="n"/>
+      <c r="F115" s="7" t="n"/>
+      <c r="G115" s="7" t="n"/>
+      <c r="H115" s="6" t="n"/>
+      <c r="I115" s="6" t="n"/>
+      <c r="J115" s="6" t="n"/>
+      <c r="K115" s="7" t="n"/>
+      <c r="L115" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="n"/>
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="D116" s="7" t="n"/>
+      <c r="E116" s="6" t="n"/>
+      <c r="F116" s="7" t="n"/>
+      <c r="G116" s="7" t="n"/>
+      <c r="H116" s="6" t="n"/>
+      <c r="I116" s="6" t="n"/>
+      <c r="J116" s="6" t="n"/>
+      <c r="K116" s="7" t="n"/>
+      <c r="L116" s="7" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B4:L4"/>
@@ -4328,10 +4532,10 @@
     <mergeCell ref="B8:L8"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="A13:A112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A13:A116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"수업자동화,업무자동화"</formula1>
     </dataValidation>
-    <dataValidation sqref="J13:J112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J13:J116" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"확정,검토 중,초안,가안,보류,재검토"</formula1>
     </dataValidation>
   </dataValidations>
